--- a/config/becExpConfig/becExpType.csv.xlsx
+++ b/config/becExpConfig/becExpType.csv.xlsx
@@ -1,21 +1,21 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="28526"/>
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="28623"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\WOODHOUSE\Documents\MMUser\config\becExpConfig\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\scientist\Documents\MMUser\config\becExpConfig\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5D116D8D-EAD1-4468-8863-5B9B1AB26BCB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E5274D37-CE91-4156-85C5-7C764BAADD7E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="191029"/>
+  <calcPr calcId="191029" fullCalcOnLoad="true"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="37" uniqueCount="34">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="226" uniqueCount="212">
   <si>
     <t>TrialName</t>
   </si>
@@ -136,6 +136,540 @@
   </si>
   <si>
     <t>WaveformAssociation</t>
+  </si>
+  <si>
+    <t>FringeRemovalMask</t>
+  </si>
+  <si>
+    <t>[]</t>
+  </si>
+  <si>
+    <t>Test</t>
+  </si>
+  <si>
+    <t>A general test.</t>
+  </si>
+  <si>
+    <t>TOP</t>
+  </si>
+  <si>
+    <t>Full</t>
+  </si>
+  <si>
+    <t>None</t>
+  </si>
+  <si>
+    <t>[]</t>
+  </si>
+  <si>
+    <t>CiceroLogTime</t>
+  </si>
+  <si>
+    <t>DensityFit</t>
+  </si>
+  <si>
+    <t>None</t>
+  </si>
+  <si>
+    <t>LF</t>
+  </si>
+  <si>
+    <t>Absorption</t>
+  </si>
+  <si>
+    <t>RandomPolarization</t>
+  </si>
+  <si>
+    <t>BosonicGaussianFit1D</t>
+  </si>
+  <si>
+    <t>LinearFit1D</t>
+  </si>
+  <si>
+    <t>StdErr</t>
+  </si>
+  <si>
+    <t>None</t>
+  </si>
+  <si>
+    <t>Test2</t>
+  </si>
+  <si>
+    <t>A general test.</t>
+  </si>
+  <si>
+    <t>TOP</t>
+  </si>
+  <si>
+    <t>Full</t>
+  </si>
+  <si>
+    <t>None</t>
+  </si>
+  <si>
+    <t>[]</t>
+  </si>
+  <si>
+    <t>CiceroLogTime</t>
+  </si>
+  <si>
+    <t>DensityFit</t>
+  </si>
+  <si>
+    <t>None</t>
+  </si>
+  <si>
+    <t>LF</t>
+  </si>
+  <si>
+    <t>Absorption</t>
+  </si>
+  <si>
+    <t>RandomPolarization</t>
+  </si>
+  <si>
+    <t>BosonicGaussianFit1D</t>
+  </si>
+  <si>
+    <t>LinearFit1D</t>
+  </si>
+  <si>
+    <t>StdErr</t>
+  </si>
+  <si>
+    <t>None</t>
+  </si>
+  <si>
+    <t>TestTOF</t>
+  </si>
+  <si>
+    <t>A general test.</t>
+  </si>
+  <si>
+    <t>TOP</t>
+  </si>
+  <si>
+    <t>Full</t>
+  </si>
+  <si>
+    <t>None</t>
+  </si>
+  <si>
+    <t>[]</t>
+  </si>
+  <si>
+    <t>TOF</t>
+  </si>
+  <si>
+    <t>DensityFit</t>
+  </si>
+  <si>
+    <t>None</t>
+  </si>
+  <si>
+    <t>LF</t>
+  </si>
+  <si>
+    <t>Absorption</t>
+  </si>
+  <si>
+    <t>RandomPolarization</t>
+  </si>
+  <si>
+    <t>BosonicGaussianFit1D</t>
+  </si>
+  <si>
+    <t>LinearFit1D</t>
+  </si>
+  <si>
+    <t>StdErr</t>
+  </si>
+  <si>
+    <t>None</t>
+  </si>
+  <si>
+    <t>TestTOF</t>
+  </si>
+  <si>
+    <t>A general test.</t>
+  </si>
+  <si>
+    <t>TOP</t>
+  </si>
+  <si>
+    <t>Full</t>
+  </si>
+  <si>
+    <t>None</t>
+  </si>
+  <si>
+    <t>[111 208;196 154;296 143;374 148;404 202;416 297;416 367;330 388;198 384;110 350]</t>
+  </si>
+  <si>
+    <t>TOF</t>
+  </si>
+  <si>
+    <t>DensityFit</t>
+  </si>
+  <si>
+    <t>None</t>
+  </si>
+  <si>
+    <t>LF</t>
+  </si>
+  <si>
+    <t>Absorption</t>
+  </si>
+  <si>
+    <t>RandomPolarization</t>
+  </si>
+  <si>
+    <t>BosonicGaussianFit1D</t>
+  </si>
+  <si>
+    <t>LinearFit1D</t>
+  </si>
+  <si>
+    <t>StdErr</t>
+  </si>
+  <si>
+    <t>None</t>
+  </si>
+  <si>
+    <t>RMTOF</t>
+  </si>
+  <si>
+    <t>A general test.</t>
+  </si>
+  <si>
+    <t>TOP</t>
+  </si>
+  <si>
+    <t>Full</t>
+  </si>
+  <si>
+    <t>None</t>
+  </si>
+  <si>
+    <t>[]</t>
+  </si>
+  <si>
+    <t>CiceroLogTime</t>
+  </si>
+  <si>
+    <t>DensityFit</t>
+  </si>
+  <si>
+    <t>None</t>
+  </si>
+  <si>
+    <t>LF</t>
+  </si>
+  <si>
+    <t>Absorption</t>
+  </si>
+  <si>
+    <t>RandomPolarization</t>
+  </si>
+  <si>
+    <t>BosonicGaussianFit1D</t>
+  </si>
+  <si>
+    <t>LinearFit1D</t>
+  </si>
+  <si>
+    <t>StdErr</t>
+  </si>
+  <si>
+    <t>None</t>
+  </si>
+  <si>
+    <t>RMTOF</t>
+  </si>
+  <si>
+    <t>A general test.</t>
+  </si>
+  <si>
+    <t>TOP</t>
+  </si>
+  <si>
+    <t>Full</t>
+  </si>
+  <si>
+    <t>None</t>
+  </si>
+  <si>
+    <t>[]</t>
+  </si>
+  <si>
+    <t>TOF</t>
+  </si>
+  <si>
+    <t>DensityFit</t>
+  </si>
+  <si>
+    <t>None</t>
+  </si>
+  <si>
+    <t>LF</t>
+  </si>
+  <si>
+    <t>Absorption</t>
+  </si>
+  <si>
+    <t>RandomPolarization</t>
+  </si>
+  <si>
+    <t>BosonicGaussianFit1D</t>
+  </si>
+  <si>
+    <t>LinearFit1D</t>
+  </si>
+  <si>
+    <t>StdErr</t>
+  </si>
+  <si>
+    <t>None</t>
+  </si>
+  <si>
+    <t>RMTOF</t>
+  </si>
+  <si>
+    <t>Check Red MOT (RM) at different TOF</t>
+  </si>
+  <si>
+    <t>TOP</t>
+  </si>
+  <si>
+    <t>Full</t>
+  </si>
+  <si>
+    <t>None</t>
+  </si>
+  <si>
+    <t>[]</t>
+  </si>
+  <si>
+    <t>TOF</t>
+  </si>
+  <si>
+    <t>DensityFit</t>
+  </si>
+  <si>
+    <t>None</t>
+  </si>
+  <si>
+    <t>LF</t>
+  </si>
+  <si>
+    <t>Absorption</t>
+  </si>
+  <si>
+    <t>RandomPolarization</t>
+  </si>
+  <si>
+    <t>BosonicGaussianFit1D</t>
+  </si>
+  <si>
+    <t>LinearFit1D</t>
+  </si>
+  <si>
+    <t>StdErr</t>
+  </si>
+  <si>
+    <t>None</t>
+  </si>
+  <si>
+    <t>RMTOF</t>
+  </si>
+  <si>
+    <t>Check Red MOT (RM) at different TOF</t>
+  </si>
+  <si>
+    <t>TOP</t>
+  </si>
+  <si>
+    <t>Full</t>
+  </si>
+  <si>
+    <t>None</t>
+  </si>
+  <si>
+    <t>[]</t>
+  </si>
+  <si>
+    <t>TOF</t>
+  </si>
+  <si>
+    <t>AtomNumber;DensityFit</t>
+  </si>
+  <si>
+    <t>None</t>
+  </si>
+  <si>
+    <t>LF</t>
+  </si>
+  <si>
+    <t>Absorption</t>
+  </si>
+  <si>
+    <t>RandomPolarization</t>
+  </si>
+  <si>
+    <t>BosonicGaussianFit1D</t>
+  </si>
+  <si>
+    <t>LinearFit1D</t>
+  </si>
+  <si>
+    <t>StdErr</t>
+  </si>
+  <si>
+    <t>None</t>
+  </si>
+  <si>
+    <t>RMTOF</t>
+  </si>
+  <si>
+    <t>Check Red MOT (RM) at different TOF</t>
+  </si>
+  <si>
+    <t>TOP</t>
+  </si>
+  <si>
+    <t>Full</t>
+  </si>
+  <si>
+    <t>None</t>
+  </si>
+  <si>
+    <t>[]</t>
+  </si>
+  <si>
+    <t>TOF</t>
+  </si>
+  <si>
+    <t>Tof;AtomNumber;DensityFit</t>
+  </si>
+  <si>
+    <t>None</t>
+  </si>
+  <si>
+    <t>LF</t>
+  </si>
+  <si>
+    <t>Absorption</t>
+  </si>
+  <si>
+    <t>RandomPolarization</t>
+  </si>
+  <si>
+    <t>BosonicGaussianFit1D</t>
+  </si>
+  <si>
+    <t>LinearFit1D</t>
+  </si>
+  <si>
+    <t>StdErr</t>
+  </si>
+  <si>
+    <t>None</t>
+  </si>
+  <si>
+    <t>RMTOF</t>
+  </si>
+  <si>
+    <t>Check Red MOT (RM) at different TOF</t>
+  </si>
+  <si>
+    <t>TOP</t>
+  </si>
+  <si>
+    <t>Full</t>
+  </si>
+  <si>
+    <t>None</t>
+  </si>
+  <si>
+    <t>[]</t>
+  </si>
+  <si>
+    <t>TOF</t>
+  </si>
+  <si>
+    <t>Tof;AtomNumber;DensityFit</t>
+  </si>
+  <si>
+    <t>None</t>
+  </si>
+  <si>
+    <t>LF</t>
+  </si>
+  <si>
+    <t>Absorption</t>
+  </si>
+  <si>
+    <t>RandomPolarization</t>
+  </si>
+  <si>
+    <t>BosonicGaussianFit1D</t>
+  </si>
+  <si>
+    <t>LinearFit1D</t>
+  </si>
+  <si>
+    <t>StdErr</t>
+  </si>
+  <si>
+    <t>None</t>
+  </si>
+  <si>
+    <t>ODT</t>
+  </si>
+  <si>
+    <t>Check ODT at various TOF</t>
+  </si>
+  <si>
+    <t>TOP</t>
+  </si>
+  <si>
+    <t>Full</t>
+  </si>
+  <si>
+    <t>None</t>
+  </si>
+  <si>
+    <t>[111 208;196 154;296 143;374 148;404 202;416 297;416 367;330 388;198 384;110 350]</t>
+  </si>
+  <si>
+    <t>TOF</t>
+  </si>
+  <si>
+    <t>DensityFit;Tof;AtomNumber</t>
+  </si>
+  <si>
+    <t>None</t>
+  </si>
+  <si>
+    <t>LF</t>
+  </si>
+  <si>
+    <t>Absorption</t>
+  </si>
+  <si>
+    <t>RandomPolarization</t>
+  </si>
+  <si>
+    <t>BosonicGaussianFit1D</t>
+  </si>
+  <si>
+    <t>LinearFit1D</t>
+  </si>
+  <si>
+    <t>StdErr</t>
+  </si>
+  <si>
+    <t>None</t>
   </si>
 </sst>
 </file>
@@ -166,7 +700,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -174,13 +708,15 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border/>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="true"/>
+    <xf numFmtId="22" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="true"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -461,31 +997,33 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:T2"/>
+  <dimension ref="A1:U6"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="36.42578125" customWidth="1"/>
-    <col min="2" max="2" width="95.28515625" customWidth="1"/>
-    <col min="3" max="3" width="16.42578125" customWidth="1"/>
-    <col min="4" max="4" width="25.7109375" customWidth="1"/>
-    <col min="5" max="5" width="21.42578125" customWidth="1"/>
-    <col min="6" max="6" width="8" customWidth="1"/>
-    <col min="7" max="7" width="19.5703125" customWidth="1"/>
-    <col min="8" max="8" width="35.140625" customWidth="1"/>
-    <col min="9" max="9" width="21.42578125" customWidth="1"/>
-    <col min="10" max="10" width="13" customWidth="1"/>
-    <col min="11" max="11" width="17" customWidth="1"/>
-    <col min="12" max="12" width="19" customWidth="1"/>
-    <col min="13" max="13" width="7.85546875" customWidth="1"/>
-    <col min="14" max="14" width="20.42578125" customWidth="1"/>
-    <col min="15" max="15" width="17.42578125" customWidth="1"/>
-    <col min="16" max="16" width="16.42578125" customWidth="1"/>
-    <col min="17" max="17" width="17" customWidth="1"/>
-    <col min="18" max="18" width="16.85546875" customWidth="1"/>
-    <col min="19" max="19" width="17.28515625" customWidth="1"/>
+    <col min="1" max="1" width="10.28515625" customWidth="true"/>
+    <col min="2" max="2" width="34" customWidth="true"/>
+    <col min="3" max="3" width="16.42578125" customWidth="true"/>
+    <col min="4" max="4" width="9.28515625" customWidth="true"/>
+    <col min="5" max="5" width="21.42578125" customWidth="true"/>
+    <col min="6" max="6" width="8" customWidth="true"/>
+    <col min="8" max="8" width="17.85546875" customWidth="true"/>
+    <col min="9" max="9" width="26.28515625" customWidth="true"/>
+    <col min="10" max="10" width="21.42578125" customWidth="true"/>
+    <col min="11" max="11" width="13" customWidth="true"/>
+    <col min="12" max="12" width="15.140625" customWidth="true"/>
+    <col min="13" max="13" width="19" customWidth="true"/>
+    <col min="14" max="14" width="7.85546875" customWidth="true"/>
+    <col min="15" max="15" width="20.42578125" customWidth="true"/>
+    <col min="16" max="16" width="17.42578125" customWidth="true"/>
+    <col min="17" max="17" width="16.42578125" customWidth="true"/>
+    <col min="18" max="18" width="17" customWidth="true"/>
+    <col min="19" max="19" width="16.85546875" customWidth="true"/>
+    <col min="20" max="20" width="20.42578125" customWidth="true"/>
+    <col min="7" max="7" width="72" customWidth="true"/>
+    <col min="21" max="21" width="20.5703125" customWidth="true"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:20">
+    <row r="1">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -505,109 +1043,365 @@
         <v>4</v>
       </c>
       <c r="G1" t="s">
+        <v>34</v>
+      </c>
+      <c r="H1" t="s">
         <v>1</v>
       </c>
-      <c r="H1" t="s">
+      <c r="I1" t="s">
         <v>2</v>
       </c>
-      <c r="I1" t="s">
+      <c r="J1" t="s">
         <v>8</v>
       </c>
-      <c r="J1" t="s">
+      <c r="K1" t="s">
         <v>5</v>
       </c>
-      <c r="K1" t="s">
+      <c r="L1" t="s">
         <v>30</v>
       </c>
-      <c r="L1" t="s">
+      <c r="M1" t="s">
         <v>9</v>
       </c>
-      <c r="M1" t="s">
+      <c r="N1" t="s">
         <v>10</v>
       </c>
-      <c r="N1" t="s">
+      <c r="O1" t="s">
         <v>12</v>
       </c>
-      <c r="O1" t="s">
+      <c r="P1" t="s">
         <v>11</v>
       </c>
-      <c r="P1" t="s">
+      <c r="Q1" t="s">
         <v>20</v>
       </c>
-      <c r="Q1" t="s">
+      <c r="R1" t="s">
         <v>23</v>
       </c>
-      <c r="R1" t="s">
+      <c r="S1" t="s">
         <v>25</v>
       </c>
-      <c r="S1" t="s">
+      <c r="T1" t="s">
         <v>32</v>
       </c>
-      <c r="T1" t="s">
+      <c r="U1" t="s">
         <v>33</v>
       </c>
     </row>
-    <row r="2" spans="1:20">
-      <c r="A2" t="s">
-        <v>13</v>
-      </c>
-      <c r="B2" t="s">
-        <v>14</v>
-      </c>
-      <c r="C2" t="s">
-        <v>26</v>
-      </c>
-      <c r="D2" t="s">
-        <v>15</v>
-      </c>
-      <c r="E2" t="s">
-        <v>28</v>
-      </c>
-      <c r="F2">
+    <row r="2">
+      <c r="A2" s="0" t="s">
+        <v>36</v>
+      </c>
+      <c r="B2" s="0" t="s">
+        <v>37</v>
+      </c>
+      <c r="C2" s="0" t="s">
+        <v>38</v>
+      </c>
+      <c r="D2" s="0" t="s">
+        <v>39</v>
+      </c>
+      <c r="E2" s="0" t="s">
+        <v>40</v>
+      </c>
+      <c r="F2" s="0">
         <v>4</v>
       </c>
-      <c r="G2" t="s">
-        <v>16</v>
-      </c>
-      <c r="H2" t="s">
-        <v>29</v>
-      </c>
-      <c r="I2" t="s">
-        <v>17</v>
-      </c>
-      <c r="J2" t="s">
-        <v>18</v>
-      </c>
-      <c r="K2" t="s">
-        <v>31</v>
-      </c>
-      <c r="L2" t="s">
-        <v>27</v>
-      </c>
-      <c r="M2">
+      <c r="G2" s="0" t="s">
+        <v>41</v>
+      </c>
+      <c r="H2" s="0" t="s">
+        <v>42</v>
+      </c>
+      <c r="I2" s="0" t="s">
+        <v>43</v>
+      </c>
+      <c r="J2" s="0" t="s">
+        <v>44</v>
+      </c>
+      <c r="K2" s="0" t="s">
+        <v>45</v>
+      </c>
+      <c r="L2" s="0" t="s">
+        <v>46</v>
+      </c>
+      <c r="M2" s="0" t="s">
+        <v>47</v>
+      </c>
+      <c r="N2" s="0">
         <v>8</v>
       </c>
-      <c r="N2" t="s">
-        <v>19</v>
-      </c>
-      <c r="O2">
+      <c r="O2" s="0" t="s">
+        <v>48</v>
+      </c>
+      <c r="P2" s="0">
         <v>30</v>
       </c>
-      <c r="P2" t="s">
-        <v>21</v>
-      </c>
-      <c r="Q2" t="s">
-        <v>24</v>
-      </c>
-      <c r="R2" s="1" t="s">
-        <v>28</v>
-      </c>
-      <c r="S2" t="s">
-        <v>17</v>
-      </c>
-      <c r="T2" t="s">
-        <v>17</v>
-      </c>
+      <c r="Q2" s="0" t="s">
+        <v>49</v>
+      </c>
+      <c r="R2" s="0" t="s">
+        <v>50</v>
+      </c>
+      <c r="S2" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="T2" s="0" t="s">
+        <v>51</v>
+      </c>
+      <c r="U2" s="0"/>
+    </row>
+    <row r="3">
+      <c r="A3" s="0" t="s">
+        <v>52</v>
+      </c>
+      <c r="B3" s="0" t="s">
+        <v>53</v>
+      </c>
+      <c r="C3" s="0" t="s">
+        <v>54</v>
+      </c>
+      <c r="D3" s="0" t="s">
+        <v>55</v>
+      </c>
+      <c r="E3" s="0" t="s">
+        <v>56</v>
+      </c>
+      <c r="F3" s="0">
+        <v>4</v>
+      </c>
+      <c r="G3" s="0" t="s">
+        <v>57</v>
+      </c>
+      <c r="H3" s="0" t="s">
+        <v>58</v>
+      </c>
+      <c r="I3" s="0" t="s">
+        <v>59</v>
+      </c>
+      <c r="J3" s="0" t="s">
+        <v>60</v>
+      </c>
+      <c r="K3" s="0" t="s">
+        <v>61</v>
+      </c>
+      <c r="L3" s="0" t="s">
+        <v>62</v>
+      </c>
+      <c r="M3" s="0" t="s">
+        <v>63</v>
+      </c>
+      <c r="N3" s="0">
+        <v>8</v>
+      </c>
+      <c r="O3" s="0" t="s">
+        <v>64</v>
+      </c>
+      <c r="P3" s="0">
+        <v>30</v>
+      </c>
+      <c r="Q3" s="0" t="s">
+        <v>65</v>
+      </c>
+      <c r="R3" s="0" t="s">
+        <v>66</v>
+      </c>
+      <c r="S3" s="0" t="s">
+        <v>67</v>
+      </c>
+      <c r="T3" s="0" t="s">
+        <v>67</v>
+      </c>
+      <c r="U3" s="0"/>
+    </row>
+    <row r="4">
+      <c r="A4" s="0" t="s">
+        <v>84</v>
+      </c>
+      <c r="B4" s="0" t="s">
+        <v>85</v>
+      </c>
+      <c r="C4" s="0" t="s">
+        <v>86</v>
+      </c>
+      <c r="D4" s="0" t="s">
+        <v>87</v>
+      </c>
+      <c r="E4" s="0" t="s">
+        <v>88</v>
+      </c>
+      <c r="F4" s="0">
+        <v>4</v>
+      </c>
+      <c r="G4" s="0" t="s">
+        <v>89</v>
+      </c>
+      <c r="H4" s="0" t="s">
+        <v>90</v>
+      </c>
+      <c r="I4" s="0" t="s">
+        <v>91</v>
+      </c>
+      <c r="J4" s="0" t="s">
+        <v>92</v>
+      </c>
+      <c r="K4" s="0" t="s">
+        <v>93</v>
+      </c>
+      <c r="L4" s="0" t="s">
+        <v>94</v>
+      </c>
+      <c r="M4" s="0" t="s">
+        <v>95</v>
+      </c>
+      <c r="N4" s="0">
+        <v>8</v>
+      </c>
+      <c r="O4" s="0" t="s">
+        <v>96</v>
+      </c>
+      <c r="P4" s="0">
+        <v>30</v>
+      </c>
+      <c r="Q4" s="0" t="s">
+        <v>97</v>
+      </c>
+      <c r="R4" s="0" t="s">
+        <v>98</v>
+      </c>
+      <c r="S4" s="0" t="s">
+        <v>99</v>
+      </c>
+      <c r="T4" s="0" t="s">
+        <v>99</v>
+      </c>
+      <c r="U4" s="0"/>
+    </row>
+    <row r="5">
+      <c r="A5" s="0" t="s">
+        <v>180</v>
+      </c>
+      <c r="B5" s="0" t="s">
+        <v>181</v>
+      </c>
+      <c r="C5" s="0" t="s">
+        <v>182</v>
+      </c>
+      <c r="D5" s="0" t="s">
+        <v>183</v>
+      </c>
+      <c r="E5" s="0" t="s">
+        <v>184</v>
+      </c>
+      <c r="F5" s="0">
+        <v>4</v>
+      </c>
+      <c r="G5" s="0" t="s">
+        <v>185</v>
+      </c>
+      <c r="H5" s="0" t="s">
+        <v>186</v>
+      </c>
+      <c r="I5" s="0" t="s">
+        <v>187</v>
+      </c>
+      <c r="J5" s="0" t="s">
+        <v>188</v>
+      </c>
+      <c r="K5" s="0" t="s">
+        <v>189</v>
+      </c>
+      <c r="L5" s="0" t="s">
+        <v>190</v>
+      </c>
+      <c r="M5" s="0" t="s">
+        <v>191</v>
+      </c>
+      <c r="N5" s="0">
+        <v>8</v>
+      </c>
+      <c r="O5" s="0" t="s">
+        <v>192</v>
+      </c>
+      <c r="P5" s="0">
+        <v>30</v>
+      </c>
+      <c r="Q5" s="0" t="s">
+        <v>193</v>
+      </c>
+      <c r="R5" s="0" t="s">
+        <v>194</v>
+      </c>
+      <c r="S5" s="0" t="s">
+        <v>195</v>
+      </c>
+      <c r="T5" s="0" t="s">
+        <v>195</v>
+      </c>
+      <c r="U5" s="0"/>
+    </row>
+    <row r="6">
+      <c r="A6" s="0" t="s">
+        <v>196</v>
+      </c>
+      <c r="B6" s="0" t="s">
+        <v>197</v>
+      </c>
+      <c r="C6" s="0" t="s">
+        <v>198</v>
+      </c>
+      <c r="D6" s="0" t="s">
+        <v>199</v>
+      </c>
+      <c r="E6" s="0" t="s">
+        <v>200</v>
+      </c>
+      <c r="F6" s="0">
+        <v>4</v>
+      </c>
+      <c r="G6" s="0" t="s">
+        <v>201</v>
+      </c>
+      <c r="H6" s="0" t="s">
+        <v>202</v>
+      </c>
+      <c r="I6" s="0" t="s">
+        <v>203</v>
+      </c>
+      <c r="J6" s="0" t="s">
+        <v>204</v>
+      </c>
+      <c r="K6" s="0" t="s">
+        <v>205</v>
+      </c>
+      <c r="L6" s="0" t="s">
+        <v>206</v>
+      </c>
+      <c r="M6" s="0" t="s">
+        <v>207</v>
+      </c>
+      <c r="N6" s="0">
+        <v>8</v>
+      </c>
+      <c r="O6" s="0" t="s">
+        <v>208</v>
+      </c>
+      <c r="P6" s="0">
+        <v>30</v>
+      </c>
+      <c r="Q6" s="0" t="s">
+        <v>209</v>
+      </c>
+      <c r="R6" s="0" t="s">
+        <v>210</v>
+      </c>
+      <c r="S6" s="0" t="s">
+        <v>211</v>
+      </c>
+      <c r="T6" s="0" t="s">
+        <v>211</v>
+      </c>
+      <c r="U6" s="0"/>
     </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>

--- a/config/becExpConfig/becExpType.csv.xlsx
+++ b/config/becExpConfig/becExpType.csv.xlsx
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1465" uniqueCount="1198">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1936" uniqueCount="1669">
   <si>
     <t>TrialName</t>
   </si>
@@ -3624,6 +3624,1419 @@
   </si>
   <si>
     <t>PhaseLockName,ImagingLock;Frequency,700000000;VariableName,hw_ImagingLf</t>
+  </si>
+  <si>
+    <t>NiBecIMCNonInter</t>
+  </si>
+  <si>
+    <t>An experiment at the non-interacting BEC stage. Scan NI imaging frequency.</t>
+  </si>
+  <si>
+    <t>TOP</t>
+  </si>
+  <si>
+    <t>Bec</t>
+  </si>
+  <si>
+    <t>None</t>
+  </si>
+  <si>
+    <t>hw_ImagingNi</t>
+  </si>
+  <si>
+    <t>DensityFit;AtomNumber</t>
+  </si>
+  <si>
+    <t>LSR</t>
+  </si>
+  <si>
+    <t>[935 1602;959 1624;1000 1632;1030 1596;1033 1565;1017 1546;965 1539;941 1549]</t>
+  </si>
+  <si>
+    <t>NI</t>
+  </si>
+  <si>
+    <t>Absorption</t>
+  </si>
+  <si>
+    <t>StrongLight</t>
+  </si>
+  <si>
+    <t>BosonicGaussianFit1D</t>
+  </si>
+  <si>
+    <t>None</t>
+  </si>
+  <si>
+    <t>ParabolicFit1D</t>
+  </si>
+  <si>
+    <t>StdErr</t>
+  </si>
+  <si>
+    <t>WaveformGeneratorName,XvWingMod;ChannelName,Ch1;WaveformListName,XvWingNi</t>
+  </si>
+  <si>
+    <t>PhaseLockName,ImagingLock;Frequency,700000000;VariableName,hw_ImagingNi</t>
+  </si>
+  <si>
+    <t>NiLatticeSdCalibFreqStart</t>
+  </si>
+  <si>
+    <t>An experiment at the non-interacting lattice stage. Scan hw_SdCalibFreqStart.</t>
+  </si>
+  <si>
+    <t>TOP</t>
+  </si>
+  <si>
+    <t>NiLatticeDepthCalib</t>
+  </si>
+  <si>
+    <t>None</t>
+  </si>
+  <si>
+    <t>hw_SdCalibFreqStart</t>
+  </si>
+  <si>
+    <t>DensityFit;AtomNumber</t>
+  </si>
+  <si>
+    <t>LSR</t>
+  </si>
+  <si>
+    <t>HF</t>
+  </si>
+  <si>
+    <t>Absorption</t>
+  </si>
+  <si>
+    <t>StrongLight</t>
+  </si>
+  <si>
+    <t>BosonicGaussianFit1D</t>
+  </si>
+  <si>
+    <t>None</t>
+  </si>
+  <si>
+    <t>ParabolicFit1D</t>
+  </si>
+  <si>
+    <t>StdErr</t>
+  </si>
+  <si>
+    <t>WaveformGeneratorName,LatticeMod,XvWingMod;ChannelName,Ch2,Ch1;WaveformListName,SdDepthCalib,XvWingNi</t>
+  </si>
+  <si>
+    <t>PhaseLockName,ImagingLock;Frequency,700000000;VariableName,hw_ImagingNi</t>
+  </si>
+  <si>
+    <t>NiLatticeSdCalibFreqStart</t>
+  </si>
+  <si>
+    <t>An experiment at the non-interacting lattice stage. Scan hw_SdCalibFreqStart.</t>
+  </si>
+  <si>
+    <t>TOP</t>
+  </si>
+  <si>
+    <t>NiLatticeDepthCalib</t>
+  </si>
+  <si>
+    <t>None</t>
+  </si>
+  <si>
+    <t>hw_SdCalibFreqStart</t>
+  </si>
+  <si>
+    <t>DensityFit;AtomNumber</t>
+  </si>
+  <si>
+    <t>LSR</t>
+  </si>
+  <si>
+    <t>HF</t>
+  </si>
+  <si>
+    <t>Absorption</t>
+  </si>
+  <si>
+    <t>StrongLight</t>
+  </si>
+  <si>
+    <t>BosonicGaussianFit1D</t>
+  </si>
+  <si>
+    <t>None</t>
+  </si>
+  <si>
+    <t>ParabolicFit1D</t>
+  </si>
+  <si>
+    <t>StdErr</t>
+  </si>
+  <si>
+    <t>WaveformGeneratorName,LatticeMod,XvWingMod;ChannelName,Ch2,Ch1;WaveformListName,SdDepthCalib,XvWingNi</t>
+  </si>
+  <si>
+    <t>PhaseLockName,ImagingLock;Frequency,700000000;VariableName,hw_ImagingNi</t>
+  </si>
+  <si>
+    <t>EvapD</t>
+  </si>
+  <si>
+    <t>An experiment at evaporation stage D.</t>
+  </si>
+  <si>
+    <t>TOP</t>
+  </si>
+  <si>
+    <t>EvapDOdt1</t>
+  </si>
+  <si>
+    <t>None</t>
+  </si>
+  <si>
+    <t>CiceroLogTime</t>
+  </si>
+  <si>
+    <t>AtomNumber;DensityFit;CenterFit</t>
+  </si>
+  <si>
+    <t>LSR</t>
+  </si>
+  <si>
+    <t>[549 1745;903 1905;1286 1930;1532 1678;1603 1325;1617 1085;1501 850;1355 743;908 715;693 740;535 925;522 1284]</t>
+  </si>
+  <si>
+    <t>LF</t>
+  </si>
+  <si>
+    <t>Absorption</t>
+  </si>
+  <si>
+    <t>RandomPolarization</t>
+  </si>
+  <si>
+    <t>BosonicGaussianFit1D</t>
+  </si>
+  <si>
+    <t>None</t>
+  </si>
+  <si>
+    <t>LinearFit1D</t>
+  </si>
+  <si>
+    <t>StdErr</t>
+  </si>
+  <si>
+    <t>PhaseLockName,ImagingLock;Frequency,700000000;VariableName,hw_ImagingLf</t>
+  </si>
+  <si>
+    <t>NiLatticeSdCalibFreqStart</t>
+  </si>
+  <si>
+    <t>An experiment at the non-interacting lattice stage. Scan hw_SdCalibFreqStart.</t>
+  </si>
+  <si>
+    <t>TOP</t>
+  </si>
+  <si>
+    <t>NiLatticeDepthCalibTof6000</t>
+  </si>
+  <si>
+    <t>None</t>
+  </si>
+  <si>
+    <t>hw_SdCalibFreqStart</t>
+  </si>
+  <si>
+    <t>DensityFit;AtomNumber</t>
+  </si>
+  <si>
+    <t>LSR</t>
+  </si>
+  <si>
+    <t>HF</t>
+  </si>
+  <si>
+    <t>Absorption</t>
+  </si>
+  <si>
+    <t>StrongLight</t>
+  </si>
+  <si>
+    <t>BosonicGaussianFit1D</t>
+  </si>
+  <si>
+    <t>None</t>
+  </si>
+  <si>
+    <t>ParabolicFit1D</t>
+  </si>
+  <si>
+    <t>StdErr</t>
+  </si>
+  <si>
+    <t>WaveformGeneratorName,LatticeMod,XvWingMod;ChannelName,Ch2,Ch1;WaveformListName,SdDepthCalib,XvWingNi</t>
+  </si>
+  <si>
+    <t>PhaseLockName,ImagingLock;Frequency,700000000;VariableName,hw_ImagingNi</t>
+  </si>
+  <si>
+    <t>NiLatticePdModDepth</t>
+  </si>
+  <si>
+    <t>An experiment at the non-interacting lattice stage. Scan PD modulation depth.</t>
+  </si>
+  <si>
+    <t>TOP</t>
+  </si>
+  <si>
+    <t>BMPDloopTof6000</t>
+  </si>
+  <si>
+    <t>None</t>
+  </si>
+  <si>
+    <t>hw_PdModDepth</t>
+  </si>
+  <si>
+    <t>DensityFit;AtomNumber</t>
+  </si>
+  <si>
+    <t>LSR</t>
+  </si>
+  <si>
+    <t>[472 1324;662 1408;1019 1467;1425 1547;1509 1503;1526 1442;1450 1382;1185 1334;857 1266;548 1231;495 1256]</t>
+  </si>
+  <si>
+    <t>HF</t>
+  </si>
+  <si>
+    <t>Absorption</t>
+  </si>
+  <si>
+    <t>StrongLight</t>
+  </si>
+  <si>
+    <t>BosonicGaussianFit1D</t>
+  </si>
+  <si>
+    <t>None</t>
+  </si>
+  <si>
+    <t>LinearFit1D</t>
+  </si>
+  <si>
+    <t>StdErr</t>
+  </si>
+  <si>
+    <t>PhaseLockName,ImagingLock;Frequency,700000000;VariableName,hw_ImagingNi</t>
+  </si>
+  <si>
+    <t>NiLatticePdModDepth</t>
+  </si>
+  <si>
+    <t>An experiment at the non-interacting lattice stage. Scan PD modulation depth.</t>
+  </si>
+  <si>
+    <t>TOP</t>
+  </si>
+  <si>
+    <t>BMPDloopTof6000</t>
+  </si>
+  <si>
+    <t>None</t>
+  </si>
+  <si>
+    <t>hw_PdModDepth</t>
+  </si>
+  <si>
+    <t>DensityFit;AtomNumber</t>
+  </si>
+  <si>
+    <t>LSR</t>
+  </si>
+  <si>
+    <t>[1481 1300;350 1352;339 1212;1496 1146]</t>
+  </si>
+  <si>
+    <t>HF</t>
+  </si>
+  <si>
+    <t>Absorption</t>
+  </si>
+  <si>
+    <t>StrongLight</t>
+  </si>
+  <si>
+    <t>BosonicGaussianFit1D</t>
+  </si>
+  <si>
+    <t>None</t>
+  </si>
+  <si>
+    <t>LinearFit1D</t>
+  </si>
+  <si>
+    <t>StdErr</t>
+  </si>
+  <si>
+    <t>PhaseLockName,ImagingLock;Frequency,700000000;VariableName,hw_ImagingNi</t>
+  </si>
+  <si>
+    <t>NiLatticePdModDepth</t>
+  </si>
+  <si>
+    <t>An experiment at the non-interacting lattice stage. Scan PD modulation depth.</t>
+  </si>
+  <si>
+    <t>TOP</t>
+  </si>
+  <si>
+    <t>BMPDloopTof6000</t>
+  </si>
+  <si>
+    <t>None</t>
+  </si>
+  <si>
+    <t>hw_PdModDepth</t>
+  </si>
+  <si>
+    <t>DensityFit;AtomNumber</t>
+  </si>
+  <si>
+    <t>LSR</t>
+  </si>
+  <si>
+    <t>[405 1189;681 1173;1573 1141;1664 1288;1578 1335;814 1380;432 1392;357 1309]</t>
+  </si>
+  <si>
+    <t>HF</t>
+  </si>
+  <si>
+    <t>Absorption</t>
+  </si>
+  <si>
+    <t>StrongLight</t>
+  </si>
+  <si>
+    <t>BosonicGaussianFit1D</t>
+  </si>
+  <si>
+    <t>None</t>
+  </si>
+  <si>
+    <t>LinearFit1D</t>
+  </si>
+  <si>
+    <t>StdErr</t>
+  </si>
+  <si>
+    <t>PhaseLockName,ImagingLock;Frequency,700000000;VariableName,hw_ImagingNi</t>
+  </si>
+  <si>
+    <t>NiLatticePdModDepth</t>
+  </si>
+  <si>
+    <t>An experiment at the non-interacting lattice stage. Scan PD modulation depth.</t>
+  </si>
+  <si>
+    <t>TOP</t>
+  </si>
+  <si>
+    <t>BMPDloopTof8000</t>
+  </si>
+  <si>
+    <t>None</t>
+  </si>
+  <si>
+    <t>hw_PdModDepth</t>
+  </si>
+  <si>
+    <t>DensityFit;AtomNumber</t>
+  </si>
+  <si>
+    <t>LSR</t>
+  </si>
+  <si>
+    <t>[405 1189;681 1173;1573 1141;1664 1288;1578 1335;814 1380;432 1392;357 1309]</t>
+  </si>
+  <si>
+    <t>HF</t>
+  </si>
+  <si>
+    <t>Absorption</t>
+  </si>
+  <si>
+    <t>StrongLight</t>
+  </si>
+  <si>
+    <t>BosonicGaussianFit1D</t>
+  </si>
+  <si>
+    <t>None</t>
+  </si>
+  <si>
+    <t>LinearFit1D</t>
+  </si>
+  <si>
+    <t>StdErr</t>
+  </si>
+  <si>
+    <t>PhaseLockName,ImagingLock;Frequency,700000000;VariableName,hw_ImagingNi</t>
+  </si>
+  <si>
+    <t>NiLatticeXvLatticeBm</t>
+  </si>
+  <si>
+    <t>An experiment at the non-interacting lattice stage. Scan xvlattice. With band mapping.</t>
+  </si>
+  <si>
+    <t>TOP</t>
+  </si>
+  <si>
+    <t>BMPDloopTof8000</t>
+  </si>
+  <si>
+    <t>None</t>
+  </si>
+  <si>
+    <t>hw_XvLattice</t>
+  </si>
+  <si>
+    <t>DensityFit;AtomNumber</t>
+  </si>
+  <si>
+    <t>LSR</t>
+  </si>
+  <si>
+    <t>[990 1542;442 1576;429 1460;1047 1449;1591 1420;1594 1530]</t>
+  </si>
+  <si>
+    <t>HF</t>
+  </si>
+  <si>
+    <t>Absorption</t>
+  </si>
+  <si>
+    <t>StrongLight</t>
+  </si>
+  <si>
+    <t>BosonicGaussianFit1D</t>
+  </si>
+  <si>
+    <t>None</t>
+  </si>
+  <si>
+    <t>LinearFit1D</t>
+  </si>
+  <si>
+    <t>StdErr</t>
+  </si>
+  <si>
+    <t>WaveformGeneratorName,LatticeMod,XvWingMod;ChannelName,Ch2,Ch1;WaveformListName,PdAi,XvWingLattice</t>
+  </si>
+  <si>
+    <t>PhaseLockName,ImagingLock;Frequency,700000000;VariableName,hw_ImagingNi</t>
+  </si>
+  <si>
+    <t>NiLatticeXvLatticeBm</t>
+  </si>
+  <si>
+    <t>An experiment at the non-interacting lattice stage. Scan xvlattice. With band mapping.</t>
+  </si>
+  <si>
+    <t>TOP</t>
+  </si>
+  <si>
+    <t>BMPDloopTof8000</t>
+  </si>
+  <si>
+    <t>None</t>
+  </si>
+  <si>
+    <t>hw_XvLattice</t>
+  </si>
+  <si>
+    <t>DensityFit;AtomNumber</t>
+  </si>
+  <si>
+    <t>LSR</t>
+  </si>
+  <si>
+    <t>[353 1231;517 1162;1370 1128;1605 1136;1657 1227;1628 1333;1262 1362;668 1384;385 1392;364 1330]</t>
+  </si>
+  <si>
+    <t>HF</t>
+  </si>
+  <si>
+    <t>Absorption</t>
+  </si>
+  <si>
+    <t>StrongLight</t>
+  </si>
+  <si>
+    <t>BosonicGaussianFit1D</t>
+  </si>
+  <si>
+    <t>None</t>
+  </si>
+  <si>
+    <t>LinearFit1D</t>
+  </si>
+  <si>
+    <t>StdErr</t>
+  </si>
+  <si>
+    <t>WaveformGeneratorName,LatticeMod,XvWingMod;ChannelName,Ch2,Ch1;WaveformListName,PdAi,XvWingLattice</t>
+  </si>
+  <si>
+    <t>PhaseLockName,ImagingLock;Frequency,700000000;VariableName,hw_ImagingNi</t>
+  </si>
+  <si>
+    <t>NiLatticeKP2VVA</t>
+  </si>
+  <si>
+    <t>An experiment at the non-interacting lattice stage. Scan KP2VVA.</t>
+  </si>
+  <si>
+    <t>TOP</t>
+  </si>
+  <si>
+    <t>NiLatticeDepthCalibTof8000</t>
+  </si>
+  <si>
+    <t>None</t>
+  </si>
+  <si>
+    <t>KP2VVA</t>
+  </si>
+  <si>
+    <t>DensityFit;AtomNumber</t>
+  </si>
+  <si>
+    <t>LSR</t>
+  </si>
+  <si>
+    <t>[663 1306;740 1266;897 1252;1209 1242;1363 1249;1367 1346;1350 1392;1186 1395;931 1409;692 1415]</t>
+  </si>
+  <si>
+    <t>HF</t>
+  </si>
+  <si>
+    <t>Absorption</t>
+  </si>
+  <si>
+    <t>StrongLight</t>
+  </si>
+  <si>
+    <t>BosonicGaussianFit1D</t>
+  </si>
+  <si>
+    <t>None</t>
+  </si>
+  <si>
+    <t>ParabolicFit1D</t>
+  </si>
+  <si>
+    <t>StdErr</t>
+  </si>
+  <si>
+    <t>WaveformGeneratorName,LatticeMod,XvWingMod;ChannelName,Ch2,Ch1;WaveformListName,SdDepthCalib,XvWingNi</t>
+  </si>
+  <si>
+    <t>PhaseLockName,ImagingLock;Frequency,700000000;VariableName,hw_ImagingNi</t>
+  </si>
+  <si>
+    <t>NiLatticeKP2VVA</t>
+  </si>
+  <si>
+    <t>An experiment at the non-interacting lattice stage. Scan KP2VVA.</t>
+  </si>
+  <si>
+    <t>TOP</t>
+  </si>
+  <si>
+    <t>NiLatticeDepthCalibTof8000</t>
+  </si>
+  <si>
+    <t>None</t>
+  </si>
+  <si>
+    <t>KP2VVA</t>
+  </si>
+  <si>
+    <t>DensityFit;AtomNumber</t>
+  </si>
+  <si>
+    <t>LSR</t>
+  </si>
+  <si>
+    <t>[499 1181;674 1101;1129 1095;1440 1108;1494 1174;1485 1357;1357 1397;969 1436;668 1432;530 1388]</t>
+  </si>
+  <si>
+    <t>HF</t>
+  </si>
+  <si>
+    <t>Absorption</t>
+  </si>
+  <si>
+    <t>StrongLight</t>
+  </si>
+  <si>
+    <t>BosonicGaussianFit1D</t>
+  </si>
+  <si>
+    <t>None</t>
+  </si>
+  <si>
+    <t>ParabolicFit1D</t>
+  </si>
+  <si>
+    <t>StdErr</t>
+  </si>
+  <si>
+    <t>WaveformGeneratorName,LatticeMod,XvWingMod;ChannelName,Ch2,Ch1;WaveformListName,SdDepthCalib,XvWingNi</t>
+  </si>
+  <si>
+    <t>PhaseLockName,ImagingLock;Frequency,700000000;VariableName,hw_ImagingNi</t>
+  </si>
+  <si>
+    <t>NiLatticeKP2VVA</t>
+  </si>
+  <si>
+    <t>An experiment at the non-interacting lattice stage. Scan KP2VVA.</t>
+  </si>
+  <si>
+    <t>TOP</t>
+  </si>
+  <si>
+    <t>NiLatticeDepthCalibTof8000</t>
+  </si>
+  <si>
+    <t>None</t>
+  </si>
+  <si>
+    <t>KP2VVA</t>
+  </si>
+  <si>
+    <t>DensityFit;AtomNumber</t>
+  </si>
+  <si>
+    <t>LSR</t>
+  </si>
+  <si>
+    <t>[499 1181;674 1101;1129 1095;1440 1108;1494 1174;1485 1357;1357 1397;969 1436;668 1432;530 1388]</t>
+  </si>
+  <si>
+    <t>HF</t>
+  </si>
+  <si>
+    <t>Absorption</t>
+  </si>
+  <si>
+    <t>StrongLight</t>
+  </si>
+  <si>
+    <t>BosonicGaussianFit1D</t>
+  </si>
+  <si>
+    <t>None</t>
+  </si>
+  <si>
+    <t>ParabolicFit1D</t>
+  </si>
+  <si>
+    <t>StdErr</t>
+  </si>
+  <si>
+    <t>WaveformGeneratorName,LatticeMod,XvWingMod;ChannelName,Ch2,Ch1;WaveformListName,SdDepthCalib,XvWingNi</t>
+  </si>
+  <si>
+    <t>PhaseLockName,ImagingLock;Frequency,700000000;VariableName,hw_ImagingNi</t>
+  </si>
+  <si>
+    <t>NiLatticeKP2VVA</t>
+  </si>
+  <si>
+    <t>An experiment at the non-interacting lattice stage. Scan KP2VVA.</t>
+  </si>
+  <si>
+    <t>TOP</t>
+  </si>
+  <si>
+    <t>NiLatticeDepthCalibTof8000</t>
+  </si>
+  <si>
+    <t>None</t>
+  </si>
+  <si>
+    <t>KP2VVA</t>
+  </si>
+  <si>
+    <t>DensityFit;AtomNumber</t>
+  </si>
+  <si>
+    <t>LSR</t>
+  </si>
+  <si>
+    <t>[428 1188;595 1085;914 1060;1346 1060;1549 1122;1581 1345;1453 1464;1010 1503;481 1490]</t>
+  </si>
+  <si>
+    <t>HF</t>
+  </si>
+  <si>
+    <t>Absorption</t>
+  </si>
+  <si>
+    <t>StrongLight</t>
+  </si>
+  <si>
+    <t>BosonicGaussianFit1D</t>
+  </si>
+  <si>
+    <t>None</t>
+  </si>
+  <si>
+    <t>ParabolicFit1D</t>
+  </si>
+  <si>
+    <t>StdErr</t>
+  </si>
+  <si>
+    <t>WaveformGeneratorName,LatticeMod,XvWingMod;ChannelName,Ch2,Ch1;WaveformListName,SdDepthCalib,XvWingNi</t>
+  </si>
+  <si>
+    <t>PhaseLockName,ImagingLock;Frequency,700000000;VariableName,hw_ImagingNi</t>
+  </si>
+  <si>
+    <t>NiBecPci</t>
+  </si>
+  <si>
+    <t>An experiment at the non-interacting BEC stage.</t>
+  </si>
+  <si>
+    <t>TOP</t>
+  </si>
+  <si>
+    <t>Bec</t>
+  </si>
+  <si>
+    <t>None</t>
+  </si>
+  <si>
+    <t>RunIndex</t>
+  </si>
+  <si>
+    <t>DensityFit;AtomNumber;CenterFit</t>
+  </si>
+  <si>
+    <t>LSR</t>
+  </si>
+  <si>
+    <t>[883 1331;920 1373;977 1409;1044 1385;1079 1289;1076 1226;1060 1180;1016 1173;953 1169;903 1189;878 1246]</t>
+  </si>
+  <si>
+    <t>NI</t>
+  </si>
+  <si>
+    <t>Absorption</t>
+  </si>
+  <si>
+    <t>StrongLight</t>
+  </si>
+  <si>
+    <t>BosonicGaussianFit1D</t>
+  </si>
+  <si>
+    <t>None</t>
+  </si>
+  <si>
+    <t>ParabolicFit1D</t>
+  </si>
+  <si>
+    <t>StdErr</t>
+  </si>
+  <si>
+    <t>WaveformGeneratorName,XvWingMod;ChannelName,Ch1;WaveformListName,XvWingNi</t>
+  </si>
+  <si>
+    <t>PhaseLockName,ImagingLock;Frequency,700000000;VariableName,hw_ImagingNi</t>
+  </si>
+  <si>
+    <t>HfBecPci</t>
+  </si>
+  <si>
+    <t>An experiment at the high-field BEC stage.</t>
+  </si>
+  <si>
+    <t>TOP</t>
+  </si>
+  <si>
+    <t>Bec</t>
+  </si>
+  <si>
+    <t>RunIndex</t>
+  </si>
+  <si>
+    <t>DensityFit;AtomNumber</t>
+  </si>
+  <si>
+    <t>LSR</t>
+  </si>
+  <si>
+    <t>[883 1377;966 1445;1038 1463;1096 1410;1124 1337;1126 1262;1065 1216;1013 1203;958 1212;897 1248;871 1292]</t>
+  </si>
+  <si>
+    <t>HF</t>
+  </si>
+  <si>
+    <t>Absorption</t>
+  </si>
+  <si>
+    <t>StrongLight</t>
+  </si>
+  <si>
+    <t>BosonicGaussianFit1D</t>
+  </si>
+  <si>
+    <t>None</t>
+  </si>
+  <si>
+    <t>LinearFit1D</t>
+  </si>
+  <si>
+    <t>StdErr</t>
+  </si>
+  <si>
+    <t>WaveformGeneratorName,XvWingMod;ChannelName,Ch1;WaveformListName,XvWingHf</t>
+  </si>
+  <si>
+    <t>PhaseLockName,ImagingLock;Frequency,700000000;VariableName,hw_ImagingHf</t>
+  </si>
+  <si>
+    <t>NiBecPci</t>
+  </si>
+  <si>
+    <t>An experiment at the non-interacting BEC stage.</t>
+  </si>
+  <si>
+    <t>TOP</t>
+  </si>
+  <si>
+    <t>Bec</t>
+  </si>
+  <si>
+    <t>None</t>
+  </si>
+  <si>
+    <t>hw_ImagingPci</t>
+  </si>
+  <si>
+    <t>DensityFit;AtomNumber;CenterFit</t>
+  </si>
+  <si>
+    <t>LSR</t>
+  </si>
+  <si>
+    <t>[883 1331;920 1373;977 1409;1044 1385;1079 1289;1076 1226;1060 1180;1016 1173;953 1169;903 1189;878 1246]</t>
+  </si>
+  <si>
+    <t>NI</t>
+  </si>
+  <si>
+    <t>Absorption</t>
+  </si>
+  <si>
+    <t>StrongLight</t>
+  </si>
+  <si>
+    <t>BosonicGaussianFit1D</t>
+  </si>
+  <si>
+    <t>None</t>
+  </si>
+  <si>
+    <t>ParabolicFit1D</t>
+  </si>
+  <si>
+    <t>StdErr</t>
+  </si>
+  <si>
+    <t>WaveformGeneratorName,XvWingMod;ChannelName,Ch1;WaveformListName,XvWingNi</t>
+  </si>
+  <si>
+    <t>PhaseLockName,ImagingLock;Frequency,700000000;VariableName,hw_ImagingNi</t>
+  </si>
+  <si>
+    <t>NiBecPci</t>
+  </si>
+  <si>
+    <t>An experiment at the non-interacting BEC stage.</t>
+  </si>
+  <si>
+    <t>TOP</t>
+  </si>
+  <si>
+    <t>Bec</t>
+  </si>
+  <si>
+    <t>None</t>
+  </si>
+  <si>
+    <t>hw_ImagingPci</t>
+  </si>
+  <si>
+    <t>DensityFit;AtomNumber;CenterFit</t>
+  </si>
+  <si>
+    <t>LSR</t>
+  </si>
+  <si>
+    <t>[883 1331;920 1373;977 1409;1044 1385;1079 1289;1076 1226;1060 1180;1016 1173;953 1169;903 1189;878 1246]</t>
+  </si>
+  <si>
+    <t>NI</t>
+  </si>
+  <si>
+    <t>Absorption</t>
+  </si>
+  <si>
+    <t>StrongLight</t>
+  </si>
+  <si>
+    <t>BosonicGaussianFit1D</t>
+  </si>
+  <si>
+    <t>None</t>
+  </si>
+  <si>
+    <t>ParabolicFit1D</t>
+  </si>
+  <si>
+    <t>StdErr</t>
+  </si>
+  <si>
+    <t>WaveformGeneratorName,XvWingMod;ChannelName,Ch1;WaveformListName,XvWingNi</t>
+  </si>
+  <si>
+    <t>PhaseLockName,ImagingLock;Frequency,700000000;VariableName,hw_ImagingNi</t>
+  </si>
+  <si>
+    <t>NiBecPci</t>
+  </si>
+  <si>
+    <t>An experiment at the non-interacting BEC stage.</t>
+  </si>
+  <si>
+    <t>TOP</t>
+  </si>
+  <si>
+    <t>Bec</t>
+  </si>
+  <si>
+    <t>None</t>
+  </si>
+  <si>
+    <t>hw_ImagingPci</t>
+  </si>
+  <si>
+    <t>DensityFit;AtomNumber;CenterFit</t>
+  </si>
+  <si>
+    <t>LSR</t>
+  </si>
+  <si>
+    <t>[883 1331;920 1373;977 1409;1044 1385;1079 1289;1076 1226;1060 1180;1016 1173;953 1169;903 1189;878 1246]</t>
+  </si>
+  <si>
+    <t>NI</t>
+  </si>
+  <si>
+    <t>Absorption</t>
+  </si>
+  <si>
+    <t>StrongLight</t>
+  </si>
+  <si>
+    <t>BosonicGaussianFit1D</t>
+  </si>
+  <si>
+    <t>None</t>
+  </si>
+  <si>
+    <t>ParabolicFit1D</t>
+  </si>
+  <si>
+    <t>StdErr</t>
+  </si>
+  <si>
+    <t>WaveformGeneratorName,XvWingMod;ChannelName,Ch1;WaveformListName,XvWingNi</t>
+  </si>
+  <si>
+    <t>PhaseLockName,ImagingLock;Frequency,700000000;VariableName,hw_ImagingPci</t>
+  </si>
+  <si>
+    <t>EvapD</t>
+  </si>
+  <si>
+    <t>An experiment at evaporation stage D.</t>
+  </si>
+  <si>
+    <t>TOP</t>
+  </si>
+  <si>
+    <t>EvapDOdt1</t>
+  </si>
+  <si>
+    <t>None</t>
+  </si>
+  <si>
+    <t>CiceroLogTime</t>
+  </si>
+  <si>
+    <t>AtomNumber;DensityFit;CenterFit</t>
+  </si>
+  <si>
+    <t>LSR</t>
+  </si>
+  <si>
+    <t>[549 1745;903 1905;1286 1930;1532 1678;1603 1325;1617 1085;1501 850;1355 743;908 715;693 740;535 925;522 1284]</t>
+  </si>
+  <si>
+    <t>LF</t>
+  </si>
+  <si>
+    <t>Absorption</t>
+  </si>
+  <si>
+    <t>RandomPolarization</t>
+  </si>
+  <si>
+    <t>BosonicGaussianFit1D</t>
+  </si>
+  <si>
+    <t>None</t>
+  </si>
+  <si>
+    <t>LinearFit1D</t>
+  </si>
+  <si>
+    <t>StdErr</t>
+  </si>
+  <si>
+    <t>PhaseLockName,ImagingLock;Frequency,700000000;VariableName,hw_ImagingLf</t>
+  </si>
+  <si>
+    <t>NiBec</t>
+  </si>
+  <si>
+    <t>An experiment at the non-interacting BEC stage.</t>
+  </si>
+  <si>
+    <t>TOP</t>
+  </si>
+  <si>
+    <t>Bec</t>
+  </si>
+  <si>
+    <t>None</t>
+  </si>
+  <si>
+    <t>RunIndex</t>
+  </si>
+  <si>
+    <t>DensityFit;AtomNumber;CenterFit</t>
+  </si>
+  <si>
+    <t>LSR</t>
+  </si>
+  <si>
+    <t>[822 1197;891 1124;967 1135;1062 1182;1073 1305;1048 1369;985 1397;905 1407;829 1336]</t>
+  </si>
+  <si>
+    <t>NI</t>
+  </si>
+  <si>
+    <t>Absorption</t>
+  </si>
+  <si>
+    <t>StrongLight</t>
+  </si>
+  <si>
+    <t>BosonicGaussianFit1D</t>
+  </si>
+  <si>
+    <t>None</t>
+  </si>
+  <si>
+    <t>ParabolicFit1D</t>
+  </si>
+  <si>
+    <t>StdErr</t>
+  </si>
+  <si>
+    <t>WaveformGeneratorName,XvWingMod;ChannelName,Ch1;WaveformListName,XvWingNi</t>
+  </si>
+  <si>
+    <t>PhaseLockName,ImagingLock;Frequency,700000000;VariableName,hw_ImagingNi</t>
+  </si>
+  <si>
+    <t>NiLatticeSdCalibFreqStart</t>
+  </si>
+  <si>
+    <t>An experiment at the non-interacting lattice stage. Scan hw_SdCalibFreqStart.</t>
+  </si>
+  <si>
+    <t>TOP</t>
+  </si>
+  <si>
+    <t>NiLatticeDepthCalibTof6000</t>
+  </si>
+  <si>
+    <t>None</t>
+  </si>
+  <si>
+    <t>hw_SdCalibFreqStart</t>
+  </si>
+  <si>
+    <t>DensityFit;AtomNumber</t>
+  </si>
+  <si>
+    <t>LSR</t>
+  </si>
+  <si>
+    <t>HF</t>
+  </si>
+  <si>
+    <t>Absorption</t>
+  </si>
+  <si>
+    <t>StrongLight</t>
+  </si>
+  <si>
+    <t>BosonicGaussianFit1D</t>
+  </si>
+  <si>
+    <t>None</t>
+  </si>
+  <si>
+    <t>ParabolicFit1D</t>
+  </si>
+  <si>
+    <t>StdErr</t>
+  </si>
+  <si>
+    <t>WaveformGeneratorName,LatticeMod,XvWingMod;ChannelName,Ch2,Ch1;WaveformListName,SdDepthCalib,XvWingNi</t>
+  </si>
+  <si>
+    <t>PhaseLockName,ImagingLock;Frequency,700000000;VariableName,hw_ImagingNi</t>
+  </si>
+  <si>
+    <t>NiLatticeSdCalibFreqStart</t>
+  </si>
+  <si>
+    <t>An experiment at the non-interacting lattice stage. Scan hw_SdCalibFreqStart.</t>
+  </si>
+  <si>
+    <t>TOP</t>
+  </si>
+  <si>
+    <t>NiLatticeDepthCalibTof8000</t>
+  </si>
+  <si>
+    <t>None</t>
+  </si>
+  <si>
+    <t>hw_SdCalibFreqStart</t>
+  </si>
+  <si>
+    <t>DensityFit;AtomNumber</t>
+  </si>
+  <si>
+    <t>LSR</t>
+  </si>
+  <si>
+    <t>HF</t>
+  </si>
+  <si>
+    <t>Absorption</t>
+  </si>
+  <si>
+    <t>StrongLight</t>
+  </si>
+  <si>
+    <t>BosonicGaussianFit1D</t>
+  </si>
+  <si>
+    <t>None</t>
+  </si>
+  <si>
+    <t>ParabolicFit1D</t>
+  </si>
+  <si>
+    <t>StdErr</t>
+  </si>
+  <si>
+    <t>WaveformGeneratorName,LatticeMod,XvWingMod;ChannelName,Ch2,Ch1;WaveformListName,SdDepthCalib,XvWingNi</t>
+  </si>
+  <si>
+    <t>PhaseLockName,ImagingLock;Frequency,700000000;VariableName,hw_ImagingNi</t>
+  </si>
+  <si>
+    <t>NiBecTof</t>
+  </si>
+  <si>
+    <t>A TOF experiment at the non-interacting BEC stage.</t>
+  </si>
+  <si>
+    <t>TOP</t>
+  </si>
+  <si>
+    <t>Bec</t>
+  </si>
+  <si>
+    <t>TOF</t>
+  </si>
+  <si>
+    <t>DensityFit;AtomNumber;Tof;CenterFit</t>
+  </si>
+  <si>
+    <t>LSR</t>
+  </si>
+  <si>
+    <t>[835 1202;930 1127;1041 1147;1072 1219;1080 1324;1023 1388;924 1403;856 1386;824 1327]</t>
+  </si>
+  <si>
+    <t>HF</t>
+  </si>
+  <si>
+    <t>Absorption</t>
+  </si>
+  <si>
+    <t>StrongLight</t>
+  </si>
+  <si>
+    <t>BosonicGaussianFit1D</t>
+  </si>
+  <si>
+    <t>None</t>
+  </si>
+  <si>
+    <t>ParabolicFit1D</t>
+  </si>
+  <si>
+    <t>StdErr</t>
+  </si>
+  <si>
+    <t>WaveformGeneratorName,XvWingMod;ChannelName,Ch1;WaveformListName,XvWingNi</t>
+  </si>
+  <si>
+    <t>PhaseLockName,ImagingLock;Frequency,700000000;VariableName,hw_ImagingNi</t>
+  </si>
+  <si>
+    <t>HfBecRfknifeend</t>
+  </si>
+  <si>
+    <t>An experiment at the high-field BEC stage.</t>
+  </si>
+  <si>
+    <t>TOP</t>
+  </si>
+  <si>
+    <t>Bec</t>
+  </si>
+  <si>
+    <t>rfknifeend</t>
+  </si>
+  <si>
+    <t>DensityFit;AtomNumber</t>
+  </si>
+  <si>
+    <t>LSR</t>
+  </si>
+  <si>
+    <t>[883 1377;966 1445;1038 1463;1096 1410;1124 1337;1126 1262;1065 1216;1013 1203;958 1212;897 1248;871 1292]</t>
+  </si>
+  <si>
+    <t>HF</t>
+  </si>
+  <si>
+    <t>Absorption</t>
+  </si>
+  <si>
+    <t>StrongLight</t>
+  </si>
+  <si>
+    <t>BosonicGaussianFit1D</t>
+  </si>
+  <si>
+    <t>None</t>
+  </si>
+  <si>
+    <t>LinearFit1D</t>
+  </si>
+  <si>
+    <t>StdErr</t>
+  </si>
+  <si>
+    <t>WaveformGeneratorName,XvWingMod;ChannelName,Ch1;WaveformListName,XvWingHf</t>
+  </si>
+  <si>
+    <t>PhaseLockName,ImagingLock;Frequency,700000000;VariableName,hw_ImagingHf</t>
+  </si>
+  <si>
+    <t>HfBecRfknifeend</t>
+  </si>
+  <si>
+    <t>An experiment at the high-field BEC stage.</t>
+  </si>
+  <si>
+    <t>TOP</t>
+  </si>
+  <si>
+    <t>Bec</t>
+  </si>
+  <si>
+    <t>rfknifeend</t>
+  </si>
+  <si>
+    <t>DensityFit;AtomNumber</t>
+  </si>
+  <si>
+    <t>LSR</t>
+  </si>
+  <si>
+    <t>[819 1184;867 1111;984 1113;1071 1141;1082 1294;1069 1383;975 1409;824 1384]</t>
+  </si>
+  <si>
+    <t>HF</t>
+  </si>
+  <si>
+    <t>Absorption</t>
+  </si>
+  <si>
+    <t>StrongLight</t>
+  </si>
+  <si>
+    <t>BosonicGaussianFit1D</t>
+  </si>
+  <si>
+    <t>None</t>
+  </si>
+  <si>
+    <t>LinearFit1D</t>
+  </si>
+  <si>
+    <t>StdErr</t>
+  </si>
+  <si>
+    <t>WaveformGeneratorName,XvWingMod;ChannelName,Ch1;WaveformListName,XvWingHf</t>
+  </si>
+  <si>
+    <t>PhaseLockName,ImagingLock;Frequency,700000000;VariableName,hw_ImagingHf</t>
   </si>
 </sst>
 </file>
@@ -3950,7 +5363,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:V86"/>
+  <dimension ref="A1:V89"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="36.42578125" customWidth="true"/>
@@ -3973,8 +5386,8 @@
     <col min="18" max="18" width="16.42578125" customWidth="true"/>
     <col min="19" max="19" width="17" customWidth="true"/>
     <col min="20" max="20" width="16.85546875" customWidth="true"/>
-    <col min="21" max="21" width="84.28515625" customWidth="true"/>
-    <col min="22" max="22" width="73" customWidth="true"/>
+    <col min="21" max="21" width="107.28515625" customWidth="true"/>
+    <col min="22" max="22" width="73.5703125" customWidth="true"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -4152,65 +5565,67 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" t="s">
-        <v>1136</v>
-      </c>
-      <c r="B4" t="s">
-        <v>1137</v>
-      </c>
-      <c r="C4" t="s">
-        <v>1138</v>
-      </c>
-      <c r="D4" t="s">
-        <v>1139</v>
-      </c>
-      <c r="E4" t="s">
-        <v>1140</v>
-      </c>
-      <c r="F4">
+      <c r="A4" s="0" t="s">
+        <v>1549</v>
+      </c>
+      <c r="B4" s="0" t="s">
+        <v>1550</v>
+      </c>
+      <c r="C4" s="0" t="s">
+        <v>1551</v>
+      </c>
+      <c r="D4" s="0" t="s">
+        <v>1552</v>
+      </c>
+      <c r="E4" s="0" t="s">
+        <v>1553</v>
+      </c>
+      <c r="F4" s="0">
         <v>4</v>
       </c>
-      <c r="G4" t="s">
-        <v>1141</v>
-      </c>
-      <c r="H4" t="s">
-        <v>1142</v>
-      </c>
-      <c r="I4" t="s">
-        <v>1143</v>
-      </c>
-      <c r="J4" t="s">
-        <v>1144</v>
-      </c>
-      <c r="K4" t="s">
-        <v>1145</v>
-      </c>
-      <c r="L4" t="s">
-        <v>1146</v>
-      </c>
-      <c r="M4" t="s">
-        <v>1147</v>
-      </c>
-      <c r="N4">
+      <c r="G4" s="0" t="s">
+        <v>1554</v>
+      </c>
+      <c r="H4" s="0" t="s">
+        <v>1555</v>
+      </c>
+      <c r="I4" s="0" t="s">
+        <v>1556</v>
+      </c>
+      <c r="J4" s="0" t="s">
+        <v>1557</v>
+      </c>
+      <c r="K4" s="0" t="s">
+        <v>1558</v>
+      </c>
+      <c r="L4" s="0" t="s">
+        <v>1559</v>
+      </c>
+      <c r="M4" s="0" t="s">
+        <v>1560</v>
+      </c>
+      <c r="N4" s="0">
         <v>8</v>
       </c>
-      <c r="O4" t="s">
-        <v>1148</v>
-      </c>
-      <c r="P4">
-        <v>40</v>
-      </c>
-      <c r="Q4" t="s">
-        <v>19</v>
-      </c>
-      <c r="R4" t="s">
-        <v>1149</v>
-      </c>
-      <c r="S4" t="s">
-        <v>1150</v>
-      </c>
-      <c r="V4" t="s">
-        <v>1151</v>
+      <c r="O4" s="0" t="s">
+        <v>1561</v>
+      </c>
+      <c r="P4" s="0">
+        <v>60</v>
+      </c>
+      <c r="Q4" s="0" t="s">
+        <v>1562</v>
+      </c>
+      <c r="R4" s="0" t="s">
+        <v>1563</v>
+      </c>
+      <c r="S4" s="0" t="s">
+        <v>1564</v>
+      </c>
+      <c r="T4" s="0"/>
+      <c r="U4" s="0"/>
+      <c r="V4" s="0" t="s">
+        <v>1565</v>
       </c>
     </row>
     <row r="5">
@@ -5705,68 +7120,69 @@
       </c>
     </row>
     <row r="30">
-      <c r="A30" t="s">
-        <v>1104</v>
-      </c>
-      <c r="B30" t="s">
-        <v>1105</v>
-      </c>
-      <c r="C30" t="s">
-        <v>1106</v>
-      </c>
-      <c r="D30" t="s">
-        <v>1107</v>
-      </c>
-      <c r="E30" t="s">
-        <v>1108</v>
-      </c>
-      <c r="F30">
+      <c r="A30" s="0" t="s">
+        <v>1566</v>
+      </c>
+      <c r="B30" s="0" t="s">
+        <v>1567</v>
+      </c>
+      <c r="C30" s="0" t="s">
+        <v>1568</v>
+      </c>
+      <c r="D30" s="0" t="s">
+        <v>1569</v>
+      </c>
+      <c r="E30" s="0" t="s">
+        <v>1570</v>
+      </c>
+      <c r="F30" s="0">
         <v>4</v>
       </c>
-      <c r="G30" t="s">
-        <v>1109</v>
-      </c>
-      <c r="H30" t="s">
-        <v>1110</v>
-      </c>
-      <c r="I30" t="s">
-        <v>1111</v>
-      </c>
-      <c r="J30" t="s">
-        <v>1112</v>
-      </c>
-      <c r="K30" t="s">
-        <v>1113</v>
-      </c>
-      <c r="L30" t="s">
-        <v>1114</v>
-      </c>
-      <c r="M30" t="s">
-        <v>1115</v>
-      </c>
-      <c r="N30">
+      <c r="G30" s="0" t="s">
+        <v>1571</v>
+      </c>
+      <c r="H30" s="0" t="s">
+        <v>1572</v>
+      </c>
+      <c r="I30" s="0" t="s">
+        <v>1573</v>
+      </c>
+      <c r="J30" s="0" t="s">
+        <v>1574</v>
+      </c>
+      <c r="K30" s="0" t="s">
+        <v>1575</v>
+      </c>
+      <c r="L30" s="0" t="s">
+        <v>1576</v>
+      </c>
+      <c r="M30" s="0" t="s">
+        <v>1577</v>
+      </c>
+      <c r="N30" s="0">
         <v>8</v>
       </c>
-      <c r="O30" t="s">
-        <v>1116</v>
-      </c>
-      <c r="P30">
-        <v>0.2</v>
-      </c>
-      <c r="Q30" t="s">
-        <v>19</v>
-      </c>
-      <c r="R30" t="s">
-        <v>1117</v>
-      </c>
-      <c r="S30" t="s">
-        <v>1118</v>
-      </c>
-      <c r="U30" t="s">
-        <v>1119</v>
-      </c>
-      <c r="V30" t="s">
-        <v>1120</v>
+      <c r="O30" s="0" t="s">
+        <v>1578</v>
+      </c>
+      <c r="P30" s="0">
+        <v>0.20000000000000001</v>
+      </c>
+      <c r="Q30" s="0" t="s">
+        <v>1579</v>
+      </c>
+      <c r="R30" s="0" t="s">
+        <v>1580</v>
+      </c>
+      <c r="S30" s="0" t="s">
+        <v>1581</v>
+      </c>
+      <c r="T30" s="0"/>
+      <c r="U30" s="0" t="s">
+        <v>1582</v>
+      </c>
+      <c r="V30" s="0" t="s">
+        <v>1583</v>
       </c>
     </row>
     <row r="31">
@@ -6021,68 +7437,69 @@
       </c>
     </row>
     <row r="35">
-      <c r="A35" t="s">
-        <v>770</v>
-      </c>
-      <c r="B35" t="s">
-        <v>771</v>
-      </c>
-      <c r="C35" t="s">
-        <v>772</v>
-      </c>
-      <c r="D35" t="s">
-        <v>773</v>
-      </c>
-      <c r="E35" t="s">
-        <v>774</v>
-      </c>
-      <c r="F35">
+      <c r="A35" s="0" t="s">
+        <v>1198</v>
+      </c>
+      <c r="B35" s="0" t="s">
+        <v>1199</v>
+      </c>
+      <c r="C35" s="0" t="s">
+        <v>1200</v>
+      </c>
+      <c r="D35" s="0" t="s">
+        <v>1201</v>
+      </c>
+      <c r="E35" s="0" t="s">
+        <v>1202</v>
+      </c>
+      <c r="F35" s="0">
         <v>4</v>
       </c>
-      <c r="G35" t="s">
-        <v>775</v>
-      </c>
-      <c r="H35" t="s">
-        <v>776</v>
-      </c>
-      <c r="I35" t="s">
-        <v>777</v>
-      </c>
-      <c r="J35" t="s">
-        <v>778</v>
-      </c>
-      <c r="K35" t="s">
-        <v>779</v>
-      </c>
-      <c r="L35" t="s">
-        <v>780</v>
-      </c>
-      <c r="M35" t="s">
-        <v>781</v>
-      </c>
-      <c r="N35">
+      <c r="G35" s="0" t="s">
+        <v>1203</v>
+      </c>
+      <c r="H35" s="0" t="s">
+        <v>1204</v>
+      </c>
+      <c r="I35" s="0" t="s">
+        <v>1205</v>
+      </c>
+      <c r="J35" s="0" t="s">
+        <v>1206</v>
+      </c>
+      <c r="K35" s="0" t="s">
+        <v>1207</v>
+      </c>
+      <c r="L35" s="0" t="s">
+        <v>1208</v>
+      </c>
+      <c r="M35" s="0" t="s">
+        <v>1209</v>
+      </c>
+      <c r="N35" s="0">
         <v>8</v>
       </c>
-      <c r="O35" t="s">
-        <v>782</v>
-      </c>
-      <c r="P35">
+      <c r="O35" s="0" t="s">
+        <v>1210</v>
+      </c>
+      <c r="P35" s="0">
         <v>0.5</v>
       </c>
-      <c r="Q35" t="s">
-        <v>19</v>
-      </c>
-      <c r="R35" t="s">
-        <v>783</v>
-      </c>
-      <c r="S35" t="s">
-        <v>784</v>
-      </c>
-      <c r="U35" t="s">
-        <v>979</v>
-      </c>
-      <c r="V35" t="s">
-        <v>1120</v>
+      <c r="Q35" s="0" t="s">
+        <v>1211</v>
+      </c>
+      <c r="R35" s="0" t="s">
+        <v>1212</v>
+      </c>
+      <c r="S35" s="0" t="s">
+        <v>1213</v>
+      </c>
+      <c r="T35" s="0"/>
+      <c r="U35" s="0" t="s">
+        <v>1214</v>
+      </c>
+      <c r="V35" s="0" t="s">
+        <v>1215</v>
       </c>
     </row>
     <row r="36">
@@ -6399,65 +7816,67 @@
       </c>
     </row>
     <row r="41">
-      <c r="A41" t="s">
-        <v>625</v>
-      </c>
-      <c r="B41" t="s">
-        <v>626</v>
-      </c>
-      <c r="C41" t="s">
-        <v>627</v>
-      </c>
-      <c r="D41" t="s">
-        <v>628</v>
-      </c>
-      <c r="F41">
+      <c r="A41" s="0" t="s">
+        <v>1618</v>
+      </c>
+      <c r="B41" s="0" t="s">
+        <v>1619</v>
+      </c>
+      <c r="C41" s="0" t="s">
+        <v>1620</v>
+      </c>
+      <c r="D41" s="0" t="s">
+        <v>1621</v>
+      </c>
+      <c r="E41" s="0"/>
+      <c r="F41" s="0">
         <v>4</v>
       </c>
-      <c r="G41" t="s">
-        <v>629</v>
-      </c>
-      <c r="H41" t="s">
-        <v>630</v>
-      </c>
-      <c r="I41" t="s">
-        <v>631</v>
-      </c>
-      <c r="J41" t="s">
-        <v>632</v>
-      </c>
-      <c r="K41" t="s">
-        <v>633</v>
-      </c>
-      <c r="L41" t="s">
-        <v>634</v>
-      </c>
-      <c r="M41" t="s">
-        <v>635</v>
-      </c>
-      <c r="N41">
+      <c r="G41" s="0" t="s">
+        <v>1622</v>
+      </c>
+      <c r="H41" s="0" t="s">
+        <v>1623</v>
+      </c>
+      <c r="I41" s="0" t="s">
+        <v>1624</v>
+      </c>
+      <c r="J41" s="0" t="s">
+        <v>1625</v>
+      </c>
+      <c r="K41" s="0" t="s">
+        <v>1626</v>
+      </c>
+      <c r="L41" s="0" t="s">
+        <v>1627</v>
+      </c>
+      <c r="M41" s="0" t="s">
+        <v>1628</v>
+      </c>
+      <c r="N41" s="0">
         <v>8</v>
       </c>
-      <c r="O41" t="s">
-        <v>636</v>
-      </c>
-      <c r="P41">
+      <c r="O41" s="0" t="s">
+        <v>1629</v>
+      </c>
+      <c r="P41" s="0">
         <v>1</v>
       </c>
-      <c r="Q41" t="s">
-        <v>19</v>
-      </c>
-      <c r="R41" t="s">
-        <v>637</v>
-      </c>
-      <c r="S41" t="s">
-        <v>638</v>
-      </c>
-      <c r="U41" t="s">
-        <v>979</v>
-      </c>
-      <c r="V41" t="s">
-        <v>1120</v>
+      <c r="Q41" s="0" t="s">
+        <v>1630</v>
+      </c>
+      <c r="R41" s="0" t="s">
+        <v>1631</v>
+      </c>
+      <c r="S41" s="0" t="s">
+        <v>1632</v>
+      </c>
+      <c r="T41" s="0"/>
+      <c r="U41" s="0" t="s">
+        <v>1633</v>
+      </c>
+      <c r="V41" s="0" t="s">
+        <v>1634</v>
       </c>
     </row>
     <row r="42">
@@ -7193,65 +8612,69 @@
       </c>
     </row>
     <row r="54">
-      <c r="A54" t="s">
-        <v>815</v>
-      </c>
-      <c r="B54" t="s">
-        <v>816</v>
-      </c>
-      <c r="C54" t="s">
-        <v>817</v>
-      </c>
-      <c r="D54" t="s">
-        <v>818</v>
-      </c>
-      <c r="E54" t="s">
-        <v>819</v>
-      </c>
-      <c r="F54">
+      <c r="A54" s="0" t="s">
+        <v>1442</v>
+      </c>
+      <c r="B54" s="0" t="s">
+        <v>1443</v>
+      </c>
+      <c r="C54" s="0" t="s">
+        <v>1444</v>
+      </c>
+      <c r="D54" s="0" t="s">
+        <v>1445</v>
+      </c>
+      <c r="E54" s="0" t="s">
+        <v>1446</v>
+      </c>
+      <c r="F54" s="0">
         <v>4</v>
       </c>
-      <c r="G54" t="s">
-        <v>820</v>
-      </c>
-      <c r="H54" t="s">
-        <v>821</v>
-      </c>
-      <c r="I54" t="s">
-        <v>822</v>
-      </c>
-      <c r="J54" t="s">
-        <v>823</v>
-      </c>
-      <c r="K54" t="s">
-        <v>824</v>
-      </c>
-      <c r="L54" t="s">
-        <v>825</v>
-      </c>
-      <c r="M54" t="s">
-        <v>826</v>
-      </c>
-      <c r="N54">
+      <c r="G54" s="0" t="s">
+        <v>1447</v>
+      </c>
+      <c r="H54" s="0" t="s">
+        <v>1448</v>
+      </c>
+      <c r="I54" s="0" t="s">
+        <v>1449</v>
+      </c>
+      <c r="J54" s="0" t="s">
+        <v>1450</v>
+      </c>
+      <c r="K54" s="0" t="s">
+        <v>1451</v>
+      </c>
+      <c r="L54" s="0" t="s">
+        <v>1452</v>
+      </c>
+      <c r="M54" s="0" t="s">
+        <v>1453</v>
+      </c>
+      <c r="N54" s="0">
         <v>2</v>
       </c>
-      <c r="O54" t="s">
-        <v>827</v>
-      </c>
-      <c r="P54">
-        <v>0.2</v>
-      </c>
-      <c r="Q54" t="s">
-        <v>19</v>
-      </c>
-      <c r="R54" t="s">
-        <v>828</v>
-      </c>
-      <c r="S54" t="s">
-        <v>829</v>
-      </c>
-      <c r="V54" t="s">
-        <v>1120</v>
+      <c r="O54" s="0" t="s">
+        <v>1454</v>
+      </c>
+      <c r="P54" s="0">
+        <v>0.20000000000000001</v>
+      </c>
+      <c r="Q54" s="0" t="s">
+        <v>1455</v>
+      </c>
+      <c r="R54" s="0" t="s">
+        <v>1456</v>
+      </c>
+      <c r="S54" s="0" t="s">
+        <v>1457</v>
+      </c>
+      <c r="T54" s="0"/>
+      <c r="U54" s="0" t="s">
+        <v>1458</v>
+      </c>
+      <c r="V54" s="0" t="s">
+        <v>1459</v>
       </c>
     </row>
     <row r="55">
@@ -7317,65 +8740,67 @@
       </c>
     </row>
     <row r="56">
-      <c r="A56" t="s">
-        <v>860</v>
-      </c>
-      <c r="B56" t="s">
-        <v>861</v>
-      </c>
-      <c r="C56" t="s">
-        <v>862</v>
-      </c>
-      <c r="D56" t="s">
-        <v>863</v>
-      </c>
-      <c r="E56" t="s">
-        <v>864</v>
-      </c>
-      <c r="F56">
+      <c r="A56" s="0" t="s">
+        <v>1335</v>
+      </c>
+      <c r="B56" s="0" t="s">
+        <v>1336</v>
+      </c>
+      <c r="C56" s="0" t="s">
+        <v>1337</v>
+      </c>
+      <c r="D56" s="0" t="s">
+        <v>1338</v>
+      </c>
+      <c r="E56" s="0" t="s">
+        <v>1339</v>
+      </c>
+      <c r="F56" s="0">
         <v>4</v>
       </c>
-      <c r="G56" t="s">
-        <v>865</v>
-      </c>
-      <c r="H56" t="s">
-        <v>866</v>
-      </c>
-      <c r="I56" t="s">
-        <v>867</v>
-      </c>
-      <c r="J56" t="s">
-        <v>868</v>
-      </c>
-      <c r="K56" t="s">
-        <v>869</v>
-      </c>
-      <c r="L56" t="s">
-        <v>870</v>
-      </c>
-      <c r="M56" t="s">
-        <v>871</v>
-      </c>
-      <c r="N56">
+      <c r="G56" s="0" t="s">
+        <v>1340</v>
+      </c>
+      <c r="H56" s="0" t="s">
+        <v>1341</v>
+      </c>
+      <c r="I56" s="0" t="s">
+        <v>1342</v>
+      </c>
+      <c r="J56" s="0" t="s">
+        <v>1343</v>
+      </c>
+      <c r="K56" s="0" t="s">
+        <v>1344</v>
+      </c>
+      <c r="L56" s="0" t="s">
+        <v>1345</v>
+      </c>
+      <c r="M56" s="0" t="s">
+        <v>1346</v>
+      </c>
+      <c r="N56" s="0">
         <v>8</v>
       </c>
-      <c r="O56" t="s">
-        <v>872</v>
-      </c>
-      <c r="P56">
+      <c r="O56" s="0" t="s">
+        <v>1347</v>
+      </c>
+      <c r="P56" s="0">
         <v>1</v>
       </c>
-      <c r="Q56" t="s">
-        <v>19</v>
-      </c>
-      <c r="R56" t="s">
-        <v>873</v>
-      </c>
-      <c r="S56" t="s">
-        <v>874</v>
-      </c>
-      <c r="V56" t="s">
-        <v>1120</v>
+      <c r="Q56" s="0" t="s">
+        <v>1348</v>
+      </c>
+      <c r="R56" s="0" t="s">
+        <v>1349</v>
+      </c>
+      <c r="S56" s="0" t="s">
+        <v>1350</v>
+      </c>
+      <c r="T56" s="0"/>
+      <c r="U56" s="0"/>
+      <c r="V56" s="0" t="s">
+        <v>1351</v>
       </c>
     </row>
     <row r="57">
@@ -7438,62 +8863,67 @@
       </c>
     </row>
     <row r="58">
-      <c r="A58" t="s">
-        <v>461</v>
-      </c>
-      <c r="B58" t="s">
-        <v>462</v>
-      </c>
-      <c r="C58" t="s">
-        <v>463</v>
-      </c>
-      <c r="D58" t="s">
-        <v>464</v>
-      </c>
-      <c r="E58" t="s">
-        <v>465</v>
-      </c>
-      <c r="F58">
+      <c r="A58" s="0" t="s">
+        <v>1601</v>
+      </c>
+      <c r="B58" s="0" t="s">
+        <v>1602</v>
+      </c>
+      <c r="C58" s="0" t="s">
+        <v>1603</v>
+      </c>
+      <c r="D58" s="0" t="s">
+        <v>1604</v>
+      </c>
+      <c r="E58" s="0" t="s">
+        <v>1605</v>
+      </c>
+      <c r="F58" s="0">
         <v>4</v>
       </c>
-      <c r="G58" t="s">
-        <v>466</v>
-      </c>
-      <c r="H58" t="s">
-        <v>467</v>
-      </c>
-      <c r="I58" t="s">
-        <v>468</v>
-      </c>
-      <c r="K58" t="s">
-        <v>469</v>
-      </c>
-      <c r="L58" t="s">
-        <v>580</v>
-      </c>
-      <c r="M58" t="s">
-        <v>470</v>
-      </c>
-      <c r="N58">
+      <c r="G58" s="0" t="s">
+        <v>1606</v>
+      </c>
+      <c r="H58" s="0" t="s">
+        <v>1607</v>
+      </c>
+      <c r="I58" s="0" t="s">
+        <v>1608</v>
+      </c>
+      <c r="J58" s="0"/>
+      <c r="K58" s="0" t="s">
+        <v>1609</v>
+      </c>
+      <c r="L58" s="0" t="s">
+        <v>1610</v>
+      </c>
+      <c r="M58" s="0" t="s">
+        <v>1611</v>
+      </c>
+      <c r="N58" s="0">
         <v>2</v>
       </c>
-      <c r="O58" t="s">
-        <v>471</v>
-      </c>
-      <c r="P58">
-        <v>0.2</v>
-      </c>
-      <c r="Q58" t="s">
-        <v>19</v>
-      </c>
-      <c r="R58" t="s">
-        <v>472</v>
-      </c>
-      <c r="S58" t="s">
-        <v>473</v>
-      </c>
-      <c r="V58" t="s">
-        <v>1120</v>
+      <c r="O58" s="0" t="s">
+        <v>1612</v>
+      </c>
+      <c r="P58" s="0">
+        <v>0.20000000000000001</v>
+      </c>
+      <c r="Q58" s="0" t="s">
+        <v>1613</v>
+      </c>
+      <c r="R58" s="0" t="s">
+        <v>1614</v>
+      </c>
+      <c r="S58" s="0" t="s">
+        <v>1615</v>
+      </c>
+      <c r="T58" s="0"/>
+      <c r="U58" s="0" t="s">
+        <v>1616</v>
+      </c>
+      <c r="V58" s="0" t="s">
+        <v>1617</v>
       </c>
     </row>
     <row r="59">
@@ -7925,65 +9355,69 @@
       </c>
     </row>
     <row r="66">
-      <c r="A66" t="s">
-        <v>726</v>
-      </c>
-      <c r="B66" t="s">
-        <v>727</v>
-      </c>
-      <c r="C66" t="s">
-        <v>728</v>
-      </c>
-      <c r="D66" t="s">
-        <v>729</v>
-      </c>
-      <c r="E66" t="s">
-        <v>730</v>
-      </c>
-      <c r="F66">
+      <c r="A66" s="0" t="s">
+        <v>1370</v>
+      </c>
+      <c r="B66" s="0" t="s">
+        <v>1371</v>
+      </c>
+      <c r="C66" s="0" t="s">
+        <v>1372</v>
+      </c>
+      <c r="D66" s="0" t="s">
+        <v>1373</v>
+      </c>
+      <c r="E66" s="0" t="s">
+        <v>1374</v>
+      </c>
+      <c r="F66" s="0">
         <v>4</v>
       </c>
-      <c r="G66" t="s">
-        <v>731</v>
-      </c>
-      <c r="H66" t="s">
-        <v>732</v>
-      </c>
-      <c r="I66" t="s">
-        <v>733</v>
-      </c>
-      <c r="J66" t="s">
-        <v>734</v>
-      </c>
-      <c r="K66" t="s">
-        <v>735</v>
-      </c>
-      <c r="L66" t="s">
-        <v>736</v>
-      </c>
-      <c r="M66" t="s">
-        <v>737</v>
-      </c>
-      <c r="N66">
+      <c r="G66" s="0" t="s">
+        <v>1375</v>
+      </c>
+      <c r="H66" s="0" t="s">
+        <v>1376</v>
+      </c>
+      <c r="I66" s="0" t="s">
+        <v>1377</v>
+      </c>
+      <c r="J66" s="0" t="s">
+        <v>1378</v>
+      </c>
+      <c r="K66" s="0" t="s">
+        <v>1379</v>
+      </c>
+      <c r="L66" s="0" t="s">
+        <v>1380</v>
+      </c>
+      <c r="M66" s="0" t="s">
+        <v>1381</v>
+      </c>
+      <c r="N66" s="0">
         <v>4</v>
       </c>
-      <c r="O66" t="s">
-        <v>738</v>
-      </c>
-      <c r="P66">
+      <c r="O66" s="0" t="s">
+        <v>1382</v>
+      </c>
+      <c r="P66" s="0">
         <v>1</v>
       </c>
-      <c r="Q66" t="s">
-        <v>19</v>
-      </c>
-      <c r="R66" t="s">
-        <v>739</v>
-      </c>
-      <c r="S66" t="s">
-        <v>740</v>
-      </c>
-      <c r="V66" t="s">
-        <v>1120</v>
+      <c r="Q66" s="0" t="s">
+        <v>1383</v>
+      </c>
+      <c r="R66" s="0" t="s">
+        <v>1384</v>
+      </c>
+      <c r="S66" s="0" t="s">
+        <v>1385</v>
+      </c>
+      <c r="T66" s="0"/>
+      <c r="U66" s="0" t="s">
+        <v>1386</v>
+      </c>
+      <c r="V66" s="0" t="s">
+        <v>1387</v>
       </c>
     </row>
     <row r="67">
@@ -9176,6 +10610,200 @@
       </c>
       <c r="V86" t="s">
         <v>1120</v>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" s="0" t="s">
+        <v>1531</v>
+      </c>
+      <c r="B87" s="0" t="s">
+        <v>1532</v>
+      </c>
+      <c r="C87" s="0" t="s">
+        <v>1533</v>
+      </c>
+      <c r="D87" s="0" t="s">
+        <v>1534</v>
+      </c>
+      <c r="E87" s="0" t="s">
+        <v>1535</v>
+      </c>
+      <c r="F87" s="0">
+        <v>4</v>
+      </c>
+      <c r="G87" s="0" t="s">
+        <v>1536</v>
+      </c>
+      <c r="H87" s="0" t="s">
+        <v>1537</v>
+      </c>
+      <c r="I87" s="0" t="s">
+        <v>1538</v>
+      </c>
+      <c r="J87" s="0" t="s">
+        <v>1539</v>
+      </c>
+      <c r="K87" s="0" t="s">
+        <v>1540</v>
+      </c>
+      <c r="L87" s="0" t="s">
+        <v>1541</v>
+      </c>
+      <c r="M87" s="0" t="s">
+        <v>1542</v>
+      </c>
+      <c r="N87" s="0">
+        <v>8</v>
+      </c>
+      <c r="O87" s="0" t="s">
+        <v>1543</v>
+      </c>
+      <c r="P87" s="0">
+        <v>0.20000000000000001</v>
+      </c>
+      <c r="Q87" s="0" t="s">
+        <v>1544</v>
+      </c>
+      <c r="R87" s="0" t="s">
+        <v>1545</v>
+      </c>
+      <c r="S87" s="0" t="s">
+        <v>1546</v>
+      </c>
+      <c r="T87" s="0"/>
+      <c r="U87" s="0" t="s">
+        <v>1547</v>
+      </c>
+      <c r="V87" s="0" t="s">
+        <v>1548</v>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" s="0" t="s">
+        <v>1478</v>
+      </c>
+      <c r="B88" s="0" t="s">
+        <v>1479</v>
+      </c>
+      <c r="C88" s="0" t="s">
+        <v>1480</v>
+      </c>
+      <c r="D88" s="0" t="s">
+        <v>1481</v>
+      </c>
+      <c r="E88" s="0"/>
+      <c r="F88" s="0">
+        <v>4</v>
+      </c>
+      <c r="G88" s="0" t="s">
+        <v>1482</v>
+      </c>
+      <c r="H88" s="0" t="s">
+        <v>1483</v>
+      </c>
+      <c r="I88" s="0" t="s">
+        <v>1484</v>
+      </c>
+      <c r="J88" s="0" t="s">
+        <v>1485</v>
+      </c>
+      <c r="K88" s="0" t="s">
+        <v>1486</v>
+      </c>
+      <c r="L88" s="0" t="s">
+        <v>1487</v>
+      </c>
+      <c r="M88" s="0" t="s">
+        <v>1488</v>
+      </c>
+      <c r="N88" s="0">
+        <v>8</v>
+      </c>
+      <c r="O88" s="0" t="s">
+        <v>1489</v>
+      </c>
+      <c r="P88" s="0">
+        <v>2</v>
+      </c>
+      <c r="Q88" s="0" t="s">
+        <v>1490</v>
+      </c>
+      <c r="R88" s="0" t="s">
+        <v>1491</v>
+      </c>
+      <c r="S88" s="0" t="s">
+        <v>1492</v>
+      </c>
+      <c r="T88" s="0"/>
+      <c r="U88" s="0" t="s">
+        <v>1493</v>
+      </c>
+      <c r="V88" s="0" t="s">
+        <v>1494</v>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" s="0" t="s">
+        <v>1652</v>
+      </c>
+      <c r="B89" s="0" t="s">
+        <v>1653</v>
+      </c>
+      <c r="C89" s="0" t="s">
+        <v>1654</v>
+      </c>
+      <c r="D89" s="0" t="s">
+        <v>1655</v>
+      </c>
+      <c r="E89" s="0"/>
+      <c r="F89" s="0">
+        <v>4</v>
+      </c>
+      <c r="G89" s="0" t="s">
+        <v>1656</v>
+      </c>
+      <c r="H89" s="0" t="s">
+        <v>1657</v>
+      </c>
+      <c r="I89" s="0" t="s">
+        <v>1658</v>
+      </c>
+      <c r="J89" s="0" t="s">
+        <v>1659</v>
+      </c>
+      <c r="K89" s="0" t="s">
+        <v>1660</v>
+      </c>
+      <c r="L89" s="0" t="s">
+        <v>1661</v>
+      </c>
+      <c r="M89" s="0" t="s">
+        <v>1662</v>
+      </c>
+      <c r="N89" s="0">
+        <v>8</v>
+      </c>
+      <c r="O89" s="0" t="s">
+        <v>1663</v>
+      </c>
+      <c r="P89" s="0">
+        <v>2</v>
+      </c>
+      <c r="Q89" s="0" t="s">
+        <v>1664</v>
+      </c>
+      <c r="R89" s="0" t="s">
+        <v>1665</v>
+      </c>
+      <c r="S89" s="0" t="s">
+        <v>1666</v>
+      </c>
+      <c r="T89" s="0"/>
+      <c r="U89" s="0" t="s">
+        <v>1667</v>
+      </c>
+      <c r="V89" s="0" t="s">
+        <v>1668</v>
       </c>
     </row>
   </sheetData>

--- a/config/becExpConfig/becExpType.csv.xlsx
+++ b/config/becExpConfig/becExpType.csv.xlsx
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1936" uniqueCount="1669">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2479" uniqueCount="2212">
   <si>
     <t>TrialName</t>
   </si>
@@ -5037,6 +5037,1635 @@
   </si>
   <si>
     <t>PhaseLockName,ImagingLock;Frequency,700000000;VariableName,hw_ImagingHf</t>
+  </si>
+  <si>
+    <t>NiLatticeCameraOdt</t>
+  </si>
+  <si>
+    <t>An experiment at the non-interacting lattice stage.</t>
+  </si>
+  <si>
+    <t>ODT</t>
+  </si>
+  <si>
+    <t>SideOdtCamera</t>
+  </si>
+  <si>
+    <t>None</t>
+  </si>
+  <si>
+    <t>RunIndex</t>
+  </si>
+  <si>
+    <t>DensityFit;AtomNumber;CenterFit</t>
+  </si>
+  <si>
+    <t>LSR</t>
+  </si>
+  <si>
+    <t>HF</t>
+  </si>
+  <si>
+    <t>Absorption</t>
+  </si>
+  <si>
+    <t>RandomPolarization</t>
+  </si>
+  <si>
+    <t>BosonicGaussianFit1D</t>
+  </si>
+  <si>
+    <t>None</t>
+  </si>
+  <si>
+    <t>LinearFit1D</t>
+  </si>
+  <si>
+    <t>StdErr</t>
+  </si>
+  <si>
+    <t>WaveformGeneratorName,XvWingMod;ChannelName,Ch1;WaveformListName,XvWingNi</t>
+  </si>
+  <si>
+    <t>PhaseLockName,ImagingLock;Frequency,700000000;VariableName,hw_ImagingNi</t>
+  </si>
+  <si>
+    <t>EvapD</t>
+  </si>
+  <si>
+    <t>An experiment at evaporation stage D.</t>
+  </si>
+  <si>
+    <t>TOP</t>
+  </si>
+  <si>
+    <t>EvapDOdt1</t>
+  </si>
+  <si>
+    <t>None</t>
+  </si>
+  <si>
+    <t>CiceroLogTime</t>
+  </si>
+  <si>
+    <t>AtomNumber;DensityFit;CenterFit</t>
+  </si>
+  <si>
+    <t>LSR</t>
+  </si>
+  <si>
+    <t>[549 1745;903 1905;1286 1930;1532 1678;1603 1325;1617 1085;1501 850;1355 743;908 715;693 740;535 925;522 1284]</t>
+  </si>
+  <si>
+    <t>LF</t>
+  </si>
+  <si>
+    <t>Absorption</t>
+  </si>
+  <si>
+    <t>RandomPolarization</t>
+  </si>
+  <si>
+    <t>BosonicGaussianFit1D</t>
+  </si>
+  <si>
+    <t>None</t>
+  </si>
+  <si>
+    <t>LinearFit1D</t>
+  </si>
+  <si>
+    <t>StdErr</t>
+  </si>
+  <si>
+    <t>PhaseLockName,ImagingLock;Frequency,700000000;VariableName,hw_ImagingLf</t>
+  </si>
+  <si>
+    <t>NiLatticePdMagic</t>
+  </si>
+  <si>
+    <t>An experiment at the non-interacting lattice stage. Scan KP2VVA.</t>
+  </si>
+  <si>
+    <t>TOP</t>
+  </si>
+  <si>
+    <t>BMPDloopTof8000</t>
+  </si>
+  <si>
+    <t>None</t>
+  </si>
+  <si>
+    <t>KP2VVA</t>
+  </si>
+  <si>
+    <t>DensityFit;AtomNumber</t>
+  </si>
+  <si>
+    <t>LSR</t>
+  </si>
+  <si>
+    <t>[428 1188;595 1085;914 1060;1346 1060;1549 1122;1581 1345;1453 1464;1010 1503;481 1490]</t>
+  </si>
+  <si>
+    <t>HF</t>
+  </si>
+  <si>
+    <t>Absorption</t>
+  </si>
+  <si>
+    <t>StrongLight</t>
+  </si>
+  <si>
+    <t>BosonicGaussianFit1D</t>
+  </si>
+  <si>
+    <t>None</t>
+  </si>
+  <si>
+    <t>ParabolicFit1D</t>
+  </si>
+  <si>
+    <t>StdErr</t>
+  </si>
+  <si>
+    <t>WaveformGeneratorName,LatticeMod,XvWingMod;ChannelName,Ch2,Ch1;WaveformListName,PdAi,XvWingLattice</t>
+  </si>
+  <si>
+    <t>PhaseLockName,ImagingLock;Frequency,700000000;VariableName,hw_ImagingNi</t>
+  </si>
+  <si>
+    <t>NiLatticeKPRampTimeBm</t>
+  </si>
+  <si>
+    <t>An experiment at the non-interacting lattice stage. With band mapping.</t>
+  </si>
+  <si>
+    <t>TOP</t>
+  </si>
+  <si>
+    <t>NiLattice</t>
+  </si>
+  <si>
+    <t>None</t>
+  </si>
+  <si>
+    <t>KPRampTime</t>
+  </si>
+  <si>
+    <t>DensityFit;AtomNumber;CenterFit</t>
+  </si>
+  <si>
+    <t>LSR</t>
+  </si>
+  <si>
+    <t>HF</t>
+  </si>
+  <si>
+    <t>Absorption</t>
+  </si>
+  <si>
+    <t>StrongLight</t>
+  </si>
+  <si>
+    <t>BosonicGaussianFit1D</t>
+  </si>
+  <si>
+    <t>None</t>
+  </si>
+  <si>
+    <t>LinearFit1D</t>
+  </si>
+  <si>
+    <t>StdErr</t>
+  </si>
+  <si>
+    <t>WaveformGeneratorName,XvWingMod;ChannelName,Ch1;WaveformListName,XvWingNi</t>
+  </si>
+  <si>
+    <t>PhaseLockName,ImagingLock;Frequency,700000000;VariableName,hw_ImagingNi</t>
+  </si>
+  <si>
+    <t>NiLatticeKPRampTimeBm</t>
+  </si>
+  <si>
+    <t>An experiment at the non-interacting lattice stage. With band mapping. Scan KPRampTime.</t>
+  </si>
+  <si>
+    <t>TOP</t>
+  </si>
+  <si>
+    <t>NiLattice</t>
+  </si>
+  <si>
+    <t>None</t>
+  </si>
+  <si>
+    <t>KPRampTime</t>
+  </si>
+  <si>
+    <t>DensityFit;AtomNumber;CenterFit</t>
+  </si>
+  <si>
+    <t>LSR</t>
+  </si>
+  <si>
+    <t>HF</t>
+  </si>
+  <si>
+    <t>Absorption</t>
+  </si>
+  <si>
+    <t>StrongLight</t>
+  </si>
+  <si>
+    <t>BosonicGaussianFit1D</t>
+  </si>
+  <si>
+    <t>None</t>
+  </si>
+  <si>
+    <t>LinearFit1D</t>
+  </si>
+  <si>
+    <t>StdErr</t>
+  </si>
+  <si>
+    <t>WaveformGeneratorName,XvWingMod;ChannelName,Ch1;WaveformListName,XvWingNi</t>
+  </si>
+  <si>
+    <t>PhaseLockName,ImagingLock;Frequency,700000000;VariableName,hw_ImagingNi</t>
+  </si>
+  <si>
+    <t>NiLatticeKPRampTimeBm</t>
+  </si>
+  <si>
+    <t>An experiment at the non-interacting lattice stage. With band mapping. Scan KPRampTime.</t>
+  </si>
+  <si>
+    <t>TOP</t>
+  </si>
+  <si>
+    <t>NiLattice</t>
+  </si>
+  <si>
+    <t>None</t>
+  </si>
+  <si>
+    <t>KPRampTime</t>
+  </si>
+  <si>
+    <t>DensityFit;AtomNumber;CenterFit</t>
+  </si>
+  <si>
+    <t>LSR</t>
+  </si>
+  <si>
+    <t>[850 1206;943 1161;1062 1172;1097 1243;1097 1343;1054 1370;899 1373;864 1331]</t>
+  </si>
+  <si>
+    <t>HF</t>
+  </si>
+  <si>
+    <t>Absorption</t>
+  </si>
+  <si>
+    <t>StrongLight</t>
+  </si>
+  <si>
+    <t>BosonicGaussianFit1D</t>
+  </si>
+  <si>
+    <t>None</t>
+  </si>
+  <si>
+    <t>LinearFit1D</t>
+  </si>
+  <si>
+    <t>StdErr</t>
+  </si>
+  <si>
+    <t>WaveformGeneratorName,XvWingMod;ChannelName,Ch1;WaveformListName,XvWingNi</t>
+  </si>
+  <si>
+    <t>PhaseLockName,ImagingLock;Frequency,700000000;VariableName,hw_ImagingNi</t>
+  </si>
+  <si>
+    <t>NiLatticeKPRampTimeBm</t>
+  </si>
+  <si>
+    <t>An experiment at the non-interacting lattice stage. With band mapping. Scan KPRampTime.</t>
+  </si>
+  <si>
+    <t>TOP</t>
+  </si>
+  <si>
+    <t>NiLattice</t>
+  </si>
+  <si>
+    <t>None</t>
+  </si>
+  <si>
+    <t>KPRampTime</t>
+  </si>
+  <si>
+    <t>DensityFit;AtomNumber;CenterFit</t>
+  </si>
+  <si>
+    <t>LSR</t>
+  </si>
+  <si>
+    <t>[850 1206;943 1161;1062 1172;1097 1243;1097 1343;1054 1370;899 1373;864 1331]</t>
+  </si>
+  <si>
+    <t>HF</t>
+  </si>
+  <si>
+    <t>Absorption</t>
+  </si>
+  <si>
+    <t>StrongLight</t>
+  </si>
+  <si>
+    <t>BosonicGaussianFit1D</t>
+  </si>
+  <si>
+    <t>None</t>
+  </si>
+  <si>
+    <t>LinearFit1D</t>
+  </si>
+  <si>
+    <t>StdErr</t>
+  </si>
+  <si>
+    <t>WaveformGeneratorName,XvWingMod;ChannelName,Ch1;WaveformListName,XvWingNi</t>
+  </si>
+  <si>
+    <t>PhaseLockName,ImagingLock;Frequency,700000000;VariableName,hw_ImagingNi</t>
+  </si>
+  <si>
+    <t>NiLatticeKPRampTimeBm</t>
+  </si>
+  <si>
+    <t>An experiment at the non-interacting lattice stage. With band mapping. Scan KPRampTime.</t>
+  </si>
+  <si>
+    <t>TOP</t>
+  </si>
+  <si>
+    <t>NiLattice</t>
+  </si>
+  <si>
+    <t>None</t>
+  </si>
+  <si>
+    <t>KPRampTime</t>
+  </si>
+  <si>
+    <t>DensityFit;AtomNumber;CenterFit</t>
+  </si>
+  <si>
+    <t>LSR</t>
+  </si>
+  <si>
+    <t>[850 1206;943 1161;1062 1172;1097 1243;1097 1343;1054 1370;899 1373;864 1331]</t>
+  </si>
+  <si>
+    <t>HF</t>
+  </si>
+  <si>
+    <t>Absorption</t>
+  </si>
+  <si>
+    <t>StrongLight</t>
+  </si>
+  <si>
+    <t>BosonicGaussianFit1D</t>
+  </si>
+  <si>
+    <t>None</t>
+  </si>
+  <si>
+    <t>LinearFit1D</t>
+  </si>
+  <si>
+    <t>StdErr</t>
+  </si>
+  <si>
+    <t>WaveformGeneratorName,XvWingMod;ChannelName,Ch1;WaveformListName,XvWingNi</t>
+  </si>
+  <si>
+    <t>PhaseLockName,ImagingLock;Frequency,700000000;VariableName,hw_ImagingNi</t>
+  </si>
+  <si>
+    <t>NiLatticeKPRampTimeBm</t>
+  </si>
+  <si>
+    <t>An experiment at the non-interacting lattice stage. With band mapping. Scan KPRampTime.</t>
+  </si>
+  <si>
+    <t>TOP</t>
+  </si>
+  <si>
+    <t>NiLatticeMomentumCheck</t>
+  </si>
+  <si>
+    <t>None</t>
+  </si>
+  <si>
+    <t>KPRampTime</t>
+  </si>
+  <si>
+    <t>DensityFit;AtomNumber;CenterFit</t>
+  </si>
+  <si>
+    <t>LSR</t>
+  </si>
+  <si>
+    <t>[850 1206;943 1161;1062 1172;1097 1243;1097 1343;1054 1370;899 1373;864 1331]</t>
+  </si>
+  <si>
+    <t>HF</t>
+  </si>
+  <si>
+    <t>Absorption</t>
+  </si>
+  <si>
+    <t>StrongLight</t>
+  </si>
+  <si>
+    <t>BosonicGaussianFit1D</t>
+  </si>
+  <si>
+    <t>None</t>
+  </si>
+  <si>
+    <t>LinearFit1D</t>
+  </si>
+  <si>
+    <t>StdDev</t>
+  </si>
+  <si>
+    <t>WaveformGeneratorName,XvWingMod;ChannelName,Ch1;WaveformListName,XvWingNi</t>
+  </si>
+  <si>
+    <t>PhaseLockName,ImagingLock;Frequency,700000000;VariableName,hw_ImagingNi</t>
+  </si>
+  <si>
+    <t>NiLatticeMultiplierBm</t>
+  </si>
+  <si>
+    <t>An experiment at the non-interacting lattice stage. With band mapping. Scan KPRampTime.</t>
+  </si>
+  <si>
+    <t>TOP</t>
+  </si>
+  <si>
+    <t>NiLatticeMomentumCheck</t>
+  </si>
+  <si>
+    <t>None</t>
+  </si>
+  <si>
+    <t>multiplier</t>
+  </si>
+  <si>
+    <t>DensityFit;AtomNumber;CenterFit</t>
+  </si>
+  <si>
+    <t>LSR</t>
+  </si>
+  <si>
+    <t>[850 1206;943 1161;1062 1172;1097 1243;1097 1343;1054 1370;899 1373;864 1331]</t>
+  </si>
+  <si>
+    <t>HF</t>
+  </si>
+  <si>
+    <t>Absorption</t>
+  </si>
+  <si>
+    <t>StrongLight</t>
+  </si>
+  <si>
+    <t>BosonicGaussianFit1D</t>
+  </si>
+  <si>
+    <t>None</t>
+  </si>
+  <si>
+    <t>LinearFit1D</t>
+  </si>
+  <si>
+    <t>StdDev</t>
+  </si>
+  <si>
+    <t>WaveformGeneratorName,XvWingMod;ChannelName,Ch1;WaveformListName,XvWingNi</t>
+  </si>
+  <si>
+    <t>PhaseLockName,ImagingLock;Frequency,700000000;VariableName,hw_ImagingNi</t>
+  </si>
+  <si>
+    <t>NiLatticeMultiplierBm</t>
+  </si>
+  <si>
+    <t>An experiment at the non-interacting lattice stage. With band mapping. Scan multiplier.</t>
+  </si>
+  <si>
+    <t>TOP</t>
+  </si>
+  <si>
+    <t>NiLatticeMomentumCheck</t>
+  </si>
+  <si>
+    <t>None</t>
+  </si>
+  <si>
+    <t>multiplier</t>
+  </si>
+  <si>
+    <t>DensityFit;AtomNumber;CenterFit</t>
+  </si>
+  <si>
+    <t>LSR</t>
+  </si>
+  <si>
+    <t>[850 1206;943 1161;1062 1172;1097 1243;1097 1343;1054 1370;899 1373;864 1331]</t>
+  </si>
+  <si>
+    <t>HF</t>
+  </si>
+  <si>
+    <t>Absorption</t>
+  </si>
+  <si>
+    <t>StrongLight</t>
+  </si>
+  <si>
+    <t>BosonicGaussianFit1D</t>
+  </si>
+  <si>
+    <t>None</t>
+  </si>
+  <si>
+    <t>LinearFit1D</t>
+  </si>
+  <si>
+    <t>StdDev</t>
+  </si>
+  <si>
+    <t>WaveformGeneratorName,XvWingMod;ChannelName,Ch1;WaveformListName,XvWingNi</t>
+  </si>
+  <si>
+    <t>PhaseLockName,ImagingLock;Frequency,700000000;VariableName,hw_ImagingNi</t>
+  </si>
+  <si>
+    <t>NiLatticeBoBm</t>
+  </si>
+  <si>
+    <t>A Bloch oscillation experiment at the non-interacting lattice stage. With band mapping.</t>
+  </si>
+  <si>
+    <t>TOP</t>
+  </si>
+  <si>
+    <t>NiLatticeBoBmTof5000</t>
+  </si>
+  <si>
+    <t>None</t>
+  </si>
+  <si>
+    <t>latticehold</t>
+  </si>
+  <si>
+    <t>DensityFit;AtomNumber;CenterFit</t>
+  </si>
+  <si>
+    <t>LSR</t>
+  </si>
+  <si>
+    <t>[790 1235;871 1209;1275 1193;1400 1215;1404 1288;1311 1320;928 1334;800 1309]</t>
+  </si>
+  <si>
+    <t>HF</t>
+  </si>
+  <si>
+    <t>Absorption</t>
+  </si>
+  <si>
+    <t>StrongLight</t>
+  </si>
+  <si>
+    <t>BosonicGaussianFit1D</t>
+  </si>
+  <si>
+    <t>None</t>
+  </si>
+  <si>
+    <t>TriangleFit1D</t>
+  </si>
+  <si>
+    <t>StdErr</t>
+  </si>
+  <si>
+    <t>WaveformGeneratorName,XvWingMod;ChannelName,Ch1;WaveformListName,XvWingLattice</t>
+  </si>
+  <si>
+    <t>PhaseLockName,ImagingLock;Frequency,700000000;VariableName,hw_ImagingNi</t>
+  </si>
+  <si>
+    <t>NiLatticeBoBm</t>
+  </si>
+  <si>
+    <t>A Bloch oscillation experiment at the non-interacting lattice stage. With band mapping.</t>
+  </si>
+  <si>
+    <t>TOP</t>
+  </si>
+  <si>
+    <t>NiLatticeBoBmTof8000</t>
+  </si>
+  <si>
+    <t>None</t>
+  </si>
+  <si>
+    <t>latticehold</t>
+  </si>
+  <si>
+    <t>DensityFit;AtomNumber;CenterFit</t>
+  </si>
+  <si>
+    <t>LSR</t>
+  </si>
+  <si>
+    <t>[790 1235;871 1209;1275 1193;1400 1215;1404 1288;1311 1320;928 1334;800 1309]</t>
+  </si>
+  <si>
+    <t>HF</t>
+  </si>
+  <si>
+    <t>Absorption</t>
+  </si>
+  <si>
+    <t>StrongLight</t>
+  </si>
+  <si>
+    <t>BosonicGaussianFit1D</t>
+  </si>
+  <si>
+    <t>None</t>
+  </si>
+  <si>
+    <t>TriangleFit1D</t>
+  </si>
+  <si>
+    <t>StdErr</t>
+  </si>
+  <si>
+    <t>WaveformGeneratorName,XvWingMod;ChannelName,Ch1;WaveformListName,XvWingLattice</t>
+  </si>
+  <si>
+    <t>PhaseLockName,ImagingLock;Frequency,700000000;VariableName,hw_ImagingNi</t>
+  </si>
+  <si>
+    <t>NiLatticeSdCalibFreqStart</t>
+  </si>
+  <si>
+    <t>An experiment at the non-interacting lattice stage. Scan hw_SdCalibFreqStart.</t>
+  </si>
+  <si>
+    <t>TOP</t>
+  </si>
+  <si>
+    <t>NiLatticeDepthCalibTof8000</t>
+  </si>
+  <si>
+    <t>None</t>
+  </si>
+  <si>
+    <t>hw_SdCalibFreqStart</t>
+  </si>
+  <si>
+    <t>DensityFit;AtomNumber</t>
+  </si>
+  <si>
+    <t>LSR</t>
+  </si>
+  <si>
+    <t>[1522 1105;1564 1192;1550 1361;428 1404;424 1170]</t>
+  </si>
+  <si>
+    <t>HF</t>
+  </si>
+  <si>
+    <t>Absorption</t>
+  </si>
+  <si>
+    <t>StrongLight</t>
+  </si>
+  <si>
+    <t>BosonicGaussianFit1D</t>
+  </si>
+  <si>
+    <t>None</t>
+  </si>
+  <si>
+    <t>ParabolicFit1D</t>
+  </si>
+  <si>
+    <t>StdErr</t>
+  </si>
+  <si>
+    <t>WaveformGeneratorName,LatticeMod,XvWingMod;ChannelName,Ch2,Ch1;WaveformListName,SdDepthCalib,XvWingNi</t>
+  </si>
+  <si>
+    <t>PhaseLockName,ImagingLock;Frequency,700000000;VariableName,hw_ImagingNi</t>
+  </si>
+  <si>
+    <t>EvapD</t>
+  </si>
+  <si>
+    <t>An experiment at evaporation stage D.</t>
+  </si>
+  <si>
+    <t>TOP</t>
+  </si>
+  <si>
+    <t>EvapDOdt1</t>
+  </si>
+  <si>
+    <t>None</t>
+  </si>
+  <si>
+    <t>CiceroLogTime</t>
+  </si>
+  <si>
+    <t>AtomNumber;DensityFit;CenterFit</t>
+  </si>
+  <si>
+    <t>LSR</t>
+  </si>
+  <si>
+    <t>[549 1745;903 1905;1286 1930;1532 1678;1603 1325;1617 1085;1501 850;1355 743;908 715;693 740;535 925;522 1284]</t>
+  </si>
+  <si>
+    <t>LF</t>
+  </si>
+  <si>
+    <t>Absorption</t>
+  </si>
+  <si>
+    <t>RandomPolarization</t>
+  </si>
+  <si>
+    <t>BosonicGaussianFit1D</t>
+  </si>
+  <si>
+    <t>None</t>
+  </si>
+  <si>
+    <t>LinearFit1D</t>
+  </si>
+  <si>
+    <t>StdErr</t>
+  </si>
+  <si>
+    <t>PhaseLockName,ImagingLock;Frequency,700000000;VariableName,hw_ImagingLf</t>
+  </si>
+  <si>
+    <t>NiLatticePdPulsePhaseBm</t>
+  </si>
+  <si>
+    <t>An experiment at the non-interacting lattice stage. Scan PD pulse phase. With band mapping.</t>
+  </si>
+  <si>
+    <t>TOP</t>
+  </si>
+  <si>
+    <t>BMPDloopTof8000</t>
+  </si>
+  <si>
+    <t>None</t>
+  </si>
+  <si>
+    <t>hw_PdModPhase</t>
+  </si>
+  <si>
+    <t>DensityFit;AtomNumber</t>
+  </si>
+  <si>
+    <t>LSR</t>
+  </si>
+  <si>
+    <t>HF</t>
+  </si>
+  <si>
+    <t>Absorption</t>
+  </si>
+  <si>
+    <t>StrongLight</t>
+  </si>
+  <si>
+    <t>BosonicGaussianFit1D</t>
+  </si>
+  <si>
+    <t>None</t>
+  </si>
+  <si>
+    <t>LinearFit1D</t>
+  </si>
+  <si>
+    <t>StdErr</t>
+  </si>
+  <si>
+    <t>WaveformGeneratorName,LatticeMod,XvWingMod;ChannelName,Ch2,Ch1;WaveformListName,PdAiPulse,XvWingLattice</t>
+  </si>
+  <si>
+    <t>PhaseLockName,ImagingLock;Frequency,700000000;VariableName,hw_ImagingNi</t>
+  </si>
+  <si>
+    <t>NiLatticePdPulsePhaseBm</t>
+  </si>
+  <si>
+    <t>An experiment at the non-interacting lattice stage. Scan PD pulse phase. With band mapping.</t>
+  </si>
+  <si>
+    <t>TOP</t>
+  </si>
+  <si>
+    <t>BMPDloopTof8000</t>
+  </si>
+  <si>
+    <t>None</t>
+  </si>
+  <si>
+    <t>hw_PdModPhase</t>
+  </si>
+  <si>
+    <t>DensityFit;AtomNumber</t>
+  </si>
+  <si>
+    <t>LSR</t>
+  </si>
+  <si>
+    <t>HF</t>
+  </si>
+  <si>
+    <t>Absorption</t>
+  </si>
+  <si>
+    <t>StrongLight</t>
+  </si>
+  <si>
+    <t>BosonicGaussianFit1D</t>
+  </si>
+  <si>
+    <t>None</t>
+  </si>
+  <si>
+    <t>LinearFit1D</t>
+  </si>
+  <si>
+    <t>StdErr</t>
+  </si>
+  <si>
+    <t>WaveformGeneratorName,LatticeMod,XvWingMod;ChannelName,Ch2,Ch1;WaveformListName,PdAiPulse,XvWingLattice</t>
+  </si>
+  <si>
+    <t>PhaseLockName,ImagingLock;Frequency,700000000;VariableName,hw_ImagingNi</t>
+  </si>
+  <si>
+    <t>NiLatticePdModDepth</t>
+  </si>
+  <si>
+    <t>An experiment at the non-interacting lattice stage. Scan PD modulation depth.</t>
+  </si>
+  <si>
+    <t>TOP</t>
+  </si>
+  <si>
+    <t>BMPDloopTof8000</t>
+  </si>
+  <si>
+    <t>None</t>
+  </si>
+  <si>
+    <t>hw_PdModDepth</t>
+  </si>
+  <si>
+    <t>DensityFit;AtomNumber</t>
+  </si>
+  <si>
+    <t>LSR</t>
+  </si>
+  <si>
+    <t>[405 1189;681 1173;1573 1141;1664 1288;1578 1335;814 1380;432 1392;357 1309]</t>
+  </si>
+  <si>
+    <t>HF</t>
+  </si>
+  <si>
+    <t>Absorption</t>
+  </si>
+  <si>
+    <t>StrongLight</t>
+  </si>
+  <si>
+    <t>BosonicGaussianFit1D</t>
+  </si>
+  <si>
+    <t>None</t>
+  </si>
+  <si>
+    <t>LinearFit1D</t>
+  </si>
+  <si>
+    <t>StdErr</t>
+  </si>
+  <si>
+    <t>PhaseLockName,ImagingLock;Frequency,700000000;VariableName,hw_ImagingNi</t>
+  </si>
+  <si>
+    <t>NiLatticePdModDepth</t>
+  </si>
+  <si>
+    <t>An experiment at the non-interacting lattice stage. Scan PD modulation depth.</t>
+  </si>
+  <si>
+    <t>TOP</t>
+  </si>
+  <si>
+    <t>BMPDloopTof8000</t>
+  </si>
+  <si>
+    <t>None</t>
+  </si>
+  <si>
+    <t>hw_PdModDepth</t>
+  </si>
+  <si>
+    <t>DensityFit;AtomNumber</t>
+  </si>
+  <si>
+    <t>LSR</t>
+  </si>
+  <si>
+    <t>[405 1189;681 1173;1573 1141;1664 1288;1578 1335;814 1380;432 1392;357 1309]</t>
+  </si>
+  <si>
+    <t>HF</t>
+  </si>
+  <si>
+    <t>Absorption</t>
+  </si>
+  <si>
+    <t>StrongLight</t>
+  </si>
+  <si>
+    <t>BosonicGaussianFit1D</t>
+  </si>
+  <si>
+    <t>None</t>
+  </si>
+  <si>
+    <t>LinearFit1D</t>
+  </si>
+  <si>
+    <t>StdErr</t>
+  </si>
+  <si>
+    <t>PhaseLockName,ImagingLock;Frequency,700000000;VariableName,hw_ImagingNi</t>
+  </si>
+  <si>
+    <t>NiLatticePdPulsePhaseBm</t>
+  </si>
+  <si>
+    <t>An experiment at the non-interacting lattice stage. Scan PD pulse phase. With band mapping.</t>
+  </si>
+  <si>
+    <t>TOP</t>
+  </si>
+  <si>
+    <t>BMPDloopTof8000</t>
+  </si>
+  <si>
+    <t>None</t>
+  </si>
+  <si>
+    <t>hw_PdModPhase</t>
+  </si>
+  <si>
+    <t>DensityFit;AtomNumber</t>
+  </si>
+  <si>
+    <t>LSR</t>
+  </si>
+  <si>
+    <t>HF</t>
+  </si>
+  <si>
+    <t>Absorption</t>
+  </si>
+  <si>
+    <t>StrongLight</t>
+  </si>
+  <si>
+    <t>BosonicGaussianFit1D</t>
+  </si>
+  <si>
+    <t>None</t>
+  </si>
+  <si>
+    <t>LinearFit1D</t>
+  </si>
+  <si>
+    <t>StdErr</t>
+  </si>
+  <si>
+    <t>WaveformGeneratorName,LatticeMod,XvWingMod;ChannelName,Ch2,Ch1;WaveformListName,PdAiPulse,XvWingLattice</t>
+  </si>
+  <si>
+    <t>PhaseLockName,ImagingLock;Frequency,700000000;VariableName,hw_ImagingNi</t>
+  </si>
+  <si>
+    <t>NiLatticePdPulsePhaseBm</t>
+  </si>
+  <si>
+    <t>An experiment at the non-interacting lattice stage. Scan PD pulse phase. With band mapping.</t>
+  </si>
+  <si>
+    <t>TOP</t>
+  </si>
+  <si>
+    <t>BMPDloopTof8000</t>
+  </si>
+  <si>
+    <t>None</t>
+  </si>
+  <si>
+    <t>hw_PdModPhase</t>
+  </si>
+  <si>
+    <t>DensityFit;AtomNumber</t>
+  </si>
+  <si>
+    <t>LSR</t>
+  </si>
+  <si>
+    <t>[369 1213;566 1175;1395 1141;1619 1168;1628 1333;436 1384;377 1344]</t>
+  </si>
+  <si>
+    <t>HF</t>
+  </si>
+  <si>
+    <t>Absorption</t>
+  </si>
+  <si>
+    <t>StrongLight</t>
+  </si>
+  <si>
+    <t>BosonicGaussianFit1D</t>
+  </si>
+  <si>
+    <t>None</t>
+  </si>
+  <si>
+    <t>LinearFit1D</t>
+  </si>
+  <si>
+    <t>StdErr</t>
+  </si>
+  <si>
+    <t>WaveformGeneratorName,LatticeMod,XvWingMod;ChannelName,Ch2,Ch1;WaveformListName,PdAiPulse,XvWingLattice</t>
+  </si>
+  <si>
+    <t>PhaseLockName,ImagingLock;Frequency,700000000;VariableName,hw_ImagingNi</t>
+  </si>
+  <si>
+    <t>NiLatticePdPulsePhaseBm</t>
+  </si>
+  <si>
+    <t>An experiment at the non-interacting lattice stage. Scan PD pulse phase. With band mapping.</t>
+  </si>
+  <si>
+    <t>TOP</t>
+  </si>
+  <si>
+    <t>BMPDloopTof8000</t>
+  </si>
+  <si>
+    <t>None</t>
+  </si>
+  <si>
+    <t>hw_PdModPhase</t>
+  </si>
+  <si>
+    <t>DensityFit;AtomNumber</t>
+  </si>
+  <si>
+    <t>LSR</t>
+  </si>
+  <si>
+    <t>[369 1213;566 1175;1395 1141;1619 1168;1628 1333;436 1384;377 1344]</t>
+  </si>
+  <si>
+    <t>HF</t>
+  </si>
+  <si>
+    <t>Absorption</t>
+  </si>
+  <si>
+    <t>StrongLight</t>
+  </si>
+  <si>
+    <t>BosonicGaussianFit1D</t>
+  </si>
+  <si>
+    <t>None</t>
+  </si>
+  <si>
+    <t>LinearFit1D</t>
+  </si>
+  <si>
+    <t>StdErr</t>
+  </si>
+  <si>
+    <t>WaveformGeneratorName,LatticeMod,XvWingMod;ChannelName,Ch2,Ch1;WaveformListName,PdAiPulse,XvWingLattice</t>
+  </si>
+  <si>
+    <t>PhaseLockName,ImagingLock;Frequency,700000000;VariableName,hw_ImagingNi</t>
+  </si>
+  <si>
+    <t>NiLatticeSpModDepth</t>
+  </si>
+  <si>
+    <t>An experiment at the non-interacting lattice stage. Scan PD modulation depth.</t>
+  </si>
+  <si>
+    <t>TOP</t>
+  </si>
+  <si>
+    <t>BMPDloopTof8000</t>
+  </si>
+  <si>
+    <t>None</t>
+  </si>
+  <si>
+    <t>hw_PdModDepth</t>
+  </si>
+  <si>
+    <t>DensityFit;AtomNumber</t>
+  </si>
+  <si>
+    <t>LSR</t>
+  </si>
+  <si>
+    <t>[405 1189;681 1173;1573 1141;1664 1288;1578 1335;814 1380;432 1392;357 1309]</t>
+  </si>
+  <si>
+    <t>HF</t>
+  </si>
+  <si>
+    <t>Absorption</t>
+  </si>
+  <si>
+    <t>StrongLight</t>
+  </si>
+  <si>
+    <t>BosonicGaussianFit1D</t>
+  </si>
+  <si>
+    <t>None</t>
+  </si>
+  <si>
+    <t>LinearFit1D</t>
+  </si>
+  <si>
+    <t>StdErr</t>
+  </si>
+  <si>
+    <t>PhaseLockName,ImagingLock;Frequency,700000000;VariableName,hw_ImagingNi</t>
+  </si>
+  <si>
+    <t>NiLatticeSpModDepth</t>
+  </si>
+  <si>
+    <t>An experiment at the non-interacting lattice stage. Scan PD modulation depth.</t>
+  </si>
+  <si>
+    <t>TOP</t>
+  </si>
+  <si>
+    <t>BMPDloopTof8000</t>
+  </si>
+  <si>
+    <t>None</t>
+  </si>
+  <si>
+    <t>hw_SpModDepth</t>
+  </si>
+  <si>
+    <t>DensityFit;AtomNumber</t>
+  </si>
+  <si>
+    <t>LSR</t>
+  </si>
+  <si>
+    <t>[405 1189;681 1173;1573 1141;1664 1288;1578 1335;814 1380;432 1392;357 1309]</t>
+  </si>
+  <si>
+    <t>HF</t>
+  </si>
+  <si>
+    <t>Absorption</t>
+  </si>
+  <si>
+    <t>StrongLight</t>
+  </si>
+  <si>
+    <t>BosonicGaussianFit1D</t>
+  </si>
+  <si>
+    <t>None</t>
+  </si>
+  <si>
+    <t>LinearFit1D</t>
+  </si>
+  <si>
+    <t>StdErr</t>
+  </si>
+  <si>
+    <t>PhaseLockName,ImagingLock;Frequency,700000000;VariableName,hw_ImagingNi</t>
+  </si>
+  <si>
+    <t>NiLatticePdFullBoModDepth</t>
+  </si>
+  <si>
+    <t>An experiment at the non-interacting lattice stage. Scan PD modulation depth.</t>
+  </si>
+  <si>
+    <t>TOP</t>
+  </si>
+  <si>
+    <t>BMPDloopTof8000</t>
+  </si>
+  <si>
+    <t>None</t>
+  </si>
+  <si>
+    <t>hw_PdModDepth</t>
+  </si>
+  <si>
+    <t>DensityFit;AtomNumber</t>
+  </si>
+  <si>
+    <t>LSR</t>
+  </si>
+  <si>
+    <t>[405 1189;681 1173;1573 1141;1664 1288;1578 1335;814 1380;432 1392;357 1309]</t>
+  </si>
+  <si>
+    <t>HF</t>
+  </si>
+  <si>
+    <t>Absorption</t>
+  </si>
+  <si>
+    <t>StrongLight</t>
+  </si>
+  <si>
+    <t>BosonicGaussianFit1D</t>
+  </si>
+  <si>
+    <t>None</t>
+  </si>
+  <si>
+    <t>LinearFit1D</t>
+  </si>
+  <si>
+    <t>StdErr</t>
+  </si>
+  <si>
+    <t>PhaseLockName,ImagingLock;Frequency,700000000;VariableName,hw_ImagingNi</t>
+  </si>
+  <si>
+    <t>NiLatticePdFullBoModDepth</t>
+  </si>
+  <si>
+    <t>An experiment at the non-interacting lattice stage. Scan PD modulation depth.</t>
+  </si>
+  <si>
+    <t>TOP</t>
+  </si>
+  <si>
+    <t>BMPDloopTof8000</t>
+  </si>
+  <si>
+    <t>None</t>
+  </si>
+  <si>
+    <t>hw_PdModDepth2</t>
+  </si>
+  <si>
+    <t>DensityFit;AtomNumber</t>
+  </si>
+  <si>
+    <t>LSR</t>
+  </si>
+  <si>
+    <t>[405 1189;681 1173;1573 1141;1664 1288;1578 1335;814 1380;432 1392;357 1309]</t>
+  </si>
+  <si>
+    <t>HF</t>
+  </si>
+  <si>
+    <t>Absorption</t>
+  </si>
+  <si>
+    <t>StrongLight</t>
+  </si>
+  <si>
+    <t>BosonicGaussianFit1D</t>
+  </si>
+  <si>
+    <t>None</t>
+  </si>
+  <si>
+    <t>LinearFit1D</t>
+  </si>
+  <si>
+    <t>StdErr</t>
+  </si>
+  <si>
+    <t>PhaseLockName,ImagingLock;Frequency,700000000;VariableName,hw_ImagingNi</t>
+  </si>
+  <si>
+    <t>NiLatticeFullBoXvLatticeBm</t>
+  </si>
+  <si>
+    <t>An experiment at the non-interacting lattice stage. Scan xvlattice. With band mapping.</t>
+  </si>
+  <si>
+    <t>TOP</t>
+  </si>
+  <si>
+    <t>BMPDLoopFullBoTof8000</t>
+  </si>
+  <si>
+    <t>None</t>
+  </si>
+  <si>
+    <t>hw_XvLattice</t>
+  </si>
+  <si>
+    <t>DensityFit;AtomNumber</t>
+  </si>
+  <si>
+    <t>LSR</t>
+  </si>
+  <si>
+    <t>[353 1231;517 1162;1370 1128;1605 1136;1657 1227;1628 1333;1262 1362;668 1384;385 1392;364 1330]</t>
+  </si>
+  <si>
+    <t>HF</t>
+  </si>
+  <si>
+    <t>Absorption</t>
+  </si>
+  <si>
+    <t>StrongLight</t>
+  </si>
+  <si>
+    <t>BosonicGaussianFit1D</t>
+  </si>
+  <si>
+    <t>None</t>
+  </si>
+  <si>
+    <t>LinearFit1D</t>
+  </si>
+  <si>
+    <t>StdErr</t>
+  </si>
+  <si>
+    <t>WaveformGeneratorName,LatticeMod,XvWingMod;ChannelName,Ch2,Ch1;WaveformListName,PdAi,XvWingLattice</t>
+  </si>
+  <si>
+    <t>PhaseLockName,ImagingLock;Frequency,700000000;VariableName,hw_ImagingNi</t>
+  </si>
+  <si>
+    <t>NiLatticeFullBoXvLatticeBm</t>
+  </si>
+  <si>
+    <t>An experiment at the non-interacting lattice stage. Scan xvlattice. With band mapping.</t>
+  </si>
+  <si>
+    <t>TOP</t>
+  </si>
+  <si>
+    <t>BMPDLoopFullBoTof8000</t>
+  </si>
+  <si>
+    <t>None</t>
+  </si>
+  <si>
+    <t>hw_XvLattice</t>
+  </si>
+  <si>
+    <t>DensityFit;AtomNumber</t>
+  </si>
+  <si>
+    <t>LSR</t>
+  </si>
+  <si>
+    <t>[353 1231;517 1162;1370 1128;1605 1136;1657 1227;1628 1333;1262 1362;668 1384;385 1392;364 1330]</t>
+  </si>
+  <si>
+    <t>HF</t>
+  </si>
+  <si>
+    <t>Absorption</t>
+  </si>
+  <si>
+    <t>StrongLight</t>
+  </si>
+  <si>
+    <t>BosonicGaussianFit1D</t>
+  </si>
+  <si>
+    <t>None</t>
+  </si>
+  <si>
+    <t>LinearFit1D</t>
+  </si>
+  <si>
+    <t>StdErr</t>
+  </si>
+  <si>
+    <t>WaveformGeneratorName,LatticeMod,XvWingMod;ChannelName,Ch2,Ch1;WaveformListName,PdAiPulseFullBo,XvWingLattice</t>
+  </si>
+  <si>
+    <t>PhaseLockName,ImagingLock;Frequency,700000000;VariableName,hw_ImagingNi</t>
+  </si>
+  <si>
+    <t>NiLatticeFullBoXvLatticeBm</t>
+  </si>
+  <si>
+    <t>An experiment at the non-interacting lattice stage. Scan xvlattice. With band mapping.</t>
+  </si>
+  <si>
+    <t>TOP</t>
+  </si>
+  <si>
+    <t>BMPDLoopFullBoTof8000</t>
+  </si>
+  <si>
+    <t>None</t>
+  </si>
+  <si>
+    <t>hw_XvLattice</t>
+  </si>
+  <si>
+    <t>DensityFit;AtomNumber</t>
+  </si>
+  <si>
+    <t>LSR</t>
+  </si>
+  <si>
+    <t>[353 1231;517 1162;1370 1128;1605 1136;1657 1227;1628 1333;1262 1362;668 1384;385 1392;364 1330]</t>
+  </si>
+  <si>
+    <t>HF</t>
+  </si>
+  <si>
+    <t>Absorption</t>
+  </si>
+  <si>
+    <t>StrongLight</t>
+  </si>
+  <si>
+    <t>BosonicGaussianFit1D</t>
+  </si>
+  <si>
+    <t>None</t>
+  </si>
+  <si>
+    <t>LinearFit1D</t>
+  </si>
+  <si>
+    <t>StdErr</t>
+  </si>
+  <si>
+    <t>WaveformGeneratorName,LatticeMod,XvWingMod;ChannelName,Ch2,Ch1;WaveformListName,PdAiPulseFullBo,XvWingLattice</t>
+  </si>
+  <si>
+    <t>PhaseLockName,ImagingLock;Frequency,700000000;VariableName,hw_ImagingNi</t>
+  </si>
+  <si>
+    <t>NiLatticePdFullBoModDepth</t>
+  </si>
+  <si>
+    <t>An experiment at the non-interacting lattice stage. Scan PD modulation depth.</t>
+  </si>
+  <si>
+    <t>TOP</t>
+  </si>
+  <si>
+    <t>BMPDLoopFullBoTof6000</t>
+  </si>
+  <si>
+    <t>None</t>
+  </si>
+  <si>
+    <t>hw_PdModDepth2</t>
+  </si>
+  <si>
+    <t>DensityFit;AtomNumber</t>
+  </si>
+  <si>
+    <t>LSR</t>
+  </si>
+  <si>
+    <t>[405 1189;681 1173;1573 1141;1664 1288;1578 1335;814 1380;432 1392;357 1309]</t>
+  </si>
+  <si>
+    <t>HF</t>
+  </si>
+  <si>
+    <t>Absorption</t>
+  </si>
+  <si>
+    <t>StrongLight</t>
+  </si>
+  <si>
+    <t>BosonicGaussianFit1D</t>
+  </si>
+  <si>
+    <t>None</t>
+  </si>
+  <si>
+    <t>LinearFit1D</t>
+  </si>
+  <si>
+    <t>StdErr</t>
+  </si>
+  <si>
+    <t>PhaseLockName,ImagingLock;Frequency,700000000;VariableName,hw_ImagingNi</t>
+  </si>
+  <si>
+    <t>NiLatticePdPulsePhaseBm</t>
+  </si>
+  <si>
+    <t>An experiment at the non-interacting lattice stage. Scan PD pulse phase. With band mapping.</t>
+  </si>
+  <si>
+    <t>TOP</t>
+  </si>
+  <si>
+    <t>BMPDLoopFullBoTof6000</t>
+  </si>
+  <si>
+    <t>None</t>
+  </si>
+  <si>
+    <t>hw_PdModPhase</t>
+  </si>
+  <si>
+    <t>DensityFit;AtomNumber</t>
+  </si>
+  <si>
+    <t>LSR</t>
+  </si>
+  <si>
+    <t>[369 1213;566 1175;1395 1141;1619 1168;1628 1333;436 1384;377 1344]</t>
+  </si>
+  <si>
+    <t>HF</t>
+  </si>
+  <si>
+    <t>Absorption</t>
+  </si>
+  <si>
+    <t>StrongLight</t>
+  </si>
+  <si>
+    <t>BosonicGaussianFit1D</t>
+  </si>
+  <si>
+    <t>None</t>
+  </si>
+  <si>
+    <t>LinearFit1D</t>
+  </si>
+  <si>
+    <t>StdErr</t>
+  </si>
+  <si>
+    <t>WaveformGeneratorName,XvWingMod;ChannelName,Ch1;WaveformListName,XvWingLattice</t>
+  </si>
+  <si>
+    <t>PhaseLockName,ImagingLock;Frequency,700000000;VariableName,hw_ImagingNi</t>
   </si>
 </sst>
 </file>
@@ -5363,7 +6992,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:V89"/>
+  <dimension ref="A1:V95"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="36.42578125" customWidth="true"/>
@@ -5386,7 +7015,7 @@
     <col min="18" max="18" width="16.42578125" customWidth="true"/>
     <col min="19" max="19" width="17" customWidth="true"/>
     <col min="20" max="20" width="16.85546875" customWidth="true"/>
-    <col min="21" max="21" width="107.28515625" customWidth="true"/>
+    <col min="21" max="21" width="113.7109375" customWidth="true"/>
     <col min="22" max="22" width="73.5703125" customWidth="true"/>
   </cols>
   <sheetData>
@@ -5566,66 +7195,66 @@
     </row>
     <row r="4">
       <c r="A4" s="0" t="s">
-        <v>1549</v>
+        <v>1917</v>
       </c>
       <c r="B4" s="0" t="s">
-        <v>1550</v>
+        <v>1918</v>
       </c>
       <c r="C4" s="0" t="s">
-        <v>1551</v>
+        <v>1919</v>
       </c>
       <c r="D4" s="0" t="s">
-        <v>1552</v>
+        <v>1920</v>
       </c>
       <c r="E4" s="0" t="s">
-        <v>1553</v>
+        <v>1921</v>
       </c>
       <c r="F4" s="0">
         <v>4</v>
       </c>
       <c r="G4" s="0" t="s">
-        <v>1554</v>
+        <v>1922</v>
       </c>
       <c r="H4" s="0" t="s">
-        <v>1555</v>
+        <v>1923</v>
       </c>
       <c r="I4" s="0" t="s">
-        <v>1556</v>
+        <v>1924</v>
       </c>
       <c r="J4" s="0" t="s">
-        <v>1557</v>
+        <v>1925</v>
       </c>
       <c r="K4" s="0" t="s">
-        <v>1558</v>
+        <v>1926</v>
       </c>
       <c r="L4" s="0" t="s">
-        <v>1559</v>
+        <v>1927</v>
       </c>
       <c r="M4" s="0" t="s">
-        <v>1560</v>
+        <v>1928</v>
       </c>
       <c r="N4" s="0">
         <v>8</v>
       </c>
       <c r="O4" s="0" t="s">
-        <v>1561</v>
+        <v>1929</v>
       </c>
       <c r="P4" s="0">
-        <v>60</v>
+        <v>45</v>
       </c>
       <c r="Q4" s="0" t="s">
-        <v>1562</v>
+        <v>1930</v>
       </c>
       <c r="R4" s="0" t="s">
-        <v>1563</v>
+        <v>1931</v>
       </c>
       <c r="S4" s="0" t="s">
-        <v>1564</v>
+        <v>1932</v>
       </c>
       <c r="T4" s="0"/>
       <c r="U4" s="0"/>
       <c r="V4" s="0" t="s">
-        <v>1565</v>
+        <v>1933</v>
       </c>
     </row>
     <row r="5">
@@ -8128,68 +9757,69 @@
       </c>
     </row>
     <row r="46">
-      <c r="A46" t="s">
-        <v>755</v>
-      </c>
-      <c r="B46" t="s">
-        <v>756</v>
-      </c>
-      <c r="C46" t="s">
-        <v>757</v>
-      </c>
-      <c r="D46" t="s">
-        <v>758</v>
-      </c>
-      <c r="E46" t="s">
-        <v>759</v>
-      </c>
-      <c r="F46">
+      <c r="A46" s="0" t="s">
+        <v>1881</v>
+      </c>
+      <c r="B46" s="0" t="s">
+        <v>1882</v>
+      </c>
+      <c r="C46" s="0" t="s">
+        <v>1883</v>
+      </c>
+      <c r="D46" s="0" t="s">
+        <v>1884</v>
+      </c>
+      <c r="E46" s="0" t="s">
+        <v>1885</v>
+      </c>
+      <c r="F46" s="0">
         <v>4</v>
       </c>
-      <c r="G46" t="s">
-        <v>760</v>
-      </c>
-      <c r="H46" t="s">
-        <v>761</v>
-      </c>
-      <c r="I46" t="s">
-        <v>762</v>
-      </c>
-      <c r="J46" t="s">
-        <v>763</v>
-      </c>
-      <c r="K46" t="s">
-        <v>764</v>
-      </c>
-      <c r="L46" t="s">
-        <v>765</v>
-      </c>
-      <c r="M46" t="s">
-        <v>766</v>
-      </c>
-      <c r="N46">
+      <c r="G46" s="0" t="s">
+        <v>1886</v>
+      </c>
+      <c r="H46" s="0" t="s">
+        <v>1887</v>
+      </c>
+      <c r="I46" s="0" t="s">
+        <v>1888</v>
+      </c>
+      <c r="J46" s="0" t="s">
+        <v>1889</v>
+      </c>
+      <c r="K46" s="0" t="s">
+        <v>1890</v>
+      </c>
+      <c r="L46" s="0" t="s">
+        <v>1891</v>
+      </c>
+      <c r="M46" s="0" t="s">
+        <v>1892</v>
+      </c>
+      <c r="N46" s="0">
         <v>2</v>
       </c>
-      <c r="O46" t="s">
-        <v>767</v>
-      </c>
-      <c r="P46">
-        <v>0.2</v>
-      </c>
-      <c r="Q46" t="s">
-        <v>19</v>
-      </c>
-      <c r="R46" t="s">
-        <v>768</v>
-      </c>
-      <c r="S46" t="s">
-        <v>769</v>
-      </c>
-      <c r="U46" t="s">
-        <v>980</v>
-      </c>
-      <c r="V46" t="s">
-        <v>1120</v>
+      <c r="O46" s="0" t="s">
+        <v>1893</v>
+      </c>
+      <c r="P46" s="0">
+        <v>0.20000000000000001</v>
+      </c>
+      <c r="Q46" s="0" t="s">
+        <v>1894</v>
+      </c>
+      <c r="R46" s="0" t="s">
+        <v>1895</v>
+      </c>
+      <c r="S46" s="0" t="s">
+        <v>1896</v>
+      </c>
+      <c r="T46" s="0"/>
+      <c r="U46" s="0" t="s">
+        <v>1897</v>
+      </c>
+      <c r="V46" s="0" t="s">
+        <v>1898</v>
       </c>
     </row>
     <row r="47">
@@ -8258,62 +9888,67 @@
       </c>
     </row>
     <row r="48">
-      <c r="A48" t="s">
-        <v>336</v>
-      </c>
-      <c r="B48" t="s">
-        <v>337</v>
-      </c>
-      <c r="C48" t="s">
-        <v>338</v>
-      </c>
-      <c r="D48" t="s">
-        <v>339</v>
-      </c>
-      <c r="E48" t="s">
-        <v>340</v>
-      </c>
-      <c r="F48">
+      <c r="A48" s="0" t="s">
+        <v>1669</v>
+      </c>
+      <c r="B48" s="0" t="s">
+        <v>1670</v>
+      </c>
+      <c r="C48" s="0" t="s">
+        <v>1671</v>
+      </c>
+      <c r="D48" s="0" t="s">
+        <v>1672</v>
+      </c>
+      <c r="E48" s="0" t="s">
+        <v>1673</v>
+      </c>
+      <c r="F48" s="0">
         <v>4</v>
       </c>
-      <c r="G48" t="s">
-        <v>341</v>
-      </c>
-      <c r="H48" t="s">
-        <v>342</v>
-      </c>
-      <c r="I48" t="s">
-        <v>343</v>
-      </c>
-      <c r="K48" t="s">
-        <v>344</v>
-      </c>
-      <c r="L48" t="s">
-        <v>580</v>
-      </c>
-      <c r="M48" t="s">
-        <v>345</v>
-      </c>
-      <c r="N48">
+      <c r="G48" s="0" t="s">
+        <v>1674</v>
+      </c>
+      <c r="H48" s="0" t="s">
+        <v>1675</v>
+      </c>
+      <c r="I48" s="0" t="s">
+        <v>1676</v>
+      </c>
+      <c r="J48" s="0"/>
+      <c r="K48" s="0" t="s">
+        <v>1677</v>
+      </c>
+      <c r="L48" s="0" t="s">
+        <v>1678</v>
+      </c>
+      <c r="M48" s="0" t="s">
+        <v>1679</v>
+      </c>
+      <c r="N48" s="0">
         <v>1</v>
       </c>
-      <c r="O48" t="s">
-        <v>346</v>
-      </c>
-      <c r="P48">
-        <v>0.2</v>
-      </c>
-      <c r="Q48" t="s">
-        <v>19</v>
-      </c>
-      <c r="R48" t="s">
-        <v>347</v>
-      </c>
-      <c r="S48" t="s">
-        <v>421</v>
-      </c>
-      <c r="V48" t="s">
-        <v>1120</v>
+      <c r="O48" s="0" t="s">
+        <v>1680</v>
+      </c>
+      <c r="P48" s="0">
+        <v>0.20000000000000001</v>
+      </c>
+      <c r="Q48" s="0" t="s">
+        <v>1681</v>
+      </c>
+      <c r="R48" s="0" t="s">
+        <v>1682</v>
+      </c>
+      <c r="S48" s="0" t="s">
+        <v>1683</v>
+      </c>
+      <c r="T48" s="0"/>
+      <c r="U48" s="0" t="s">
+        <v>1684</v>
+      </c>
+      <c r="V48" s="0" t="s">
+        <v>1685</v>
       </c>
     </row>
     <row r="49">
@@ -8741,189 +10376,198 @@
     </row>
     <row r="56">
       <c r="A56" s="0" t="s">
-        <v>1335</v>
+        <v>1985</v>
       </c>
       <c r="B56" s="0" t="s">
-        <v>1336</v>
+        <v>1986</v>
       </c>
       <c r="C56" s="0" t="s">
-        <v>1337</v>
+        <v>1987</v>
       </c>
       <c r="D56" s="0" t="s">
-        <v>1338</v>
+        <v>1988</v>
       </c>
       <c r="E56" s="0" t="s">
-        <v>1339</v>
+        <v>1989</v>
       </c>
       <c r="F56" s="0">
         <v>4</v>
       </c>
       <c r="G56" s="0" t="s">
-        <v>1340</v>
+        <v>1990</v>
       </c>
       <c r="H56" s="0" t="s">
-        <v>1341</v>
+        <v>1991</v>
       </c>
       <c r="I56" s="0" t="s">
-        <v>1342</v>
+        <v>1992</v>
       </c>
       <c r="J56" s="0" t="s">
-        <v>1343</v>
+        <v>1993</v>
       </c>
       <c r="K56" s="0" t="s">
-        <v>1344</v>
+        <v>1994</v>
       </c>
       <c r="L56" s="0" t="s">
-        <v>1345</v>
+        <v>1995</v>
       </c>
       <c r="M56" s="0" t="s">
-        <v>1346</v>
+        <v>1996</v>
       </c>
       <c r="N56" s="0">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="O56" s="0" t="s">
-        <v>1347</v>
+        <v>1997</v>
       </c>
       <c r="P56" s="0">
         <v>1</v>
       </c>
       <c r="Q56" s="0" t="s">
-        <v>1348</v>
+        <v>1998</v>
       </c>
       <c r="R56" s="0" t="s">
-        <v>1349</v>
+        <v>1999</v>
       </c>
       <c r="S56" s="0" t="s">
-        <v>1350</v>
+        <v>2000</v>
       </c>
       <c r="T56" s="0"/>
       <c r="U56" s="0"/>
       <c r="V56" s="0" t="s">
-        <v>1351</v>
+        <v>2001</v>
       </c>
     </row>
     <row r="57">
-      <c r="A57" t="s">
-        <v>348</v>
-      </c>
-      <c r="B57" t="s">
-        <v>349</v>
-      </c>
-      <c r="C57" t="s">
-        <v>350</v>
-      </c>
-      <c r="D57" t="s">
-        <v>351</v>
-      </c>
-      <c r="E57" t="s">
-        <v>352</v>
-      </c>
-      <c r="F57">
+      <c r="A57" s="0" t="s">
+        <v>2194</v>
+      </c>
+      <c r="B57" s="0" t="s">
+        <v>2195</v>
+      </c>
+      <c r="C57" s="0" t="s">
+        <v>2196</v>
+      </c>
+      <c r="D57" s="0" t="s">
+        <v>2197</v>
+      </c>
+      <c r="E57" s="0" t="s">
+        <v>2198</v>
+      </c>
+      <c r="F57" s="0">
         <v>4</v>
       </c>
-      <c r="G57" t="s">
-        <v>353</v>
-      </c>
-      <c r="H57" t="s">
-        <v>354</v>
-      </c>
-      <c r="I57" t="s">
-        <v>355</v>
-      </c>
-      <c r="K57" t="s">
-        <v>356</v>
-      </c>
-      <c r="L57" t="s">
-        <v>580</v>
-      </c>
-      <c r="M57" t="s">
-        <v>357</v>
-      </c>
-      <c r="N57">
-        <v>8</v>
-      </c>
-      <c r="O57" t="s">
-        <v>358</v>
-      </c>
-      <c r="P57">
+      <c r="G57" s="0" t="s">
+        <v>2199</v>
+      </c>
+      <c r="H57" s="0" t="s">
+        <v>2200</v>
+      </c>
+      <c r="I57" s="0" t="s">
+        <v>2201</v>
+      </c>
+      <c r="J57" s="0" t="s">
+        <v>2202</v>
+      </c>
+      <c r="K57" s="0" t="s">
+        <v>2203</v>
+      </c>
+      <c r="L57" s="0" t="s">
+        <v>2204</v>
+      </c>
+      <c r="M57" s="0" t="s">
+        <v>2205</v>
+      </c>
+      <c r="N57" s="0">
+        <v>4</v>
+      </c>
+      <c r="O57" s="0" t="s">
+        <v>2206</v>
+      </c>
+      <c r="P57" s="0">
         <v>1</v>
       </c>
-      <c r="Q57" t="s">
-        <v>19</v>
-      </c>
-      <c r="R57" t="s">
-        <v>359</v>
-      </c>
-      <c r="S57" t="s">
-        <v>421</v>
-      </c>
-      <c r="V57" t="s">
-        <v>1120</v>
+      <c r="Q57" s="0" t="s">
+        <v>2207</v>
+      </c>
+      <c r="R57" s="0" t="s">
+        <v>2208</v>
+      </c>
+      <c r="S57" s="0" t="s">
+        <v>2209</v>
+      </c>
+      <c r="T57" s="0"/>
+      <c r="U57" s="0" t="s">
+        <v>2210</v>
+      </c>
+      <c r="V57" s="0" t="s">
+        <v>2211</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="0" t="s">
-        <v>1601</v>
+        <v>1899</v>
       </c>
       <c r="B58" s="0" t="s">
-        <v>1602</v>
+        <v>1900</v>
       </c>
       <c r="C58" s="0" t="s">
-        <v>1603</v>
+        <v>1901</v>
       </c>
       <c r="D58" s="0" t="s">
-        <v>1604</v>
+        <v>1902</v>
       </c>
       <c r="E58" s="0" t="s">
-        <v>1605</v>
+        <v>1903</v>
       </c>
       <c r="F58" s="0">
         <v>4</v>
       </c>
       <c r="G58" s="0" t="s">
-        <v>1606</v>
+        <v>1904</v>
       </c>
       <c r="H58" s="0" t="s">
-        <v>1607</v>
+        <v>1905</v>
       </c>
       <c r="I58" s="0" t="s">
-        <v>1608</v>
-      </c>
-      <c r="J58" s="0"/>
+        <v>1906</v>
+      </c>
+      <c r="J58" s="0" t="s">
+        <v>1907</v>
+      </c>
       <c r="K58" s="0" t="s">
-        <v>1609</v>
+        <v>1908</v>
       </c>
       <c r="L58" s="0" t="s">
-        <v>1610</v>
+        <v>1909</v>
       </c>
       <c r="M58" s="0" t="s">
-        <v>1611</v>
+        <v>1910</v>
       </c>
       <c r="N58" s="0">
         <v>2</v>
       </c>
       <c r="O58" s="0" t="s">
-        <v>1612</v>
+        <v>1911</v>
       </c>
       <c r="P58" s="0">
         <v>0.20000000000000001</v>
       </c>
       <c r="Q58" s="0" t="s">
-        <v>1613</v>
+        <v>1912</v>
       </c>
       <c r="R58" s="0" t="s">
-        <v>1614</v>
+        <v>1913</v>
       </c>
       <c r="S58" s="0" t="s">
-        <v>1615</v>
+        <v>1914</v>
       </c>
       <c r="T58" s="0"/>
       <c r="U58" s="0" t="s">
-        <v>1616</v>
+        <v>1915</v>
       </c>
       <c r="V58" s="0" t="s">
-        <v>1617</v>
+        <v>1916</v>
       </c>
     </row>
     <row r="59">
@@ -10804,6 +12448,398 @@
       </c>
       <c r="V89" s="0" t="s">
         <v>1668</v>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" s="0" t="s">
+        <v>1703</v>
+      </c>
+      <c r="B90" s="0" t="s">
+        <v>1704</v>
+      </c>
+      <c r="C90" s="0" t="s">
+        <v>1705</v>
+      </c>
+      <c r="D90" s="0" t="s">
+        <v>1706</v>
+      </c>
+      <c r="E90" s="0" t="s">
+        <v>1707</v>
+      </c>
+      <c r="F90" s="0">
+        <v>4</v>
+      </c>
+      <c r="G90" s="0" t="s">
+        <v>1708</v>
+      </c>
+      <c r="H90" s="0" t="s">
+        <v>1709</v>
+      </c>
+      <c r="I90" s="0" t="s">
+        <v>1710</v>
+      </c>
+      <c r="J90" s="0" t="s">
+        <v>1711</v>
+      </c>
+      <c r="K90" s="0" t="s">
+        <v>1712</v>
+      </c>
+      <c r="L90" s="0" t="s">
+        <v>1713</v>
+      </c>
+      <c r="M90" s="0" t="s">
+        <v>1714</v>
+      </c>
+      <c r="N90" s="0">
+        <v>2</v>
+      </c>
+      <c r="O90" s="0" t="s">
+        <v>1715</v>
+      </c>
+      <c r="P90" s="0">
+        <v>0.20000000000000001</v>
+      </c>
+      <c r="Q90" s="0" t="s">
+        <v>1716</v>
+      </c>
+      <c r="R90" s="0" t="s">
+        <v>1717</v>
+      </c>
+      <c r="S90" s="0" t="s">
+        <v>1718</v>
+      </c>
+      <c r="T90" s="0"/>
+      <c r="U90" s="0" t="s">
+        <v>1719</v>
+      </c>
+      <c r="V90" s="0" t="s">
+        <v>1720</v>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" s="0" t="s">
+        <v>1809</v>
+      </c>
+      <c r="B91" s="0" t="s">
+        <v>1810</v>
+      </c>
+      <c r="C91" s="0" t="s">
+        <v>1811</v>
+      </c>
+      <c r="D91" s="0" t="s">
+        <v>1812</v>
+      </c>
+      <c r="E91" s="0" t="s">
+        <v>1813</v>
+      </c>
+      <c r="F91" s="0">
+        <v>4</v>
+      </c>
+      <c r="G91" s="0" t="s">
+        <v>1814</v>
+      </c>
+      <c r="H91" s="0" t="s">
+        <v>1815</v>
+      </c>
+      <c r="I91" s="0" t="s">
+        <v>1816</v>
+      </c>
+      <c r="J91" s="0" t="s">
+        <v>1817</v>
+      </c>
+      <c r="K91" s="0" t="s">
+        <v>1818</v>
+      </c>
+      <c r="L91" s="0" t="s">
+        <v>1819</v>
+      </c>
+      <c r="M91" s="0" t="s">
+        <v>1820</v>
+      </c>
+      <c r="N91" s="0">
+        <v>8</v>
+      </c>
+      <c r="O91" s="0" t="s">
+        <v>1821</v>
+      </c>
+      <c r="P91" s="0">
+        <v>0.29999999999999999</v>
+      </c>
+      <c r="Q91" s="0" t="s">
+        <v>1822</v>
+      </c>
+      <c r="R91" s="0" t="s">
+        <v>1823</v>
+      </c>
+      <c r="S91" s="0" t="s">
+        <v>1824</v>
+      </c>
+      <c r="T91" s="0"/>
+      <c r="U91" s="0" t="s">
+        <v>1825</v>
+      </c>
+      <c r="V91" s="0" t="s">
+        <v>1826</v>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" s="0" t="s">
+        <v>1845</v>
+      </c>
+      <c r="B92" s="0" t="s">
+        <v>1846</v>
+      </c>
+      <c r="C92" s="0" t="s">
+        <v>1847</v>
+      </c>
+      <c r="D92" s="0" t="s">
+        <v>1848</v>
+      </c>
+      <c r="E92" s="0" t="s">
+        <v>1849</v>
+      </c>
+      <c r="F92" s="0">
+        <v>4</v>
+      </c>
+      <c r="G92" s="0" t="s">
+        <v>1850</v>
+      </c>
+      <c r="H92" s="0" t="s">
+        <v>1851</v>
+      </c>
+      <c r="I92" s="0" t="s">
+        <v>1852</v>
+      </c>
+      <c r="J92" s="0" t="s">
+        <v>1853</v>
+      </c>
+      <c r="K92" s="0" t="s">
+        <v>1854</v>
+      </c>
+      <c r="L92" s="0" t="s">
+        <v>1855</v>
+      </c>
+      <c r="M92" s="0" t="s">
+        <v>1856</v>
+      </c>
+      <c r="N92" s="0">
+        <v>8</v>
+      </c>
+      <c r="O92" s="0" t="s">
+        <v>1857</v>
+      </c>
+      <c r="P92" s="0">
+        <v>0.29999999999999999</v>
+      </c>
+      <c r="Q92" s="0" t="s">
+        <v>1858</v>
+      </c>
+      <c r="R92" s="0" t="s">
+        <v>1859</v>
+      </c>
+      <c r="S92" s="0" t="s">
+        <v>1860</v>
+      </c>
+      <c r="T92" s="0"/>
+      <c r="U92" s="0" t="s">
+        <v>1861</v>
+      </c>
+      <c r="V92" s="0" t="s">
+        <v>1862</v>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" s="0" t="s">
+        <v>2072</v>
+      </c>
+      <c r="B93" s="0" t="s">
+        <v>2073</v>
+      </c>
+      <c r="C93" s="0" t="s">
+        <v>2074</v>
+      </c>
+      <c r="D93" s="0" t="s">
+        <v>2075</v>
+      </c>
+      <c r="E93" s="0" t="s">
+        <v>2076</v>
+      </c>
+      <c r="F93" s="0">
+        <v>4</v>
+      </c>
+      <c r="G93" s="0" t="s">
+        <v>2077</v>
+      </c>
+      <c r="H93" s="0" t="s">
+        <v>2078</v>
+      </c>
+      <c r="I93" s="0" t="s">
+        <v>2079</v>
+      </c>
+      <c r="J93" s="0" t="s">
+        <v>2080</v>
+      </c>
+      <c r="K93" s="0" t="s">
+        <v>2081</v>
+      </c>
+      <c r="L93" s="0" t="s">
+        <v>2082</v>
+      </c>
+      <c r="M93" s="0" t="s">
+        <v>2083</v>
+      </c>
+      <c r="N93" s="0">
+        <v>2</v>
+      </c>
+      <c r="O93" s="0" t="s">
+        <v>2084</v>
+      </c>
+      <c r="P93" s="0">
+        <v>1</v>
+      </c>
+      <c r="Q93" s="0" t="s">
+        <v>2085</v>
+      </c>
+      <c r="R93" s="0" t="s">
+        <v>2086</v>
+      </c>
+      <c r="S93" s="0" t="s">
+        <v>2087</v>
+      </c>
+      <c r="T93" s="0"/>
+      <c r="U93" s="0"/>
+      <c r="V93" s="0" t="s">
+        <v>2088</v>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" s="0" t="s">
+        <v>2177</v>
+      </c>
+      <c r="B94" s="0" t="s">
+        <v>2178</v>
+      </c>
+      <c r="C94" s="0" t="s">
+        <v>2179</v>
+      </c>
+      <c r="D94" s="0" t="s">
+        <v>2180</v>
+      </c>
+      <c r="E94" s="0" t="s">
+        <v>2181</v>
+      </c>
+      <c r="F94" s="0">
+        <v>4</v>
+      </c>
+      <c r="G94" s="0" t="s">
+        <v>2182</v>
+      </c>
+      <c r="H94" s="0" t="s">
+        <v>2183</v>
+      </c>
+      <c r="I94" s="0" t="s">
+        <v>2184</v>
+      </c>
+      <c r="J94" s="0" t="s">
+        <v>2185</v>
+      </c>
+      <c r="K94" s="0" t="s">
+        <v>2186</v>
+      </c>
+      <c r="L94" s="0" t="s">
+        <v>2187</v>
+      </c>
+      <c r="M94" s="0" t="s">
+        <v>2188</v>
+      </c>
+      <c r="N94" s="0">
+        <v>2</v>
+      </c>
+      <c r="O94" s="0" t="s">
+        <v>2189</v>
+      </c>
+      <c r="P94" s="0">
+        <v>1</v>
+      </c>
+      <c r="Q94" s="0" t="s">
+        <v>2190</v>
+      </c>
+      <c r="R94" s="0" t="s">
+        <v>2191</v>
+      </c>
+      <c r="S94" s="0" t="s">
+        <v>2192</v>
+      </c>
+      <c r="T94" s="0"/>
+      <c r="U94" s="0"/>
+      <c r="V94" s="0" t="s">
+        <v>2193</v>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" s="0" t="s">
+        <v>2159</v>
+      </c>
+      <c r="B95" s="0" t="s">
+        <v>2160</v>
+      </c>
+      <c r="C95" s="0" t="s">
+        <v>2161</v>
+      </c>
+      <c r="D95" s="0" t="s">
+        <v>2162</v>
+      </c>
+      <c r="E95" s="0" t="s">
+        <v>2163</v>
+      </c>
+      <c r="F95" s="0">
+        <v>4</v>
+      </c>
+      <c r="G95" s="0" t="s">
+        <v>2164</v>
+      </c>
+      <c r="H95" s="0" t="s">
+        <v>2165</v>
+      </c>
+      <c r="I95" s="0" t="s">
+        <v>2166</v>
+      </c>
+      <c r="J95" s="0" t="s">
+        <v>2167</v>
+      </c>
+      <c r="K95" s="0" t="s">
+        <v>2168</v>
+      </c>
+      <c r="L95" s="0" t="s">
+        <v>2169</v>
+      </c>
+      <c r="M95" s="0" t="s">
+        <v>2170</v>
+      </c>
+      <c r="N95" s="0">
+        <v>4</v>
+      </c>
+      <c r="O95" s="0" t="s">
+        <v>2171</v>
+      </c>
+      <c r="P95" s="0">
+        <v>1</v>
+      </c>
+      <c r="Q95" s="0" t="s">
+        <v>2172</v>
+      </c>
+      <c r="R95" s="0" t="s">
+        <v>2173</v>
+      </c>
+      <c r="S95" s="0" t="s">
+        <v>2174</v>
+      </c>
+      <c r="T95" s="0"/>
+      <c r="U95" s="0" t="s">
+        <v>2175</v>
+      </c>
+      <c r="V95" s="0" t="s">
+        <v>2176</v>
       </c>
     </row>
   </sheetData>

--- a/config/becExpConfig/becExpType.csv.xlsx
+++ b/config/becExpConfig/becExpType.csv.xlsx
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2479" uniqueCount="2212">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2639" uniqueCount="2372">
   <si>
     <t>TrialName</t>
   </si>
@@ -6663,6 +6663,486 @@
   </si>
   <si>
     <t>WaveformGeneratorName,XvWingMod;ChannelName,Ch1;WaveformListName,XvWingLattice</t>
+  </si>
+  <si>
+    <t>PhaseLockName,ImagingLock;Frequency,700000000;VariableName,hw_ImagingNi</t>
+  </si>
+  <si>
+    <t>NiLatticePdFullBoModDepth</t>
+  </si>
+  <si>
+    <t>An experiment at the non-interacting lattice stage. Scan PD modulation depth.</t>
+  </si>
+  <si>
+    <t>TOP</t>
+  </si>
+  <si>
+    <t>BMPDLoopFullBoTof8000</t>
+  </si>
+  <si>
+    <t>None</t>
+  </si>
+  <si>
+    <t>hw_PdModDepth2</t>
+  </si>
+  <si>
+    <t>DensityFit;AtomNumber</t>
+  </si>
+  <si>
+    <t>LSR</t>
+  </si>
+  <si>
+    <t>[405 1189;681 1173;1573 1141;1664 1288;1578 1335;814 1380;432 1392;357 1309]</t>
+  </si>
+  <si>
+    <t>HF</t>
+  </si>
+  <si>
+    <t>Absorption</t>
+  </si>
+  <si>
+    <t>StrongLight</t>
+  </si>
+  <si>
+    <t>BosonicGaussianFit1D</t>
+  </si>
+  <si>
+    <t>None</t>
+  </si>
+  <si>
+    <t>LinearFit1D</t>
+  </si>
+  <si>
+    <t>StdErr</t>
+  </si>
+  <si>
+    <t>PhaseLockName,ImagingLock;Frequency,700000000;VariableName,hw_ImagingNi</t>
+  </si>
+  <si>
+    <t>NiLatticeFullBoXvLatticeBm</t>
+  </si>
+  <si>
+    <t>An experiment at the non-interacting lattice stage. Scan xvlattice. With band mapping.</t>
+  </si>
+  <si>
+    <t>TOP</t>
+  </si>
+  <si>
+    <t>BMPDLoopFullBoTof8000</t>
+  </si>
+  <si>
+    <t>None</t>
+  </si>
+  <si>
+    <t>hw_XvLattice</t>
+  </si>
+  <si>
+    <t>DensityFit;AtomNumber</t>
+  </si>
+  <si>
+    <t>LSR</t>
+  </si>
+  <si>
+    <t>[353 1231;517 1162;1370 1128;1605 1136;1657 1227;1628 1333;1262 1362;668 1384;385 1392;364 1330]</t>
+  </si>
+  <si>
+    <t>HF</t>
+  </si>
+  <si>
+    <t>Absorption</t>
+  </si>
+  <si>
+    <t>StrongLight</t>
+  </si>
+  <si>
+    <t>BosonicGaussianFit1D</t>
+  </si>
+  <si>
+    <t>None</t>
+  </si>
+  <si>
+    <t>LinearFit1D</t>
+  </si>
+  <si>
+    <t>StdErr</t>
+  </si>
+  <si>
+    <t>WaveformGeneratorName,LatticeMod,XvWingMod;ChannelName,Ch2,Ch1;WaveformListName,PdAiPulseFullBo,XvWingLattice</t>
+  </si>
+  <si>
+    <t>PhaseLockName,ImagingLock;Frequency,700000000;VariableName,hw_ImagingNi</t>
+  </si>
+  <si>
+    <t>NiLatticeBo</t>
+  </si>
+  <si>
+    <t>A Bloch oscillation experiment at the non-interacting lattice stage.</t>
+  </si>
+  <si>
+    <t>TOP</t>
+  </si>
+  <si>
+    <t>NiLattice</t>
+  </si>
+  <si>
+    <t>latticehold</t>
+  </si>
+  <si>
+    <t>DensityFit;AtomNumber;CenterFit</t>
+  </si>
+  <si>
+    <t>LSR</t>
+  </si>
+  <si>
+    <t>[733 1252;785 1212;1295 1183;1326 1218;1334 1293;1127 1322;743 1328;743 1328;734 1299]</t>
+  </si>
+  <si>
+    <t>HF</t>
+  </si>
+  <si>
+    <t>Absorption</t>
+  </si>
+  <si>
+    <t>StrongLight</t>
+  </si>
+  <si>
+    <t>BosonicGaussianFit1D</t>
+  </si>
+  <si>
+    <t>None</t>
+  </si>
+  <si>
+    <t>SineFit1D</t>
+  </si>
+  <si>
+    <t>StdErr</t>
+  </si>
+  <si>
+    <t>WaveformGeneratorName,XvWingMod;ChannelName,Ch1;WaveformListName,XvWingLattice</t>
+  </si>
+  <si>
+    <t>PhaseLockName,ImagingLock;Frequency,700000000;VariableName,hw_ImagingNi</t>
+  </si>
+  <si>
+    <t>NiBecFeshbachField3</t>
+  </si>
+  <si>
+    <t>An experiment at the non-interacting BEC stage.</t>
+  </si>
+  <si>
+    <t>TOP</t>
+  </si>
+  <si>
+    <t>Bec</t>
+  </si>
+  <si>
+    <t>None</t>
+  </si>
+  <si>
+    <t>RunIndex</t>
+  </si>
+  <si>
+    <t>DensityFit;AtomNumber;CenterFit</t>
+  </si>
+  <si>
+    <t>LSR</t>
+  </si>
+  <si>
+    <t>[822 1197;891 1124;967 1135;1062 1182;1073 1305;1048 1369;985 1397;905 1407;829 1336]</t>
+  </si>
+  <si>
+    <t>NI</t>
+  </si>
+  <si>
+    <t>Absorption</t>
+  </si>
+  <si>
+    <t>StrongLight</t>
+  </si>
+  <si>
+    <t>BosonicGaussianFit1D</t>
+  </si>
+  <si>
+    <t>None</t>
+  </si>
+  <si>
+    <t>ParabolicFit1D</t>
+  </si>
+  <si>
+    <t>StdErr</t>
+  </si>
+  <si>
+    <t>WaveformGeneratorName,XvWingMod;ChannelName,Ch1;WaveformListName,XvWingNi</t>
+  </si>
+  <si>
+    <t>PhaseLockName,ImagingLock;Frequency,700000000;VariableName,hw_ImagingNi</t>
+  </si>
+  <si>
+    <t>NiBecFeshbachField3</t>
+  </si>
+  <si>
+    <t>An experiment at the non-interacting BEC stage.</t>
+  </si>
+  <si>
+    <t>TOP</t>
+  </si>
+  <si>
+    <t>Bec</t>
+  </si>
+  <si>
+    <t>None</t>
+  </si>
+  <si>
+    <t>FeshbachField3</t>
+  </si>
+  <si>
+    <t>DensityFit;AtomNumber;CenterFit</t>
+  </si>
+  <si>
+    <t>LSR</t>
+  </si>
+  <si>
+    <t>[822 1197;891 1124;967 1135;1062 1182;1073 1305;1048 1369;985 1397;905 1407;829 1336]</t>
+  </si>
+  <si>
+    <t>NI</t>
+  </si>
+  <si>
+    <t>Absorption</t>
+  </si>
+  <si>
+    <t>StrongLight</t>
+  </si>
+  <si>
+    <t>BosonicGaussianFit1D</t>
+  </si>
+  <si>
+    <t>None</t>
+  </si>
+  <si>
+    <t>ParabolicFit1D</t>
+  </si>
+  <si>
+    <t>StdErr</t>
+  </si>
+  <si>
+    <t>WaveformGeneratorName,XvWingMod;ChannelName,Ch1;WaveformListName,XvWingNi</t>
+  </si>
+  <si>
+    <t>PhaseLockName,ImagingLock;Frequency,700000000;VariableName,hw_ImagingNi</t>
+  </si>
+  <si>
+    <t>NiBecCC</t>
+  </si>
+  <si>
+    <t>An experiment at the non-interacting BEC stage.</t>
+  </si>
+  <si>
+    <t>TOP</t>
+  </si>
+  <si>
+    <t>Bec</t>
+  </si>
+  <si>
+    <t>None</t>
+  </si>
+  <si>
+    <t>RunIndex</t>
+  </si>
+  <si>
+    <t>DensityFit;AtomNumber;CenterFit</t>
+  </si>
+  <si>
+    <t>LSR</t>
+  </si>
+  <si>
+    <t>[822 1197;891 1124;967 1135;1062 1182;1073 1305;1048 1369;985 1397;905 1407;829 1336]</t>
+  </si>
+  <si>
+    <t>NI</t>
+  </si>
+  <si>
+    <t>Absorption</t>
+  </si>
+  <si>
+    <t>StrongLight</t>
+  </si>
+  <si>
+    <t>BosonicGaussianFit1D</t>
+  </si>
+  <si>
+    <t>None</t>
+  </si>
+  <si>
+    <t>ParabolicFit1D</t>
+  </si>
+  <si>
+    <t>StdErr</t>
+  </si>
+  <si>
+    <t>WaveformGeneratorName,XvWingMod;ChannelName,Ch1;WaveformListName,XvWingNi</t>
+  </si>
+  <si>
+    <t>PhaseLockName,ImagingLock;Frequency,700000000;VariableName,hw_ImagingNi</t>
+  </si>
+  <si>
+    <t>NiBecCC</t>
+  </si>
+  <si>
+    <t>An experiment at the non-interacting BEC stage.</t>
+  </si>
+  <si>
+    <t>TOP</t>
+  </si>
+  <si>
+    <t>Bec</t>
+  </si>
+  <si>
+    <t>None</t>
+  </si>
+  <si>
+    <t>RunIndex</t>
+  </si>
+  <si>
+    <t>DensityFit;AtomNumber;CenterFit</t>
+  </si>
+  <si>
+    <t>LSR</t>
+  </si>
+  <si>
+    <t>[822 1197;891 1124;967 1135;1062 1182;1073 1305;1048 1369;985 1397;905 1407;829 1336]</t>
+  </si>
+  <si>
+    <t>NI</t>
+  </si>
+  <si>
+    <t>Absorption</t>
+  </si>
+  <si>
+    <t>StrongLight</t>
+  </si>
+  <si>
+    <t>BosonicGaussianFit1D</t>
+  </si>
+  <si>
+    <t>None</t>
+  </si>
+  <si>
+    <t>ParabolicFit1D</t>
+  </si>
+  <si>
+    <t>StdErr</t>
+  </si>
+  <si>
+    <t>WaveformGeneratorName,XvWingMod;ChannelName,Ch1;WaveformListName,XvWingNiCC</t>
+  </si>
+  <si>
+    <t>PhaseLockName,ImagingLock;Frequency,700000000;VariableName,hw_ImagingNi</t>
+  </si>
+  <si>
+    <t>NiLatticeCCBoBm</t>
+  </si>
+  <si>
+    <t>A Bloch oscillation experiment at the non-interacting lattice stage. With band mapping.</t>
+  </si>
+  <si>
+    <t>TOP</t>
+  </si>
+  <si>
+    <t>NiLatticeBoBmTof8000</t>
+  </si>
+  <si>
+    <t>None</t>
+  </si>
+  <si>
+    <t>latticehold</t>
+  </si>
+  <si>
+    <t>DensityFit;AtomNumber;CenterFit</t>
+  </si>
+  <si>
+    <t>LSR</t>
+  </si>
+  <si>
+    <t>[790 1235;871 1209;1275 1193;1400 1215;1404 1288;1311 1320;928 1334;800 1309]</t>
+  </si>
+  <si>
+    <t>HF</t>
+  </si>
+  <si>
+    <t>Absorption</t>
+  </si>
+  <si>
+    <t>StrongLight</t>
+  </si>
+  <si>
+    <t>BosonicGaussianFit1D</t>
+  </si>
+  <si>
+    <t>None</t>
+  </si>
+  <si>
+    <t>TriangleFit1D</t>
+  </si>
+  <si>
+    <t>StdErr</t>
+  </si>
+  <si>
+    <t>WaveformGeneratorName,XvWingMod;ChannelName,Ch1;WaveformListName,XvWingLattice</t>
+  </si>
+  <si>
+    <t>PhaseLockName,ImagingLock;Frequency,700000000;VariableName,hw_ImagingNi</t>
+  </si>
+  <si>
+    <t>NiLatticeCCBoBm</t>
+  </si>
+  <si>
+    <t>A Bloch oscillation experiment at the non-interacting lattice stage. With band mapping.</t>
+  </si>
+  <si>
+    <t>TOP</t>
+  </si>
+  <si>
+    <t>NiLatticeBoBmTof8000</t>
+  </si>
+  <si>
+    <t>None</t>
+  </si>
+  <si>
+    <t>latticehold</t>
+  </si>
+  <si>
+    <t>DensityFit;AtomNumber;CenterFit</t>
+  </si>
+  <si>
+    <t>LSR</t>
+  </si>
+  <si>
+    <t>[790 1235;871 1209;1275 1193;1400 1215;1404 1288;1311 1320;928 1334;800 1309]</t>
+  </si>
+  <si>
+    <t>HF</t>
+  </si>
+  <si>
+    <t>Absorption</t>
+  </si>
+  <si>
+    <t>StrongLight</t>
+  </si>
+  <si>
+    <t>BosonicGaussianFit1D</t>
+  </si>
+  <si>
+    <t>None</t>
+  </si>
+  <si>
+    <t>TriangleFit1D</t>
+  </si>
+  <si>
+    <t>StdErr</t>
+  </si>
+  <si>
+    <t>WaveformGeneratorName,XvWingMod;ChannelName,Ch1;WaveformListName,XvWingLatticeCC</t>
   </si>
   <si>
     <t>PhaseLockName,ImagingLock;Frequency,700000000;VariableName,hw_ImagingNi</t>
@@ -6992,7 +7472,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:V95"/>
+  <dimension ref="A1:V98"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="36.42578125" customWidth="true"/>
@@ -9695,65 +10175,67 @@
       </c>
     </row>
     <row r="45">
-      <c r="A45" t="s">
-        <v>698</v>
-      </c>
-      <c r="B45" t="s">
-        <v>699</v>
-      </c>
-      <c r="C45" t="s">
-        <v>700</v>
-      </c>
-      <c r="D45" t="s">
-        <v>701</v>
-      </c>
-      <c r="F45">
+      <c r="A45" s="0" t="s">
+        <v>2247</v>
+      </c>
+      <c r="B45" s="0" t="s">
+        <v>2248</v>
+      </c>
+      <c r="C45" s="0" t="s">
+        <v>2249</v>
+      </c>
+      <c r="D45" s="0" t="s">
+        <v>2250</v>
+      </c>
+      <c r="E45" s="0"/>
+      <c r="F45" s="0">
         <v>4</v>
       </c>
-      <c r="G45" t="s">
-        <v>702</v>
-      </c>
-      <c r="H45" t="s">
-        <v>703</v>
-      </c>
-      <c r="I45" t="s">
-        <v>704</v>
-      </c>
-      <c r="J45" t="s">
-        <v>705</v>
-      </c>
-      <c r="K45" t="s">
-        <v>706</v>
-      </c>
-      <c r="L45" t="s">
-        <v>707</v>
-      </c>
-      <c r="M45" t="s">
-        <v>708</v>
-      </c>
-      <c r="N45">
+      <c r="G45" s="0" t="s">
+        <v>2251</v>
+      </c>
+      <c r="H45" s="0" t="s">
+        <v>2252</v>
+      </c>
+      <c r="I45" s="0" t="s">
+        <v>2253</v>
+      </c>
+      <c r="J45" s="0" t="s">
+        <v>2254</v>
+      </c>
+      <c r="K45" s="0" t="s">
+        <v>2255</v>
+      </c>
+      <c r="L45" s="0" t="s">
+        <v>2256</v>
+      </c>
+      <c r="M45" s="0" t="s">
+        <v>2257</v>
+      </c>
+      <c r="N45" s="0">
         <v>8</v>
       </c>
-      <c r="O45" t="s">
-        <v>709</v>
-      </c>
-      <c r="P45">
-        <v>0.2</v>
-      </c>
-      <c r="Q45" t="s">
-        <v>19</v>
-      </c>
-      <c r="R45" t="s">
-        <v>710</v>
-      </c>
-      <c r="S45" t="s">
-        <v>711</v>
-      </c>
-      <c r="U45" t="s">
-        <v>980</v>
-      </c>
-      <c r="V45" t="s">
-        <v>1120</v>
+      <c r="O45" s="0" t="s">
+        <v>2258</v>
+      </c>
+      <c r="P45" s="0">
+        <v>0.20000000000000001</v>
+      </c>
+      <c r="Q45" s="0" t="s">
+        <v>2259</v>
+      </c>
+      <c r="R45" s="0" t="s">
+        <v>2260</v>
+      </c>
+      <c r="S45" s="0" t="s">
+        <v>2261</v>
+      </c>
+      <c r="T45" s="0"/>
+      <c r="U45" s="0" t="s">
+        <v>2262</v>
+      </c>
+      <c r="V45" s="0" t="s">
+        <v>2263</v>
       </c>
     </row>
     <row r="46">
@@ -12714,132 +13196,330 @@
     </row>
     <row r="94">
       <c r="A94" s="0" t="s">
-        <v>2177</v>
+        <v>2212</v>
       </c>
       <c r="B94" s="0" t="s">
-        <v>2178</v>
+        <v>2213</v>
       </c>
       <c r="C94" s="0" t="s">
-        <v>2179</v>
+        <v>2214</v>
       </c>
       <c r="D94" s="0" t="s">
-        <v>2180</v>
+        <v>2215</v>
       </c>
       <c r="E94" s="0" t="s">
-        <v>2181</v>
+        <v>2216</v>
       </c>
       <c r="F94" s="0">
         <v>4</v>
       </c>
       <c r="G94" s="0" t="s">
-        <v>2182</v>
+        <v>2217</v>
       </c>
       <c r="H94" s="0" t="s">
-        <v>2183</v>
+        <v>2218</v>
       </c>
       <c r="I94" s="0" t="s">
-        <v>2184</v>
+        <v>2219</v>
       </c>
       <c r="J94" s="0" t="s">
-        <v>2185</v>
+        <v>2220</v>
       </c>
       <c r="K94" s="0" t="s">
-        <v>2186</v>
+        <v>2221</v>
       </c>
       <c r="L94" s="0" t="s">
-        <v>2187</v>
+        <v>2222</v>
       </c>
       <c r="M94" s="0" t="s">
-        <v>2188</v>
+        <v>2223</v>
       </c>
       <c r="N94" s="0">
         <v>2</v>
       </c>
       <c r="O94" s="0" t="s">
-        <v>2189</v>
+        <v>2224</v>
       </c>
       <c r="P94" s="0">
         <v>1</v>
       </c>
       <c r="Q94" s="0" t="s">
-        <v>2190</v>
+        <v>2225</v>
       </c>
       <c r="R94" s="0" t="s">
-        <v>2191</v>
+        <v>2226</v>
       </c>
       <c r="S94" s="0" t="s">
-        <v>2192</v>
+        <v>2227</v>
       </c>
       <c r="T94" s="0"/>
       <c r="U94" s="0"/>
       <c r="V94" s="0" t="s">
-        <v>2193</v>
+        <v>2228</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" s="0" t="s">
-        <v>2159</v>
+        <v>2229</v>
       </c>
       <c r="B95" s="0" t="s">
-        <v>2160</v>
+        <v>2230</v>
       </c>
       <c r="C95" s="0" t="s">
-        <v>2161</v>
+        <v>2231</v>
       </c>
       <c r="D95" s="0" t="s">
-        <v>2162</v>
+        <v>2232</v>
       </c>
       <c r="E95" s="0" t="s">
-        <v>2163</v>
+        <v>2233</v>
       </c>
       <c r="F95" s="0">
         <v>4</v>
       </c>
       <c r="G95" s="0" t="s">
-        <v>2164</v>
+        <v>2234</v>
       </c>
       <c r="H95" s="0" t="s">
-        <v>2165</v>
+        <v>2235</v>
       </c>
       <c r="I95" s="0" t="s">
-        <v>2166</v>
+        <v>2236</v>
       </c>
       <c r="J95" s="0" t="s">
-        <v>2167</v>
+        <v>2237</v>
       </c>
       <c r="K95" s="0" t="s">
-        <v>2168</v>
+        <v>2238</v>
       </c>
       <c r="L95" s="0" t="s">
-        <v>2169</v>
+        <v>2239</v>
       </c>
       <c r="M95" s="0" t="s">
-        <v>2170</v>
+        <v>2240</v>
       </c>
       <c r="N95" s="0">
         <v>4</v>
       </c>
       <c r="O95" s="0" t="s">
-        <v>2171</v>
+        <v>2241</v>
       </c>
       <c r="P95" s="0">
         <v>1</v>
       </c>
       <c r="Q95" s="0" t="s">
-        <v>2172</v>
+        <v>2242</v>
       </c>
       <c r="R95" s="0" t="s">
-        <v>2173</v>
+        <v>2243</v>
       </c>
       <c r="S95" s="0" t="s">
-        <v>2174</v>
+        <v>2244</v>
       </c>
       <c r="T95" s="0"/>
       <c r="U95" s="0" t="s">
-        <v>2175</v>
+        <v>2245</v>
       </c>
       <c r="V95" s="0" t="s">
-        <v>2176</v>
+        <v>2246</v>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" s="0" t="s">
+        <v>2282</v>
+      </c>
+      <c r="B96" s="0" t="s">
+        <v>2283</v>
+      </c>
+      <c r="C96" s="0" t="s">
+        <v>2284</v>
+      </c>
+      <c r="D96" s="0" t="s">
+        <v>2285</v>
+      </c>
+      <c r="E96" s="0" t="s">
+        <v>2286</v>
+      </c>
+      <c r="F96" s="0">
+        <v>4</v>
+      </c>
+      <c r="G96" s="0" t="s">
+        <v>2287</v>
+      </c>
+      <c r="H96" s="0" t="s">
+        <v>2288</v>
+      </c>
+      <c r="I96" s="0" t="s">
+        <v>2289</v>
+      </c>
+      <c r="J96" s="0" t="s">
+        <v>2290</v>
+      </c>
+      <c r="K96" s="0" t="s">
+        <v>2291</v>
+      </c>
+      <c r="L96" s="0" t="s">
+        <v>2292</v>
+      </c>
+      <c r="M96" s="0" t="s">
+        <v>2293</v>
+      </c>
+      <c r="N96" s="0">
+        <v>8</v>
+      </c>
+      <c r="O96" s="0" t="s">
+        <v>2294</v>
+      </c>
+      <c r="P96" s="0">
+        <v>0.20000000000000001</v>
+      </c>
+      <c r="Q96" s="0" t="s">
+        <v>2295</v>
+      </c>
+      <c r="R96" s="0" t="s">
+        <v>2296</v>
+      </c>
+      <c r="S96" s="0" t="s">
+        <v>2297</v>
+      </c>
+      <c r="T96" s="0"/>
+      <c r="U96" s="0" t="s">
+        <v>2298</v>
+      </c>
+      <c r="V96" s="0" t="s">
+        <v>2299</v>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" s="0" t="s">
+        <v>2318</v>
+      </c>
+      <c r="B97" s="0" t="s">
+        <v>2319</v>
+      </c>
+      <c r="C97" s="0" t="s">
+        <v>2320</v>
+      </c>
+      <c r="D97" s="0" t="s">
+        <v>2321</v>
+      </c>
+      <c r="E97" s="0" t="s">
+        <v>2322</v>
+      </c>
+      <c r="F97" s="0">
+        <v>4</v>
+      </c>
+      <c r="G97" s="0" t="s">
+        <v>2323</v>
+      </c>
+      <c r="H97" s="0" t="s">
+        <v>2324</v>
+      </c>
+      <c r="I97" s="0" t="s">
+        <v>2325</v>
+      </c>
+      <c r="J97" s="0" t="s">
+        <v>2326</v>
+      </c>
+      <c r="K97" s="0" t="s">
+        <v>2327</v>
+      </c>
+      <c r="L97" s="0" t="s">
+        <v>2328</v>
+      </c>
+      <c r="M97" s="0" t="s">
+        <v>2329</v>
+      </c>
+      <c r="N97" s="0">
+        <v>8</v>
+      </c>
+      <c r="O97" s="0" t="s">
+        <v>2330</v>
+      </c>
+      <c r="P97" s="0">
+        <v>0.20000000000000001</v>
+      </c>
+      <c r="Q97" s="0" t="s">
+        <v>2331</v>
+      </c>
+      <c r="R97" s="0" t="s">
+        <v>2332</v>
+      </c>
+      <c r="S97" s="0" t="s">
+        <v>2333</v>
+      </c>
+      <c r="T97" s="0"/>
+      <c r="U97" s="0" t="s">
+        <v>2334</v>
+      </c>
+      <c r="V97" s="0" t="s">
+        <v>2335</v>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" s="0" t="s">
+        <v>2354</v>
+      </c>
+      <c r="B98" s="0" t="s">
+        <v>2355</v>
+      </c>
+      <c r="C98" s="0" t="s">
+        <v>2356</v>
+      </c>
+      <c r="D98" s="0" t="s">
+        <v>2357</v>
+      </c>
+      <c r="E98" s="0" t="s">
+        <v>2358</v>
+      </c>
+      <c r="F98" s="0">
+        <v>4</v>
+      </c>
+      <c r="G98" s="0" t="s">
+        <v>2359</v>
+      </c>
+      <c r="H98" s="0" t="s">
+        <v>2360</v>
+      </c>
+      <c r="I98" s="0" t="s">
+        <v>2361</v>
+      </c>
+      <c r="J98" s="0" t="s">
+        <v>2362</v>
+      </c>
+      <c r="K98" s="0" t="s">
+        <v>2363</v>
+      </c>
+      <c r="L98" s="0" t="s">
+        <v>2364</v>
+      </c>
+      <c r="M98" s="0" t="s">
+        <v>2365</v>
+      </c>
+      <c r="N98" s="0">
+        <v>2</v>
+      </c>
+      <c r="O98" s="0" t="s">
+        <v>2366</v>
+      </c>
+      <c r="P98" s="0">
+        <v>0.20000000000000001</v>
+      </c>
+      <c r="Q98" s="0" t="s">
+        <v>2367</v>
+      </c>
+      <c r="R98" s="0" t="s">
+        <v>2368</v>
+      </c>
+      <c r="S98" s="0" t="s">
+        <v>2369</v>
+      </c>
+      <c r="T98" s="0"/>
+      <c r="U98" s="0" t="s">
+        <v>2370</v>
+      </c>
+      <c r="V98" s="0" t="s">
+        <v>2371</v>
       </c>
     </row>
   </sheetData>

--- a/config/becExpConfig/becExpType.csv.xlsx
+++ b/config/becExpConfig/becExpType.csv.xlsx
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2639" uniqueCount="2372">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2693" uniqueCount="2426">
   <si>
     <t>TrialName</t>
   </si>
@@ -7143,6 +7143,168 @@
   </si>
   <si>
     <t>WaveformGeneratorName,XvWingMod;ChannelName,Ch1;WaveformListName,XvWingLatticeCC</t>
+  </si>
+  <si>
+    <t>PhaseLockName,ImagingLock;Frequency,700000000;VariableName,hw_ImagingNi</t>
+  </si>
+  <si>
+    <t>NiLatticeCCXvLatticeBm</t>
+  </si>
+  <si>
+    <t>An experiment at the non-interacting lattice stage. Scan xvlattice. With band mapping.</t>
+  </si>
+  <si>
+    <t>TOP</t>
+  </si>
+  <si>
+    <t>BMPDloopTof8000</t>
+  </si>
+  <si>
+    <t>None</t>
+  </si>
+  <si>
+    <t>hw_XvLattice</t>
+  </si>
+  <si>
+    <t>DensityFit;AtomNumber</t>
+  </si>
+  <si>
+    <t>LSR</t>
+  </si>
+  <si>
+    <t>[353 1231;517 1162;1370 1128;1605 1136;1657 1227;1628 1333;1262 1362;668 1384;385 1392;364 1330]</t>
+  </si>
+  <si>
+    <t>HF</t>
+  </si>
+  <si>
+    <t>Absorption</t>
+  </si>
+  <si>
+    <t>StrongLight</t>
+  </si>
+  <si>
+    <t>BosonicGaussianFit1D</t>
+  </si>
+  <si>
+    <t>None</t>
+  </si>
+  <si>
+    <t>LinearFit1D</t>
+  </si>
+  <si>
+    <t>StdErr</t>
+  </si>
+  <si>
+    <t>WaveformGeneratorName,LatticeMod,XvWingMod;ChannelName,Ch2,Ch1;WaveformListName,PdAi,XvWingLattice</t>
+  </si>
+  <si>
+    <t>PhaseLockName,ImagingLock;Frequency,700000000;VariableName,hw_ImagingNi</t>
+  </si>
+  <si>
+    <t>NiLatticeCCXvLatticeBm</t>
+  </si>
+  <si>
+    <t>An experiment at the non-interacting lattice stage. Scan xvlattice. With band mapping.</t>
+  </si>
+  <si>
+    <t>TOP</t>
+  </si>
+  <si>
+    <t>BMPDloopTof8000</t>
+  </si>
+  <si>
+    <t>None</t>
+  </si>
+  <si>
+    <t>hw_XvLattice</t>
+  </si>
+  <si>
+    <t>DensityFit;AtomNumber</t>
+  </si>
+  <si>
+    <t>LSR</t>
+  </si>
+  <si>
+    <t>[353 1231;517 1162;1370 1128;1605 1136;1657 1227;1628 1333;1262 1362;668 1384;385 1392;364 1330]</t>
+  </si>
+  <si>
+    <t>HF</t>
+  </si>
+  <si>
+    <t>Absorption</t>
+  </si>
+  <si>
+    <t>StrongLight</t>
+  </si>
+  <si>
+    <t>BosonicGaussianFit1D</t>
+  </si>
+  <si>
+    <t>None</t>
+  </si>
+  <si>
+    <t>LinearFit1D</t>
+  </si>
+  <si>
+    <t>StdErr</t>
+  </si>
+  <si>
+    <t>WaveformGeneratorName,LatticeMod,XvWingMod;ChannelName,Ch2,Ch1;WaveformListName,PdAi,XvWingLattice</t>
+  </si>
+  <si>
+    <t>PhaseLockName,ImagingLock;Frequency,700000000;VariableName,hw_ImagingNi</t>
+  </si>
+  <si>
+    <t>NiLatticeCCXvLatticeBm</t>
+  </si>
+  <si>
+    <t>An experiment at the non-interacting lattice stage. Scan xvlattice. With band mapping.</t>
+  </si>
+  <si>
+    <t>TOP</t>
+  </si>
+  <si>
+    <t>BMPDloopTof8000</t>
+  </si>
+  <si>
+    <t>None</t>
+  </si>
+  <si>
+    <t>hw_XvLattice</t>
+  </si>
+  <si>
+    <t>DensityFit;AtomNumber</t>
+  </si>
+  <si>
+    <t>LSR</t>
+  </si>
+  <si>
+    <t>[353 1231;517 1162;1370 1128;1605 1136;1657 1227;1628 1333;1262 1362;668 1384;385 1392;364 1330]</t>
+  </si>
+  <si>
+    <t>HF</t>
+  </si>
+  <si>
+    <t>Absorption</t>
+  </si>
+  <si>
+    <t>StrongLight</t>
+  </si>
+  <si>
+    <t>BosonicGaussianFit1D</t>
+  </si>
+  <si>
+    <t>None</t>
+  </si>
+  <si>
+    <t>LinearFit1D</t>
+  </si>
+  <si>
+    <t>StdErr</t>
+  </si>
+  <si>
+    <t>WaveformGeneratorName,LatticeMod,XvWingMod;ChannelName,Ch2,Ch1;WaveformListName,PdAi,XvWingLatticeCC</t>
   </si>
   <si>
     <t>PhaseLockName,ImagingLock;Frequency,700000000;VariableName,hw_ImagingNi</t>
@@ -7472,7 +7634,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:V98"/>
+  <dimension ref="A1:V99"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="36.42578125" customWidth="true"/>
@@ -13522,6 +13684,72 @@
         <v>2371</v>
       </c>
     </row>
+    <row r="99">
+      <c r="A99" s="0" t="s">
+        <v>2408</v>
+      </c>
+      <c r="B99" s="0" t="s">
+        <v>2409</v>
+      </c>
+      <c r="C99" s="0" t="s">
+        <v>2410</v>
+      </c>
+      <c r="D99" s="0" t="s">
+        <v>2411</v>
+      </c>
+      <c r="E99" s="0" t="s">
+        <v>2412</v>
+      </c>
+      <c r="F99" s="0">
+        <v>4</v>
+      </c>
+      <c r="G99" s="0" t="s">
+        <v>2413</v>
+      </c>
+      <c r="H99" s="0" t="s">
+        <v>2414</v>
+      </c>
+      <c r="I99" s="0" t="s">
+        <v>2415</v>
+      </c>
+      <c r="J99" s="0" t="s">
+        <v>2416</v>
+      </c>
+      <c r="K99" s="0" t="s">
+        <v>2417</v>
+      </c>
+      <c r="L99" s="0" t="s">
+        <v>2418</v>
+      </c>
+      <c r="M99" s="0" t="s">
+        <v>2419</v>
+      </c>
+      <c r="N99" s="0">
+        <v>4</v>
+      </c>
+      <c r="O99" s="0" t="s">
+        <v>2420</v>
+      </c>
+      <c r="P99" s="0">
+        <v>1</v>
+      </c>
+      <c r="Q99" s="0" t="s">
+        <v>2421</v>
+      </c>
+      <c r="R99" s="0" t="s">
+        <v>2422</v>
+      </c>
+      <c r="S99" s="0" t="s">
+        <v>2423</v>
+      </c>
+      <c r="T99" s="0"/>
+      <c r="U99" s="0" t="s">
+        <v>2424</v>
+      </c>
+      <c r="V99" s="0" t="s">
+        <v>2425</v>
+      </c>
+    </row>
   </sheetData>
   <sortState ref="A2:U83">
     <sortCondition ref="A2:A83"/>

--- a/config/becExpConfig/becExpType.csv.xlsx
+++ b/config/becExpConfig/becExpType.csv.xlsx
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2693" uniqueCount="2426">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3053" uniqueCount="2786">
   <si>
     <t>TrialName</t>
   </si>
@@ -7272,6 +7272,1086 @@
   </si>
   <si>
     <t>hw_XvLattice</t>
+  </si>
+  <si>
+    <t>DensityFit;AtomNumber</t>
+  </si>
+  <si>
+    <t>LSR</t>
+  </si>
+  <si>
+    <t>[353 1231;517 1162;1370 1128;1605 1136;1657 1227;1628 1333;1262 1362;668 1384;385 1392;364 1330]</t>
+  </si>
+  <si>
+    <t>HF</t>
+  </si>
+  <si>
+    <t>Absorption</t>
+  </si>
+  <si>
+    <t>StrongLight</t>
+  </si>
+  <si>
+    <t>BosonicGaussianFit1D</t>
+  </si>
+  <si>
+    <t>None</t>
+  </si>
+  <si>
+    <t>LinearFit1D</t>
+  </si>
+  <si>
+    <t>StdErr</t>
+  </si>
+  <si>
+    <t>WaveformGeneratorName,LatticeMod,XvWingMod;ChannelName,Ch2,Ch1;WaveformListName,PdAi,XvWingLatticeCC</t>
+  </si>
+  <si>
+    <t>PhaseLockName,ImagingLock;Frequency,700000000;VariableName,hw_ImagingNi</t>
+  </si>
+  <si>
+    <t>NiLatticeCcBoBm</t>
+  </si>
+  <si>
+    <t>A Bloch oscillation experiment at the non-interacting lattice stage. With band mapping.</t>
+  </si>
+  <si>
+    <t>TOP</t>
+  </si>
+  <si>
+    <t>NiLatticeBoBmTof8000</t>
+  </si>
+  <si>
+    <t>None</t>
+  </si>
+  <si>
+    <t>latticehold</t>
+  </si>
+  <si>
+    <t>DensityFit;AtomNumber;CenterFit</t>
+  </si>
+  <si>
+    <t>LSR</t>
+  </si>
+  <si>
+    <t>[790 1235;871 1209;1275 1193;1400 1215;1404 1288;1311 1320;928 1334;800 1309]</t>
+  </si>
+  <si>
+    <t>HF</t>
+  </si>
+  <si>
+    <t>Absorption</t>
+  </si>
+  <si>
+    <t>StrongLight</t>
+  </si>
+  <si>
+    <t>BosonicGaussianFit1D</t>
+  </si>
+  <si>
+    <t>None</t>
+  </si>
+  <si>
+    <t>TriangleFit1D</t>
+  </si>
+  <si>
+    <t>StdErr</t>
+  </si>
+  <si>
+    <t>WaveformGeneratorName,XvWingMod;ChannelName,Ch1;WaveformListName,XvWingLatticeCC</t>
+  </si>
+  <si>
+    <t>PhaseLockName,ImagingLock;Frequency,700000000;VariableName,hw_ImagingNi</t>
+  </si>
+  <si>
+    <t>NiLatticeCcBoBm</t>
+  </si>
+  <si>
+    <t>A Bloch oscillation experiment at the non-interacting lattice stage. With band mapping.</t>
+  </si>
+  <si>
+    <t>TOP</t>
+  </si>
+  <si>
+    <t>NiLatticeBoBmTof8000</t>
+  </si>
+  <si>
+    <t>None</t>
+  </si>
+  <si>
+    <t>latticehold</t>
+  </si>
+  <si>
+    <t>DensityFit;AtomNumber;CenterFit</t>
+  </si>
+  <si>
+    <t>LSR</t>
+  </si>
+  <si>
+    <t>[721 1279;904 1217;1204 1213;1408 1240;1385 1312;1202 1353;844 1371;727 1325]</t>
+  </si>
+  <si>
+    <t>HF</t>
+  </si>
+  <si>
+    <t>Absorption</t>
+  </si>
+  <si>
+    <t>StrongLight</t>
+  </si>
+  <si>
+    <t>BosonicGaussianFit1D</t>
+  </si>
+  <si>
+    <t>None</t>
+  </si>
+  <si>
+    <t>TriangleFit1D</t>
+  </si>
+  <si>
+    <t>StdErr</t>
+  </si>
+  <si>
+    <t>WaveformGeneratorName,XvWingMod;ChannelName,Ch1;WaveformListName,XvWingLatticeCC</t>
+  </si>
+  <si>
+    <t>PhaseLockName,ImagingLock;Frequency,700000000;VariableName,hw_ImagingNi</t>
+  </si>
+  <si>
+    <t>NiLatticeCcBoBm</t>
+  </si>
+  <si>
+    <t>A Bloch oscillation experiment at the non-interacting lattice stage. With band mapping.</t>
+  </si>
+  <si>
+    <t>TOP</t>
+  </si>
+  <si>
+    <t>NiLatticeBoBmTof8000</t>
+  </si>
+  <si>
+    <t>None</t>
+  </si>
+  <si>
+    <t>latticehold</t>
+  </si>
+  <si>
+    <t>DensityFit;AtomNumber;CenterFit</t>
+  </si>
+  <si>
+    <t>LSR</t>
+  </si>
+  <si>
+    <t>[721 1279;904 1217;1204 1213;1408 1240;1385 1312;1202 1353;844 1371;727 1325]</t>
+  </si>
+  <si>
+    <t>HF</t>
+  </si>
+  <si>
+    <t>Absorption</t>
+  </si>
+  <si>
+    <t>StrongLight</t>
+  </si>
+  <si>
+    <t>BosonicGaussianFit1D</t>
+  </si>
+  <si>
+    <t>None</t>
+  </si>
+  <si>
+    <t>TriangleFit1D</t>
+  </si>
+  <si>
+    <t>StdErr</t>
+  </si>
+  <si>
+    <t>WaveformGeneratorName,XvWingMod;ChannelName,Ch1;WaveformListName,XvWingLatticeCC</t>
+  </si>
+  <si>
+    <t>PhaseLockName,ImagingLock;Frequency,700000000;VariableName,hw_ImagingNi</t>
+  </si>
+  <si>
+    <t>NiLatticeCcBoBm</t>
+  </si>
+  <si>
+    <t>A Bloch oscillation experiment at the non-interacting lattice stage. With band mapping.</t>
+  </si>
+  <si>
+    <t>TOP</t>
+  </si>
+  <si>
+    <t>NiLatticeBoBmTof8000</t>
+  </si>
+  <si>
+    <t>None</t>
+  </si>
+  <si>
+    <t>latticehold</t>
+  </si>
+  <si>
+    <t>DensityFit;AtomNumber;CenterFit</t>
+  </si>
+  <si>
+    <t>LSR</t>
+  </si>
+  <si>
+    <t>[812 1312;840 1282;949 1272;1108 1271;1194 1273;1212 1312;1199 1380;1138 1393;974 1395;876 1399;822 1388]</t>
+  </si>
+  <si>
+    <t>HF</t>
+  </si>
+  <si>
+    <t>Absorption</t>
+  </si>
+  <si>
+    <t>StrongLight</t>
+  </si>
+  <si>
+    <t>BosonicGaussianFit1D</t>
+  </si>
+  <si>
+    <t>None</t>
+  </si>
+  <si>
+    <t>TriangleFit1D</t>
+  </si>
+  <si>
+    <t>StdErr</t>
+  </si>
+  <si>
+    <t>WaveformGeneratorName,XvWingMod;ChannelName,Ch1;WaveformListName,XvWingLatticeCC</t>
+  </si>
+  <si>
+    <t>PhaseLockName,ImagingLock;Frequency,700000000;VariableName,hw_ImagingNi</t>
+  </si>
+  <si>
+    <t>NiLatticeCcBoBm</t>
+  </si>
+  <si>
+    <t>A Bloch oscillation experiment at the non-interacting lattice stage. With band mapping.</t>
+  </si>
+  <si>
+    <t>TOP</t>
+  </si>
+  <si>
+    <t>NiLatticeBoBmTof8000</t>
+  </si>
+  <si>
+    <t>None</t>
+  </si>
+  <si>
+    <t>latticehold</t>
+  </si>
+  <si>
+    <t>DensityFit;AtomNumber;CenterFit</t>
+  </si>
+  <si>
+    <t>LSR</t>
+  </si>
+  <si>
+    <t>[812 1312;840 1282;949 1272;1108 1271;1194 1273;1212 1312;1199 1380;1138 1393;974 1395;876 1399;822 1388]</t>
+  </si>
+  <si>
+    <t>HF</t>
+  </si>
+  <si>
+    <t>Absorption</t>
+  </si>
+  <si>
+    <t>StrongLight</t>
+  </si>
+  <si>
+    <t>BosonicGaussianFit1D</t>
+  </si>
+  <si>
+    <t>None</t>
+  </si>
+  <si>
+    <t>TriangleFit1D</t>
+  </si>
+  <si>
+    <t>StdErr</t>
+  </si>
+  <si>
+    <t>WaveformGeneratorName,XvWingMod;ChannelName,Ch1;WaveformListName,XvWingLatticeCC</t>
+  </si>
+  <si>
+    <t>PhaseLockName,ImagingLock;Frequency,700000000;VariableName,hw_ImagingNi</t>
+  </si>
+  <si>
+    <t>NiLatticeCcBoBm</t>
+  </si>
+  <si>
+    <t>A Bloch oscillation experiment at the non-interacting lattice stage. With band mapping.</t>
+  </si>
+  <si>
+    <t>TOP</t>
+  </si>
+  <si>
+    <t>NiLatticeCCBoBmTof4000</t>
+  </si>
+  <si>
+    <t>None</t>
+  </si>
+  <si>
+    <t>latticehold</t>
+  </si>
+  <si>
+    <t>DensityFit;AtomNumber;CenterFit</t>
+  </si>
+  <si>
+    <t>LSR</t>
+  </si>
+  <si>
+    <t>[812 1312;840 1282;949 1272;1108 1271;1194 1273;1212 1312;1199 1380;1138 1393;974 1395;876 1399;822 1388]</t>
+  </si>
+  <si>
+    <t>HF</t>
+  </si>
+  <si>
+    <t>Absorption</t>
+  </si>
+  <si>
+    <t>StrongLight</t>
+  </si>
+  <si>
+    <t>BosonicGaussianFit1D</t>
+  </si>
+  <si>
+    <t>None</t>
+  </si>
+  <si>
+    <t>TriangleFit1D</t>
+  </si>
+  <si>
+    <t>StdErr</t>
+  </si>
+  <si>
+    <t>WaveformGeneratorName,XvWingMod;ChannelName,Ch1;WaveformListName,XvWingLatticeCC</t>
+  </si>
+  <si>
+    <t>PhaseLockName,ImagingLock;Frequency,700000000;VariableName,hw_ImagingNi</t>
+  </si>
+  <si>
+    <t>NiLatticeCcBoBm</t>
+  </si>
+  <si>
+    <t>A Bloch oscillation experiment at the non-interacting lattice stage. With band mapping.</t>
+  </si>
+  <si>
+    <t>TOP</t>
+  </si>
+  <si>
+    <t>NiLatticeCCBoBmTof4000</t>
+  </si>
+  <si>
+    <t>None</t>
+  </si>
+  <si>
+    <t>latticehold</t>
+  </si>
+  <si>
+    <t>DensityFit;AtomNumber;CenterFit</t>
+  </si>
+  <si>
+    <t>LSR</t>
+  </si>
+  <si>
+    <t>[782 1299;854 1254;1037 1256;1161 1246;1230 1298;1241 1371;1163 1413;1025 1425;844 1425;788 1392]</t>
+  </si>
+  <si>
+    <t>HF</t>
+  </si>
+  <si>
+    <t>Absorption</t>
+  </si>
+  <si>
+    <t>StrongLight</t>
+  </si>
+  <si>
+    <t>BosonicGaussianFit1D</t>
+  </si>
+  <si>
+    <t>None</t>
+  </si>
+  <si>
+    <t>TriangleFit1D</t>
+  </si>
+  <si>
+    <t>StdErr</t>
+  </si>
+  <si>
+    <t>WaveformGeneratorName,XvWingMod;ChannelName,Ch1;WaveformListName,XvWingLatticeCC</t>
+  </si>
+  <si>
+    <t>PhaseLockName,ImagingLock;Frequency,700000000;VariableName,hw_ImagingNi</t>
+  </si>
+  <si>
+    <t>NiLatticeCcKP2VVA</t>
+  </si>
+  <si>
+    <t>An experiment at the non-interacting lattice stage. Scan KP2VVA.</t>
+  </si>
+  <si>
+    <t>TOP</t>
+  </si>
+  <si>
+    <t>NiLatticeDepthCalibTof8000</t>
+  </si>
+  <si>
+    <t>None</t>
+  </si>
+  <si>
+    <t>KP2VVA</t>
+  </si>
+  <si>
+    <t>DensityFit;AtomNumber</t>
+  </si>
+  <si>
+    <t>LSR</t>
+  </si>
+  <si>
+    <t>[428 1188;595 1085;914 1060;1346 1060;1549 1122;1581 1345;1453 1464;1010 1503;481 1490]</t>
+  </si>
+  <si>
+    <t>HF</t>
+  </si>
+  <si>
+    <t>Absorption</t>
+  </si>
+  <si>
+    <t>StrongLight</t>
+  </si>
+  <si>
+    <t>BosonicGaussianFit1D</t>
+  </si>
+  <si>
+    <t>None</t>
+  </si>
+  <si>
+    <t>ParabolicFit1D</t>
+  </si>
+  <si>
+    <t>StdErr</t>
+  </si>
+  <si>
+    <t>WaveformGeneratorName,LatticeMod,XvWingMod;ChannelName,Ch2,Ch1;WaveformListName,SdDepthCalib,XvWingNiCC</t>
+  </si>
+  <si>
+    <t>PhaseLockName,ImagingLock;Frequency,700000000;VariableName,hw_ImagingNi</t>
+  </si>
+  <si>
+    <t>NiLatticeCcKP2VVA</t>
+  </si>
+  <si>
+    <t>An experiment at the non-interacting lattice stage. Scan KP2VVA.</t>
+  </si>
+  <si>
+    <t>TOP</t>
+  </si>
+  <si>
+    <t>NiLatticeCCBoBmTof4000</t>
+  </si>
+  <si>
+    <t>None</t>
+  </si>
+  <si>
+    <t>KP2VVA</t>
+  </si>
+  <si>
+    <t>DensityFit;AtomNumber</t>
+  </si>
+  <si>
+    <t>LSR</t>
+  </si>
+  <si>
+    <t>[428 1188;595 1085;914 1060;1346 1060;1549 1122;1581 1345;1453 1464;1010 1503;481 1490]</t>
+  </si>
+  <si>
+    <t>HF</t>
+  </si>
+  <si>
+    <t>Absorption</t>
+  </si>
+  <si>
+    <t>StrongLight</t>
+  </si>
+  <si>
+    <t>BosonicGaussianFit1D</t>
+  </si>
+  <si>
+    <t>None</t>
+  </si>
+  <si>
+    <t>ParabolicFit1D</t>
+  </si>
+  <si>
+    <t>StdErr</t>
+  </si>
+  <si>
+    <t>WaveformGeneratorName,LatticeMod,XvWingMod;ChannelName,Ch2,Ch1;WaveformListName,SdDepthCalib,XvWingNiCC</t>
+  </si>
+  <si>
+    <t>PhaseLockName,ImagingLock;Frequency,700000000;VariableName,hw_ImagingNi</t>
+  </si>
+  <si>
+    <t>NiLatticeCcKP2VVA</t>
+  </si>
+  <si>
+    <t>An experiment at the non-interacting lattice stage. Scan KP2VVA.</t>
+  </si>
+  <si>
+    <t>TOP</t>
+  </si>
+  <si>
+    <t>NiLatticeCCBoBmTof4000</t>
+  </si>
+  <si>
+    <t>None</t>
+  </si>
+  <si>
+    <t>KP2VVA</t>
+  </si>
+  <si>
+    <t>DensityFit;AtomNumber</t>
+  </si>
+  <si>
+    <t>LSR</t>
+  </si>
+  <si>
+    <t>[591 1325;753 1265;1102 1240;1340 1266;1343 1376;1225 1438;961 1454;706 1461;582 1412]</t>
+  </si>
+  <si>
+    <t>HF</t>
+  </si>
+  <si>
+    <t>Absorption</t>
+  </si>
+  <si>
+    <t>StrongLight</t>
+  </si>
+  <si>
+    <t>BosonicGaussianFit1D</t>
+  </si>
+  <si>
+    <t>None</t>
+  </si>
+  <si>
+    <t>ParabolicFit1D</t>
+  </si>
+  <si>
+    <t>StdErr</t>
+  </si>
+  <si>
+    <t>WaveformGeneratorName,LatticeMod,XvWingMod;ChannelName,Ch2,Ch1;WaveformListName,SdDepthCalib,XvWingNiCC</t>
+  </si>
+  <si>
+    <t>PhaseLockName,ImagingLock;Frequency,700000000;VariableName,hw_ImagingNi</t>
+  </si>
+  <si>
+    <t>NiLatticeCcKP2VVA</t>
+  </si>
+  <si>
+    <t>An experiment at the non-interacting lattice stage. Scan KP2VVA.</t>
+  </si>
+  <si>
+    <t>TOP</t>
+  </si>
+  <si>
+    <t>NiLatticeCCBoBmTof4000</t>
+  </si>
+  <si>
+    <t>None</t>
+  </si>
+  <si>
+    <t>KP2VVA</t>
+  </si>
+  <si>
+    <t>DensityFit;AtomNumber</t>
+  </si>
+  <si>
+    <t>LSR</t>
+  </si>
+  <si>
+    <t>[591 1325;753 1265;1102 1240;1340 1266;1343 1376;1225 1438;961 1454;706 1461;582 1412]</t>
+  </si>
+  <si>
+    <t>HF</t>
+  </si>
+  <si>
+    <t>Absorption</t>
+  </si>
+  <si>
+    <t>StrongLight</t>
+  </si>
+  <si>
+    <t>BosonicGaussianFit1D</t>
+  </si>
+  <si>
+    <t>None</t>
+  </si>
+  <si>
+    <t>ParabolicFit1D</t>
+  </si>
+  <si>
+    <t>StdErr</t>
+  </si>
+  <si>
+    <t>WaveformGeneratorName,LatticeMod,XvWingMod;ChannelName,Ch2,Ch1;WaveformListName,SdDepthCalib,XvWingNiCC</t>
+  </si>
+  <si>
+    <t>PhaseLockName,ImagingLock;Frequency,700000000;VariableName,hw_ImagingNi</t>
+  </si>
+  <si>
+    <t>NiLatticeCcKP2VVA</t>
+  </si>
+  <si>
+    <t>An experiment at the non-interacting lattice stage. Scan KP2VVA.</t>
+  </si>
+  <si>
+    <t>TOP</t>
+  </si>
+  <si>
+    <t>NiLatticeCCSdTof4000</t>
+  </si>
+  <si>
+    <t>None</t>
+  </si>
+  <si>
+    <t>KP2VVA</t>
+  </si>
+  <si>
+    <t>DensityFit;AtomNumber</t>
+  </si>
+  <si>
+    <t>LSR</t>
+  </si>
+  <si>
+    <t>[591 1325;753 1265;1102 1240;1340 1266;1343 1376;1225 1438;961 1454;706 1461;582 1412]</t>
+  </si>
+  <si>
+    <t>HF</t>
+  </si>
+  <si>
+    <t>Absorption</t>
+  </si>
+  <si>
+    <t>StrongLight</t>
+  </si>
+  <si>
+    <t>BosonicGaussianFit1D</t>
+  </si>
+  <si>
+    <t>None</t>
+  </si>
+  <si>
+    <t>ParabolicFit1D</t>
+  </si>
+  <si>
+    <t>StdErr</t>
+  </si>
+  <si>
+    <t>WaveformGeneratorName,LatticeMod,XvWingMod;ChannelName,Ch2,Ch1;WaveformListName,SdDepthCalib,XvWingNiCC</t>
+  </si>
+  <si>
+    <t>PhaseLockName,ImagingLock;Frequency,700000000;VariableName,hw_ImagingNi</t>
+  </si>
+  <si>
+    <t>NiLatticeCcSdCalibFreqStart</t>
+  </si>
+  <si>
+    <t>An experiment at the non-interacting lattice stage. Scan hw_SdCalibFreqStart.</t>
+  </si>
+  <si>
+    <t>TOP</t>
+  </si>
+  <si>
+    <t>NiLatticeCCSdTof4000</t>
+  </si>
+  <si>
+    <t>None</t>
+  </si>
+  <si>
+    <t>hw_SdCalibFreqStart</t>
+  </si>
+  <si>
+    <t>DensityFit;AtomNumber</t>
+  </si>
+  <si>
+    <t>LSR</t>
+  </si>
+  <si>
+    <t>[1522 1105;1564 1192;1550 1361;428 1404;424 1170]</t>
+  </si>
+  <si>
+    <t>HF</t>
+  </si>
+  <si>
+    <t>Absorption</t>
+  </si>
+  <si>
+    <t>StrongLight</t>
+  </si>
+  <si>
+    <t>BosonicGaussianFit1D</t>
+  </si>
+  <si>
+    <t>None</t>
+  </si>
+  <si>
+    <t>ParabolicFit1D</t>
+  </si>
+  <si>
+    <t>StdErr</t>
+  </si>
+  <si>
+    <t>WaveformGeneratorName,LatticeMod,XvWingMod;ChannelName,Ch2,Ch1;WaveformListName,SdDepthCalib,XvWingNi</t>
+  </si>
+  <si>
+    <t>PhaseLockName,ImagingLock;Frequency,700000000;VariableName,hw_ImagingNi</t>
+  </si>
+  <si>
+    <t>NiLatticeCcSdCalibFreqStart</t>
+  </si>
+  <si>
+    <t>An experiment at the non-interacting lattice stage. Scan hw_SdCalibFreqStart.</t>
+  </si>
+  <si>
+    <t>TOP</t>
+  </si>
+  <si>
+    <t>NiLatticeCCSdTof4000</t>
+  </si>
+  <si>
+    <t>None</t>
+  </si>
+  <si>
+    <t>hw_SdCalibFreqStart</t>
+  </si>
+  <si>
+    <t>DensityFit;AtomNumber</t>
+  </si>
+  <si>
+    <t>LSR</t>
+  </si>
+  <si>
+    <t>[1522 1105;1564 1192;1550 1361;428 1404;424 1170]</t>
+  </si>
+  <si>
+    <t>HF</t>
+  </si>
+  <si>
+    <t>Absorption</t>
+  </si>
+  <si>
+    <t>StrongLight</t>
+  </si>
+  <si>
+    <t>BosonicGaussianFit1D</t>
+  </si>
+  <si>
+    <t>None</t>
+  </si>
+  <si>
+    <t>ParabolicFit1D</t>
+  </si>
+  <si>
+    <t>StdErr</t>
+  </si>
+  <si>
+    <t>WaveformGeneratorName,LatticeMod,XvWingMod;ChannelName,Ch2,Ch1;WaveformListName,SdDepthCalib,XvWingNiCC</t>
+  </si>
+  <si>
+    <t>PhaseLockName,ImagingLock;Frequency,700000000;VariableName,hw_ImagingNi</t>
+  </si>
+  <si>
+    <t>NiLatticeCCBoBm</t>
+  </si>
+  <si>
+    <t>A Bloch oscillation experiment at the non-interacting lattice stage. With band mapping.</t>
+  </si>
+  <si>
+    <t>TOP</t>
+  </si>
+  <si>
+    <t>NiLatticeBoBmTof8000</t>
+  </si>
+  <si>
+    <t>None</t>
+  </si>
+  <si>
+    <t>latticehold</t>
+  </si>
+  <si>
+    <t>DensityFit;AtomNumber;CenterFit</t>
+  </si>
+  <si>
+    <t>LSR</t>
+  </si>
+  <si>
+    <t>[784 1265;854 1223;1012 1216;1153 1216;1229 1282;1216 1360;1128 1373;965 1380;834 1382;786 1340]</t>
+  </si>
+  <si>
+    <t>HF</t>
+  </si>
+  <si>
+    <t>Absorption</t>
+  </si>
+  <si>
+    <t>StrongLight</t>
+  </si>
+  <si>
+    <t>BosonicGaussianFit1D</t>
+  </si>
+  <si>
+    <t>None</t>
+  </si>
+  <si>
+    <t>TriangleFit1D</t>
+  </si>
+  <si>
+    <t>StdErr</t>
+  </si>
+  <si>
+    <t>WaveformGeneratorName,XvWingMod;ChannelName,Ch1;WaveformListName,XvWingLatticeCC</t>
+  </si>
+  <si>
+    <t>PhaseLockName,ImagingLock;Frequency,700000000;VariableName,hw_ImagingNi</t>
+  </si>
+  <si>
+    <t>NiLatticeCCBoBm</t>
+  </si>
+  <si>
+    <t>A Bloch oscillation experiment at the non-interacting lattice stage. With band mapping.</t>
+  </si>
+  <si>
+    <t>TOP</t>
+  </si>
+  <si>
+    <t>NiLatticeBoBmTof8000</t>
+  </si>
+  <si>
+    <t>None</t>
+  </si>
+  <si>
+    <t>latticehold</t>
+  </si>
+  <si>
+    <t>DensityFit;AtomNumber;CenterFit</t>
+  </si>
+  <si>
+    <t>LSR</t>
+  </si>
+  <si>
+    <t>[784 1265;854 1223;1012 1216;1153 1216;1229 1282;1216 1360;1128 1373;965 1380;834 1382;786 1340]</t>
+  </si>
+  <si>
+    <t>HF</t>
+  </si>
+  <si>
+    <t>Absorption</t>
+  </si>
+  <si>
+    <t>StrongLight</t>
+  </si>
+  <si>
+    <t>BosonicGaussianFit1D</t>
+  </si>
+  <si>
+    <t>None</t>
+  </si>
+  <si>
+    <t>TriangleFit1D</t>
+  </si>
+  <si>
+    <t>StdErr</t>
+  </si>
+  <si>
+    <t>WaveformGeneratorName,XvWingMod;ChannelName,Ch1;WaveformListName,XvWingLatticeCC</t>
+  </si>
+  <si>
+    <t>PhaseLockName,ImagingLock;Frequency,700000000;VariableName,hw_ImagingNi</t>
+  </si>
+  <si>
+    <t>NiLatticeCcSdKP2VVA</t>
+  </si>
+  <si>
+    <t>An experiment at the non-interacting lattice stage. Scan KP2VVA.</t>
+  </si>
+  <si>
+    <t>TOP</t>
+  </si>
+  <si>
+    <t>NiLatticeCCSdTof4000</t>
+  </si>
+  <si>
+    <t>None</t>
+  </si>
+  <si>
+    <t>KP2VVA</t>
+  </si>
+  <si>
+    <t>DensityFit;AtomNumber</t>
+  </si>
+  <si>
+    <t>LSR</t>
+  </si>
+  <si>
+    <t>[591 1325;753 1265;1102 1240;1340 1266;1343 1376;1225 1438;961 1454;706 1461;582 1412]</t>
+  </si>
+  <si>
+    <t>HF</t>
+  </si>
+  <si>
+    <t>Absorption</t>
+  </si>
+  <si>
+    <t>StrongLight</t>
+  </si>
+  <si>
+    <t>BosonicGaussianFit1D</t>
+  </si>
+  <si>
+    <t>None</t>
+  </si>
+  <si>
+    <t>ParabolicFit1D</t>
+  </si>
+  <si>
+    <t>StdErr</t>
+  </si>
+  <si>
+    <t>WaveformGeneratorName,LatticeMod,XvWingMod;ChannelName,Ch2,Ch1;WaveformListName,PdAi,XvWingLatticeCC</t>
+  </si>
+  <si>
+    <t>PhaseLockName,ImagingLock;Frequency,700000000;VariableName,hw_ImagingNi</t>
+  </si>
+  <si>
+    <t>NiLatticeCcSdKP2VVA</t>
+  </si>
+  <si>
+    <t>An experiment at the non-interacting lattice stage. Scan KP2VVA.</t>
+  </si>
+  <si>
+    <t>TOP</t>
+  </si>
+  <si>
+    <t>NiLatticeCCSdTof4000</t>
+  </si>
+  <si>
+    <t>None</t>
+  </si>
+  <si>
+    <t>KP2VVA</t>
+  </si>
+  <si>
+    <t>DensityFit;AtomNumber</t>
+  </si>
+  <si>
+    <t>LSR</t>
+  </si>
+  <si>
+    <t>[448 1248;586 1199;1165 1188;1275 1220;1276 1348;1184 1392;766 1405;541 1407;452 1365]</t>
+  </si>
+  <si>
+    <t>HF</t>
+  </si>
+  <si>
+    <t>Absorption</t>
+  </si>
+  <si>
+    <t>StrongLight</t>
+  </si>
+  <si>
+    <t>BosonicGaussianFit1D</t>
+  </si>
+  <si>
+    <t>None</t>
+  </si>
+  <si>
+    <t>ParabolicFit1D</t>
+  </si>
+  <si>
+    <t>StdErr</t>
+  </si>
+  <si>
+    <t>WaveformGeneratorName,LatticeMod,XvWingMod;ChannelName,Ch2,Ch1;WaveformListName,PdAi,XvWingLatticeCC</t>
+  </si>
+  <si>
+    <t>PhaseLockName,ImagingLock;Frequency,700000000;VariableName,hw_ImagingNi</t>
+  </si>
+  <si>
+    <t>NiLatticeCcSdKP2VVA</t>
+  </si>
+  <si>
+    <t>An experiment at the non-interacting lattice stage. Scan KP2VVA.</t>
+  </si>
+  <si>
+    <t>TOP</t>
+  </si>
+  <si>
+    <t>NiLatticeCCSdTof4000</t>
+  </si>
+  <si>
+    <t>None</t>
+  </si>
+  <si>
+    <t>KP2VVA</t>
+  </si>
+  <si>
+    <t>DensityFit;AtomNumber</t>
+  </si>
+  <si>
+    <t>LSR</t>
+  </si>
+  <si>
+    <t>[448 1248;586 1199;1165 1188;1275 1220;1276 1348;1184 1392;766 1405;541 1407;452 1365]</t>
+  </si>
+  <si>
+    <t>HF</t>
+  </si>
+  <si>
+    <t>Absorption</t>
+  </si>
+  <si>
+    <t>StrongLight</t>
+  </si>
+  <si>
+    <t>BosonicGaussianFit1D</t>
+  </si>
+  <si>
+    <t>None</t>
+  </si>
+  <si>
+    <t>ParabolicFit1D</t>
+  </si>
+  <si>
+    <t>StdErr</t>
+  </si>
+  <si>
+    <t>WaveformGeneratorName,LatticeMod,XvWingMod;ChannelName,Ch2,Ch1;WaveformListName,PdAi,XvWingLatticeCC</t>
+  </si>
+  <si>
+    <t>PhaseLockName,ImagingLock;Frequency,700000000;VariableName,hw_ImagingNi</t>
+  </si>
+  <si>
+    <t>NiLatticeCCXvLatticeBm</t>
+  </si>
+  <si>
+    <t>An experiment at the non-interacting lattice stage. Scan xvlattice. With band mapping.</t>
+  </si>
+  <si>
+    <t>TOP</t>
+  </si>
+  <si>
+    <t>BMPDloopTof8000</t>
+  </si>
+  <si>
+    <t>None</t>
+  </si>
+  <si>
+    <t>hw_XvLatticeCC</t>
   </si>
   <si>
     <t>DensityFit;AtomNumber</t>
@@ -7634,7 +8714,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:V99"/>
+  <dimension ref="A1:V103"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="36.42578125" customWidth="true"/>
@@ -13620,134 +14700,398 @@
     </row>
     <row r="98">
       <c r="A98" s="0" t="s">
-        <v>2354</v>
+        <v>2696</v>
       </c>
       <c r="B98" s="0" t="s">
-        <v>2355</v>
+        <v>2697</v>
       </c>
       <c r="C98" s="0" t="s">
-        <v>2356</v>
+        <v>2698</v>
       </c>
       <c r="D98" s="0" t="s">
-        <v>2357</v>
+        <v>2699</v>
       </c>
       <c r="E98" s="0" t="s">
-        <v>2358</v>
+        <v>2700</v>
       </c>
       <c r="F98" s="0">
         <v>4</v>
       </c>
       <c r="G98" s="0" t="s">
-        <v>2359</v>
+        <v>2701</v>
       </c>
       <c r="H98" s="0" t="s">
-        <v>2360</v>
+        <v>2702</v>
       </c>
       <c r="I98" s="0" t="s">
-        <v>2361</v>
+        <v>2703</v>
       </c>
       <c r="J98" s="0" t="s">
-        <v>2362</v>
+        <v>2704</v>
       </c>
       <c r="K98" s="0" t="s">
-        <v>2363</v>
+        <v>2705</v>
       </c>
       <c r="L98" s="0" t="s">
-        <v>2364</v>
+        <v>2706</v>
       </c>
       <c r="M98" s="0" t="s">
-        <v>2365</v>
+        <v>2707</v>
       </c>
       <c r="N98" s="0">
         <v>2</v>
       </c>
       <c r="O98" s="0" t="s">
-        <v>2366</v>
+        <v>2708</v>
       </c>
       <c r="P98" s="0">
         <v>0.20000000000000001</v>
       </c>
       <c r="Q98" s="0" t="s">
-        <v>2367</v>
+        <v>2709</v>
       </c>
       <c r="R98" s="0" t="s">
-        <v>2368</v>
+        <v>2710</v>
       </c>
       <c r="S98" s="0" t="s">
-        <v>2369</v>
+        <v>2711</v>
       </c>
       <c r="T98" s="0"/>
       <c r="U98" s="0" t="s">
-        <v>2370</v>
+        <v>2712</v>
       </c>
       <c r="V98" s="0" t="s">
-        <v>2371</v>
+        <v>2713</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" s="0" t="s">
-        <v>2408</v>
+        <v>2768</v>
       </c>
       <c r="B99" s="0" t="s">
-        <v>2409</v>
+        <v>2769</v>
       </c>
       <c r="C99" s="0" t="s">
-        <v>2410</v>
+        <v>2770</v>
       </c>
       <c r="D99" s="0" t="s">
-        <v>2411</v>
+        <v>2771</v>
       </c>
       <c r="E99" s="0" t="s">
-        <v>2412</v>
+        <v>2772</v>
       </c>
       <c r="F99" s="0">
         <v>4</v>
       </c>
       <c r="G99" s="0" t="s">
-        <v>2413</v>
+        <v>2773</v>
       </c>
       <c r="H99" s="0" t="s">
-        <v>2414</v>
+        <v>2774</v>
       </c>
       <c r="I99" s="0" t="s">
-        <v>2415</v>
+        <v>2775</v>
       </c>
       <c r="J99" s="0" t="s">
-        <v>2416</v>
+        <v>2776</v>
       </c>
       <c r="K99" s="0" t="s">
-        <v>2417</v>
+        <v>2777</v>
       </c>
       <c r="L99" s="0" t="s">
-        <v>2418</v>
+        <v>2778</v>
       </c>
       <c r="M99" s="0" t="s">
-        <v>2419</v>
+        <v>2779</v>
       </c>
       <c r="N99" s="0">
         <v>4</v>
       </c>
       <c r="O99" s="0" t="s">
-        <v>2420</v>
+        <v>2780</v>
       </c>
       <c r="P99" s="0">
         <v>1</v>
       </c>
       <c r="Q99" s="0" t="s">
-        <v>2421</v>
+        <v>2781</v>
       </c>
       <c r="R99" s="0" t="s">
-        <v>2422</v>
+        <v>2782</v>
       </c>
       <c r="S99" s="0" t="s">
-        <v>2423</v>
+        <v>2783</v>
       </c>
       <c r="T99" s="0"/>
       <c r="U99" s="0" t="s">
-        <v>2424</v>
+        <v>2784</v>
       </c>
       <c r="V99" s="0" t="s">
-        <v>2425</v>
+        <v>2785</v>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" s="0" t="s">
+        <v>2534</v>
+      </c>
+      <c r="B100" s="0" t="s">
+        <v>2535</v>
+      </c>
+      <c r="C100" s="0" t="s">
+        <v>2536</v>
+      </c>
+      <c r="D100" s="0" t="s">
+        <v>2537</v>
+      </c>
+      <c r="E100" s="0" t="s">
+        <v>2538</v>
+      </c>
+      <c r="F100" s="0">
+        <v>4</v>
+      </c>
+      <c r="G100" s="0" t="s">
+        <v>2539</v>
+      </c>
+      <c r="H100" s="0" t="s">
+        <v>2540</v>
+      </c>
+      <c r="I100" s="0" t="s">
+        <v>2541</v>
+      </c>
+      <c r="J100" s="0" t="s">
+        <v>2542</v>
+      </c>
+      <c r="K100" s="0" t="s">
+        <v>2543</v>
+      </c>
+      <c r="L100" s="0" t="s">
+        <v>2544</v>
+      </c>
+      <c r="M100" s="0" t="s">
+        <v>2545</v>
+      </c>
+      <c r="N100" s="0">
+        <v>2</v>
+      </c>
+      <c r="O100" s="0" t="s">
+        <v>2546</v>
+      </c>
+      <c r="P100" s="0">
+        <v>0.20000000000000001</v>
+      </c>
+      <c r="Q100" s="0" t="s">
+        <v>2547</v>
+      </c>
+      <c r="R100" s="0" t="s">
+        <v>2548</v>
+      </c>
+      <c r="S100" s="0" t="s">
+        <v>2549</v>
+      </c>
+      <c r="T100" s="0"/>
+      <c r="U100" s="0" t="s">
+        <v>2550</v>
+      </c>
+      <c r="V100" s="0" t="s">
+        <v>2551</v>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" s="0" t="s">
+        <v>2624</v>
+      </c>
+      <c r="B101" s="0" t="s">
+        <v>2625</v>
+      </c>
+      <c r="C101" s="0" t="s">
+        <v>2626</v>
+      </c>
+      <c r="D101" s="0" t="s">
+        <v>2627</v>
+      </c>
+      <c r="E101" s="0" t="s">
+        <v>2628</v>
+      </c>
+      <c r="F101" s="0">
+        <v>4</v>
+      </c>
+      <c r="G101" s="0" t="s">
+        <v>2629</v>
+      </c>
+      <c r="H101" s="0" t="s">
+        <v>2630</v>
+      </c>
+      <c r="I101" s="0" t="s">
+        <v>2631</v>
+      </c>
+      <c r="J101" s="0" t="s">
+        <v>2632</v>
+      </c>
+      <c r="K101" s="0" t="s">
+        <v>2633</v>
+      </c>
+      <c r="L101" s="0" t="s">
+        <v>2634</v>
+      </c>
+      <c r="M101" s="0" t="s">
+        <v>2635</v>
+      </c>
+      <c r="N101" s="0">
+        <v>2</v>
+      </c>
+      <c r="O101" s="0" t="s">
+        <v>2636</v>
+      </c>
+      <c r="P101" s="0">
+        <v>0.20000000000000001</v>
+      </c>
+      <c r="Q101" s="0" t="s">
+        <v>2637</v>
+      </c>
+      <c r="R101" s="0" t="s">
+        <v>2638</v>
+      </c>
+      <c r="S101" s="0" t="s">
+        <v>2639</v>
+      </c>
+      <c r="T101" s="0"/>
+      <c r="U101" s="0" t="s">
+        <v>2640</v>
+      </c>
+      <c r="V101" s="0" t="s">
+        <v>2641</v>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" s="0" t="s">
+        <v>2660</v>
+      </c>
+      <c r="B102" s="0" t="s">
+        <v>2661</v>
+      </c>
+      <c r="C102" s="0" t="s">
+        <v>2662</v>
+      </c>
+      <c r="D102" s="0" t="s">
+        <v>2663</v>
+      </c>
+      <c r="E102" s="0" t="s">
+        <v>2664</v>
+      </c>
+      <c r="F102" s="0">
+        <v>4</v>
+      </c>
+      <c r="G102" s="0" t="s">
+        <v>2665</v>
+      </c>
+      <c r="H102" s="0" t="s">
+        <v>2666</v>
+      </c>
+      <c r="I102" s="0" t="s">
+        <v>2667</v>
+      </c>
+      <c r="J102" s="0" t="s">
+        <v>2668</v>
+      </c>
+      <c r="K102" s="0" t="s">
+        <v>2669</v>
+      </c>
+      <c r="L102" s="0" t="s">
+        <v>2670</v>
+      </c>
+      <c r="M102" s="0" t="s">
+        <v>2671</v>
+      </c>
+      <c r="N102" s="0">
+        <v>2</v>
+      </c>
+      <c r="O102" s="0" t="s">
+        <v>2672</v>
+      </c>
+      <c r="P102" s="0">
+        <v>0.20000000000000001</v>
+      </c>
+      <c r="Q102" s="0" t="s">
+        <v>2673</v>
+      </c>
+      <c r="R102" s="0" t="s">
+        <v>2674</v>
+      </c>
+      <c r="S102" s="0" t="s">
+        <v>2675</v>
+      </c>
+      <c r="T102" s="0"/>
+      <c r="U102" s="0" t="s">
+        <v>2676</v>
+      </c>
+      <c r="V102" s="0" t="s">
+        <v>2677</v>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" s="0" t="s">
+        <v>2750</v>
+      </c>
+      <c r="B103" s="0" t="s">
+        <v>2751</v>
+      </c>
+      <c r="C103" s="0" t="s">
+        <v>2752</v>
+      </c>
+      <c r="D103" s="0" t="s">
+        <v>2753</v>
+      </c>
+      <c r="E103" s="0" t="s">
+        <v>2754</v>
+      </c>
+      <c r="F103" s="0">
+        <v>4</v>
+      </c>
+      <c r="G103" s="0" t="s">
+        <v>2755</v>
+      </c>
+      <c r="H103" s="0" t="s">
+        <v>2756</v>
+      </c>
+      <c r="I103" s="0" t="s">
+        <v>2757</v>
+      </c>
+      <c r="J103" s="0" t="s">
+        <v>2758</v>
+      </c>
+      <c r="K103" s="0" t="s">
+        <v>2759</v>
+      </c>
+      <c r="L103" s="0" t="s">
+        <v>2760</v>
+      </c>
+      <c r="M103" s="0" t="s">
+        <v>2761</v>
+      </c>
+      <c r="N103" s="0">
+        <v>2</v>
+      </c>
+      <c r="O103" s="0" t="s">
+        <v>2762</v>
+      </c>
+      <c r="P103" s="0">
+        <v>0.20000000000000001</v>
+      </c>
+      <c r="Q103" s="0" t="s">
+        <v>2763</v>
+      </c>
+      <c r="R103" s="0" t="s">
+        <v>2764</v>
+      </c>
+      <c r="S103" s="0" t="s">
+        <v>2765</v>
+      </c>
+      <c r="T103" s="0"/>
+      <c r="U103" s="0" t="s">
+        <v>2766</v>
+      </c>
+      <c r="V103" s="0" t="s">
+        <v>2767</v>
       </c>
     </row>
   </sheetData>

--- a/config/becExpConfig/becExpType.csv.xlsx
+++ b/config/becExpConfig/becExpType.csv.xlsx
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3053" uniqueCount="2786">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3341" uniqueCount="3074">
   <si>
     <t>TrialName</t>
   </si>
@@ -8385,6 +8385,870 @@
   </si>
   <si>
     <t>WaveformGeneratorName,LatticeMod,XvWingMod;ChannelName,Ch2,Ch1;WaveformListName,PdAi,XvWingLatticeCC</t>
+  </si>
+  <si>
+    <t>PhaseLockName,ImagingLock;Frequency,700000000;VariableName,hw_ImagingNi</t>
+  </si>
+  <si>
+    <t>NiLatticeCCXvLatticeBm</t>
+  </si>
+  <si>
+    <t>An experiment at the non-interacting lattice stage. Scan xvlattice. With band mapping.</t>
+  </si>
+  <si>
+    <t>TOP</t>
+  </si>
+  <si>
+    <t>NiLatticeCCPdTof4000</t>
+  </si>
+  <si>
+    <t>None</t>
+  </si>
+  <si>
+    <t>hw_XvLatticeCC</t>
+  </si>
+  <si>
+    <t>DensityFit;AtomNumber</t>
+  </si>
+  <si>
+    <t>LSR</t>
+  </si>
+  <si>
+    <t>[353 1231;517 1162;1370 1128;1605 1136;1657 1227;1628 1333;1262 1362;668 1384;385 1392;364 1330]</t>
+  </si>
+  <si>
+    <t>HF</t>
+  </si>
+  <si>
+    <t>Absorption</t>
+  </si>
+  <si>
+    <t>StrongLight</t>
+  </si>
+  <si>
+    <t>BosonicGaussianFit1D</t>
+  </si>
+  <si>
+    <t>None</t>
+  </si>
+  <si>
+    <t>LinearFit1D</t>
+  </si>
+  <si>
+    <t>StdErr</t>
+  </si>
+  <si>
+    <t>WaveformGeneratorName,LatticeMod,XvWingMod;ChannelName,Ch2,Ch1;WaveformListName,PdAi,XvWingLatticeCC</t>
+  </si>
+  <si>
+    <t>PhaseLockName,ImagingLock;Frequency,700000000;VariableName,hw_ImagingNi</t>
+  </si>
+  <si>
+    <t>NiLatticeCCPdModDepthBm</t>
+  </si>
+  <si>
+    <t>An experiment at the non-interacting lattice stage. Scan xvlattice. With band mapping.</t>
+  </si>
+  <si>
+    <t>TOP</t>
+  </si>
+  <si>
+    <t>NiLatticeCCPdTof4000</t>
+  </si>
+  <si>
+    <t>None</t>
+  </si>
+  <si>
+    <t>hw_PdModDepth</t>
+  </si>
+  <si>
+    <t>DensityFit;AtomNumber</t>
+  </si>
+  <si>
+    <t>LSR</t>
+  </si>
+  <si>
+    <t>[353 1231;517 1162;1370 1128;1605 1136;1657 1227;1628 1333;1262 1362;668 1384;385 1392;364 1330]</t>
+  </si>
+  <si>
+    <t>HF</t>
+  </si>
+  <si>
+    <t>Absorption</t>
+  </si>
+  <si>
+    <t>StrongLight</t>
+  </si>
+  <si>
+    <t>BosonicGaussianFit1D</t>
+  </si>
+  <si>
+    <t>None</t>
+  </si>
+  <si>
+    <t>LinearFit1D</t>
+  </si>
+  <si>
+    <t>StdErr</t>
+  </si>
+  <si>
+    <t>WaveformGeneratorName,LatticeMod,XvWingMod;ChannelName,Ch2,Ch1;WaveformListName,PdAi,XvWingLatticeCC</t>
+  </si>
+  <si>
+    <t>PhaseLockName,ImagingLock;Frequency,700000000;VariableName,hw_ImagingNi</t>
+  </si>
+  <si>
+    <t>NiLatticeCCBo</t>
+  </si>
+  <si>
+    <t>A Bloch oscillation experiment at the non-interacting lattice stage. With band mapping.</t>
+  </si>
+  <si>
+    <t>TOP</t>
+  </si>
+  <si>
+    <t>NiLattice</t>
+  </si>
+  <si>
+    <t>None</t>
+  </si>
+  <si>
+    <t>latticehold</t>
+  </si>
+  <si>
+    <t>DensityFit;AtomNumber;CenterFit</t>
+  </si>
+  <si>
+    <t>LSR</t>
+  </si>
+  <si>
+    <t>[784 1265;854 1223;1012 1216;1153 1216;1229 1282;1216 1360;1128 1373;965 1380;834 1382;786 1340]</t>
+  </si>
+  <si>
+    <t>HF</t>
+  </si>
+  <si>
+    <t>Absorption</t>
+  </si>
+  <si>
+    <t>StrongLight</t>
+  </si>
+  <si>
+    <t>BosonicGaussianFit1D</t>
+  </si>
+  <si>
+    <t>None</t>
+  </si>
+  <si>
+    <t>TriangleFit1D</t>
+  </si>
+  <si>
+    <t>StdErr</t>
+  </si>
+  <si>
+    <t>WaveformGeneratorName,XvWingMod;ChannelName,Ch1;WaveformListName,XvWingLatticeCC</t>
+  </si>
+  <si>
+    <t>PhaseLockName,ImagingLock;Frequency,700000000;VariableName,hw_ImagingNi</t>
+  </si>
+  <si>
+    <t>NiLatticeCCPdPulsePhaseBm</t>
+  </si>
+  <si>
+    <t>An experiment at the non-interacting lattice stage. Scan xvlattice. With band mapping.</t>
+  </si>
+  <si>
+    <t>TOP</t>
+  </si>
+  <si>
+    <t>NiLatticeCCPdTof4000</t>
+  </si>
+  <si>
+    <t>None</t>
+  </si>
+  <si>
+    <t>hw_PdModPhase</t>
+  </si>
+  <si>
+    <t>DensityFit;AtomNumber</t>
+  </si>
+  <si>
+    <t>LSR</t>
+  </si>
+  <si>
+    <t>[353 1231;517 1162;1370 1128;1605 1136;1657 1227;1628 1333;1262 1362;668 1384;385 1392;364 1330]</t>
+  </si>
+  <si>
+    <t>HF</t>
+  </si>
+  <si>
+    <t>Absorption</t>
+  </si>
+  <si>
+    <t>StrongLight</t>
+  </si>
+  <si>
+    <t>BosonicGaussianFit1D</t>
+  </si>
+  <si>
+    <t>None</t>
+  </si>
+  <si>
+    <t>LinearFit1D</t>
+  </si>
+  <si>
+    <t>StdErr</t>
+  </si>
+  <si>
+    <t>WaveformGeneratorName,LatticeMod,XvWingMod;ChannelName,Ch2,Ch1;WaveformListName,PdAi,XvWingLatticeCC</t>
+  </si>
+  <si>
+    <t>PhaseLockName,ImagingLock;Frequency,700000000;VariableName,hw_ImagingNi</t>
+  </si>
+  <si>
+    <t>NiLatticeCCPdPulsePhaseBm</t>
+  </si>
+  <si>
+    <t>An experiment at the non-interacting lattice stage. Scan xvlattice. With band mapping.</t>
+  </si>
+  <si>
+    <t>TOP</t>
+  </si>
+  <si>
+    <t>NiLatticeCCPdTof4000</t>
+  </si>
+  <si>
+    <t>None</t>
+  </si>
+  <si>
+    <t>hw_PdModPhase</t>
+  </si>
+  <si>
+    <t>DensityFit;AtomNumber</t>
+  </si>
+  <si>
+    <t>LSR</t>
+  </si>
+  <si>
+    <t>[353 1231;517 1162;1370 1128;1605 1136;1657 1227;1628 1333;1262 1362;668 1384;385 1392;364 1330]</t>
+  </si>
+  <si>
+    <t>HF</t>
+  </si>
+  <si>
+    <t>Absorption</t>
+  </si>
+  <si>
+    <t>StrongLight</t>
+  </si>
+  <si>
+    <t>BosonicGaussianFit1D</t>
+  </si>
+  <si>
+    <t>None</t>
+  </si>
+  <si>
+    <t>LinearFit1D</t>
+  </si>
+  <si>
+    <t>StdErr</t>
+  </si>
+  <si>
+    <t>WaveformGeneratorName,LatticeMod,XvWingMod;ChannelName,Ch2,Ch1;WaveformListName,PdAiPulse,XvWingLatticeCC</t>
+  </si>
+  <si>
+    <t>PhaseLockName,ImagingLock;Frequency,700000000;VariableName,hw_ImagingNi</t>
+  </si>
+  <si>
+    <t>NiLatticeCCBoBm</t>
+  </si>
+  <si>
+    <t>A Bloch oscillation experiment at the non-interacting lattice stage. With band mapping.</t>
+  </si>
+  <si>
+    <t>TOP</t>
+  </si>
+  <si>
+    <t>NiLatticeCCBoBmTof4000</t>
+  </si>
+  <si>
+    <t>None</t>
+  </si>
+  <si>
+    <t>latticehold</t>
+  </si>
+  <si>
+    <t>DensityFit;AtomNumber;CenterFit</t>
+  </si>
+  <si>
+    <t>LSR</t>
+  </si>
+  <si>
+    <t>[784 1265;854 1223;1012 1216;1153 1216;1229 1282;1216 1360;1128 1373;965 1380;834 1382;786 1340]</t>
+  </si>
+  <si>
+    <t>HF</t>
+  </si>
+  <si>
+    <t>Absorption</t>
+  </si>
+  <si>
+    <t>StrongLight</t>
+  </si>
+  <si>
+    <t>BosonicGaussianFit1D</t>
+  </si>
+  <si>
+    <t>None</t>
+  </si>
+  <si>
+    <t>TriangleFit1D</t>
+  </si>
+  <si>
+    <t>StdErr</t>
+  </si>
+  <si>
+    <t>WaveformGeneratorName,XvWingMod;ChannelName,Ch1;WaveformListName,XvWingLatticeCC</t>
+  </si>
+  <si>
+    <t>PhaseLockName,ImagingLock;Frequency,700000000;VariableName,hw_ImagingNi</t>
+  </si>
+  <si>
+    <t>NiLatticeCcFullBoXvLatticeBm</t>
+  </si>
+  <si>
+    <t>An experiment at the non-interacting lattice stage. Scan xvlattice. With band mapping.</t>
+  </si>
+  <si>
+    <t>TOP</t>
+  </si>
+  <si>
+    <t>NiLatticeCCPdTof4000</t>
+  </si>
+  <si>
+    <t>None</t>
+  </si>
+  <si>
+    <t>hw_XvLattice</t>
+  </si>
+  <si>
+    <t>DensityFit;AtomNumber</t>
+  </si>
+  <si>
+    <t>LSR</t>
+  </si>
+  <si>
+    <t>[353 1231;517 1162;1370 1128;1605 1136;1657 1227;1628 1333;1262 1362;668 1384;385 1392;364 1330]</t>
+  </si>
+  <si>
+    <t>HF</t>
+  </si>
+  <si>
+    <t>Absorption</t>
+  </si>
+  <si>
+    <t>StrongLight</t>
+  </si>
+  <si>
+    <t>BosonicGaussianFit1D</t>
+  </si>
+  <si>
+    <t>None</t>
+  </si>
+  <si>
+    <t>LinearFit1D</t>
+  </si>
+  <si>
+    <t>StdErr</t>
+  </si>
+  <si>
+    <t>WaveformGeneratorName,LatticeMod,XvWingMod;ChannelName,Ch2,Ch1;WaveformListName,PdAiPulseFullBo,XvWingLatticeCC</t>
+  </si>
+  <si>
+    <t>PhaseLockName,ImagingLock;Frequency,700000000;VariableName,hw_ImagingNi</t>
+  </si>
+  <si>
+    <t>NiLatticeCcFullBoXvLatticeBm</t>
+  </si>
+  <si>
+    <t>An experiment at the non-interacting lattice stage. Scan xvlattice. With band mapping.</t>
+  </si>
+  <si>
+    <t>TOP</t>
+  </si>
+  <si>
+    <t>NiLatticeCCFulBoPdTof4000</t>
+  </si>
+  <si>
+    <t>None</t>
+  </si>
+  <si>
+    <t>hw_XvLatticeCC</t>
+  </si>
+  <si>
+    <t>DensityFit;AtomNumber</t>
+  </si>
+  <si>
+    <t>LSR</t>
+  </si>
+  <si>
+    <t>[353 1231;517 1162;1370 1128;1605 1136;1657 1227;1628 1333;1262 1362;668 1384;385 1392;364 1330]</t>
+  </si>
+  <si>
+    <t>HF</t>
+  </si>
+  <si>
+    <t>Absorption</t>
+  </si>
+  <si>
+    <t>StrongLight</t>
+  </si>
+  <si>
+    <t>BosonicGaussianFit1D</t>
+  </si>
+  <si>
+    <t>None</t>
+  </si>
+  <si>
+    <t>LinearFit1D</t>
+  </si>
+  <si>
+    <t>StdErr</t>
+  </si>
+  <si>
+    <t>WaveformGeneratorName,LatticeMod,XvWingMod;ChannelName,Ch2,Ch1;WaveformListName,PdAiPulseFullBo,XvWingLatticeCC</t>
+  </si>
+  <si>
+    <t>PhaseLockName,ImagingLock;Frequency,700000000;VariableName,hw_ImagingNi</t>
+  </si>
+  <si>
+    <t>NiLatticeCCFullBoPdModDepthBm</t>
+  </si>
+  <si>
+    <t>An experiment at the non-interacting lattice stage. Scan xvlattice. With band mapping.</t>
+  </si>
+  <si>
+    <t>TOP</t>
+  </si>
+  <si>
+    <t>NiLatticeCCFulBoPdTof4000</t>
+  </si>
+  <si>
+    <t>None</t>
+  </si>
+  <si>
+    <t>hw_PdModDepth2</t>
+  </si>
+  <si>
+    <t>DensityFit;AtomNumber</t>
+  </si>
+  <si>
+    <t>LSR</t>
+  </si>
+  <si>
+    <t>[353 1231;517 1162;1370 1128;1605 1136;1657 1227;1628 1333;1262 1362;668 1384;385 1392;364 1330]</t>
+  </si>
+  <si>
+    <t>HF</t>
+  </si>
+  <si>
+    <t>Absorption</t>
+  </si>
+  <si>
+    <t>StrongLight</t>
+  </si>
+  <si>
+    <t>BosonicGaussianFit1D</t>
+  </si>
+  <si>
+    <t>None</t>
+  </si>
+  <si>
+    <t>LinearFit1D</t>
+  </si>
+  <si>
+    <t>StdErr</t>
+  </si>
+  <si>
+    <t>WaveformGeneratorName,LatticeMod,XvWingMod;ChannelName,Ch2,Ch1;WaveformListName,PdAi,XvWingLatticeCC</t>
+  </si>
+  <si>
+    <t>PhaseLockName,ImagingLock;Frequency,700000000;VariableName,hw_ImagingNi</t>
+  </si>
+  <si>
+    <t>NiLatticeCCFullBoPdModDepthBm</t>
+  </si>
+  <si>
+    <t>An experiment at the non-interacting lattice stage. Scan xvlattice. With band mapping.</t>
+  </si>
+  <si>
+    <t>TOP</t>
+  </si>
+  <si>
+    <t>NiLatticeCCFulBoPdTof4000</t>
+  </si>
+  <si>
+    <t>None</t>
+  </si>
+  <si>
+    <t>hw_PdModDepth2</t>
+  </si>
+  <si>
+    <t>DensityFit;AtomNumber</t>
+  </si>
+  <si>
+    <t>LSR</t>
+  </si>
+  <si>
+    <t>[353 1231;517 1162;1370 1128;1605 1136;1657 1227;1628 1333;1262 1362;668 1384;385 1392;364 1330]</t>
+  </si>
+  <si>
+    <t>HF</t>
+  </si>
+  <si>
+    <t>Absorption</t>
+  </si>
+  <si>
+    <t>StrongLight</t>
+  </si>
+  <si>
+    <t>BosonicGaussianFit1D</t>
+  </si>
+  <si>
+    <t>None</t>
+  </si>
+  <si>
+    <t>LinearFit1D</t>
+  </si>
+  <si>
+    <t>StdErr</t>
+  </si>
+  <si>
+    <t>WaveformGeneratorName,LatticeMod,XvWingMod;ChannelName,Ch2,Ch1;WaveformListName,PdAiPulseFullBo,XvWingLatticeCC</t>
+  </si>
+  <si>
+    <t>PhaseLockName,ImagingLock;Frequency,700000000;VariableName,hw_ImagingNi</t>
+  </si>
+  <si>
+    <t>NiLatticeCcFullBoPdKp2vva</t>
+  </si>
+  <si>
+    <t>An experiment at the non-interacting lattice stage. Scan xvlattice. With band mapping.</t>
+  </si>
+  <si>
+    <t>TOP</t>
+  </si>
+  <si>
+    <t>NiLatticeCCFulBoPdTof4000</t>
+  </si>
+  <si>
+    <t>None</t>
+  </si>
+  <si>
+    <t>KP2VVA</t>
+  </si>
+  <si>
+    <t>DensityFit;AtomNumber</t>
+  </si>
+  <si>
+    <t>LSR</t>
+  </si>
+  <si>
+    <t>[353 1231;517 1162;1370 1128;1605 1136;1657 1227;1628 1333;1262 1362;668 1384;385 1392;364 1330]</t>
+  </si>
+  <si>
+    <t>HF</t>
+  </si>
+  <si>
+    <t>Absorption</t>
+  </si>
+  <si>
+    <t>StrongLight</t>
+  </si>
+  <si>
+    <t>BosonicGaussianFit1D</t>
+  </si>
+  <si>
+    <t>None</t>
+  </si>
+  <si>
+    <t>LinearFit1D</t>
+  </si>
+  <si>
+    <t>StdErr</t>
+  </si>
+  <si>
+    <t>WaveformGeneratorName,LatticeMod,XvWingMod;ChannelName,Ch2,Ch1;WaveformListName,PdAiPulseFullBo,XvWingLatticeCC</t>
+  </si>
+  <si>
+    <t>PhaseLockName,ImagingLock;Frequency,700000000;VariableName,hw_ImagingNi</t>
+  </si>
+  <si>
+    <t>NiLatticeCcFullBoXvLatticeBm</t>
+  </si>
+  <si>
+    <t>An experiment at the non-interacting lattice stage. Scan xvlattice. With band mapping.</t>
+  </si>
+  <si>
+    <t>TOP</t>
+  </si>
+  <si>
+    <t>NiLatticeCCFulBoPdTof4000</t>
+  </si>
+  <si>
+    <t>None</t>
+  </si>
+  <si>
+    <t>hw_XvLatticeCC</t>
+  </si>
+  <si>
+    <t>DensityFit;AtomNumber</t>
+  </si>
+  <si>
+    <t>LSR</t>
+  </si>
+  <si>
+    <t>[626 1259;693 1230;1137 1199;1250 1219;1280 1311;1238 1369;1102 1379;727 1376;625 1358]</t>
+  </si>
+  <si>
+    <t>HF</t>
+  </si>
+  <si>
+    <t>Absorption</t>
+  </si>
+  <si>
+    <t>StrongLight</t>
+  </si>
+  <si>
+    <t>BosonicGaussianFit1D</t>
+  </si>
+  <si>
+    <t>None</t>
+  </si>
+  <si>
+    <t>LinearFit1D</t>
+  </si>
+  <si>
+    <t>StdErr</t>
+  </si>
+  <si>
+    <t>WaveformGeneratorName,LatticeMod,XvWingMod;ChannelName,Ch2,Ch1;WaveformListName,PdAiPulseFullBo,XvWingLatticeCC</t>
+  </si>
+  <si>
+    <t>PhaseLockName,ImagingLock;Frequency,700000000;VariableName,hw_ImagingNi</t>
+  </si>
+  <si>
+    <t>NiLatticeCCBo</t>
+  </si>
+  <si>
+    <t>A Bloch oscillation experiment at the non-interacting lattice stage. With band mapping.</t>
+  </si>
+  <si>
+    <t>TOP</t>
+  </si>
+  <si>
+    <t>NiLattice</t>
+  </si>
+  <si>
+    <t>None</t>
+  </si>
+  <si>
+    <t>latticehold</t>
+  </si>
+  <si>
+    <t>DensityFit;AtomNumber;CenterFit</t>
+  </si>
+  <si>
+    <t>LSR</t>
+  </si>
+  <si>
+    <t>[784 1265;854 1223;1012 1216;1153 1216;1229 1282;1216 1360;1128 1373;965 1380;834 1382;786 1340]</t>
+  </si>
+  <si>
+    <t>HF</t>
+  </si>
+  <si>
+    <t>Absorption</t>
+  </si>
+  <si>
+    <t>StrongLight</t>
+  </si>
+  <si>
+    <t>BosonicGaussianFit1D</t>
+  </si>
+  <si>
+    <t>None</t>
+  </si>
+  <si>
+    <t>SineFit1D</t>
+  </si>
+  <si>
+    <t>StdErr</t>
+  </si>
+  <si>
+    <t>WaveformGeneratorName,XvWingMod;ChannelName,Ch1;WaveformListName,XvWingLatticeCC</t>
+  </si>
+  <si>
+    <t>PhaseLockName,ImagingLock;Frequency,700000000;VariableName,hw_ImagingNi</t>
+  </si>
+  <si>
+    <t>NiLatticeCcPdKP2VVA</t>
+  </si>
+  <si>
+    <t>An experiment at the non-interacting lattice stage. Scan KP2VVA.</t>
+  </si>
+  <si>
+    <t>TOP</t>
+  </si>
+  <si>
+    <t>NiLatticeCCPdTof4000</t>
+  </si>
+  <si>
+    <t>None</t>
+  </si>
+  <si>
+    <t>KP2VVA</t>
+  </si>
+  <si>
+    <t>DensityFit;AtomNumber</t>
+  </si>
+  <si>
+    <t>LSR</t>
+  </si>
+  <si>
+    <t>[448 1248;586 1199;1165 1188;1275 1220;1276 1348;1184 1392;766 1405;541 1407;452 1365]</t>
+  </si>
+  <si>
+    <t>HF</t>
+  </si>
+  <si>
+    <t>Absorption</t>
+  </si>
+  <si>
+    <t>StrongLight</t>
+  </si>
+  <si>
+    <t>BosonicGaussianFit1D</t>
+  </si>
+  <si>
+    <t>None</t>
+  </si>
+  <si>
+    <t>ParabolicFit1D</t>
+  </si>
+  <si>
+    <t>StdErr</t>
+  </si>
+  <si>
+    <t>WaveformGeneratorName,LatticeMod,XvWingMod;ChannelName,Ch2,Ch1;WaveformListName,PdAi,XvWingLatticeCC</t>
+  </si>
+  <si>
+    <t>PhaseLockName,ImagingLock;Frequency,700000000;VariableName,hw_ImagingNi</t>
+  </si>
+  <si>
+    <t>NiLatticeCCBm</t>
+  </si>
+  <si>
+    <t>A Bloch oscillation experiment at the non-interacting lattice stage. With band mapping.</t>
+  </si>
+  <si>
+    <t>TOP</t>
+  </si>
+  <si>
+    <t>NiLattice</t>
+  </si>
+  <si>
+    <t>None</t>
+  </si>
+  <si>
+    <t>latticehold</t>
+  </si>
+  <si>
+    <t>DensityFit;AtomNumber;CenterFit</t>
+  </si>
+  <si>
+    <t>LSR</t>
+  </si>
+  <si>
+    <t>[784 1265;854 1223;1012 1216;1153 1216;1229 1282;1216 1360;1128 1373;965 1380;834 1382;786 1340]</t>
+  </si>
+  <si>
+    <t>HF</t>
+  </si>
+  <si>
+    <t>Absorption</t>
+  </si>
+  <si>
+    <t>StrongLight</t>
+  </si>
+  <si>
+    <t>BosonicGaussianFit1D</t>
+  </si>
+  <si>
+    <t>None</t>
+  </si>
+  <si>
+    <t>SineFit1D</t>
+  </si>
+  <si>
+    <t>StdErr</t>
+  </si>
+  <si>
+    <t>WaveformGeneratorName,XvWingMod;ChannelName,Ch1;WaveformListName,XvWingLatticeCC</t>
+  </si>
+  <si>
+    <t>PhaseLockName,ImagingLock;Frequency,700000000;VariableName,hw_ImagingNi</t>
+  </si>
+  <si>
+    <t>NiLatticeCCBm</t>
+  </si>
+  <si>
+    <t>A Bloch oscillation experiment at the non-interacting lattice stage. With band mapping.</t>
+  </si>
+  <si>
+    <t>TOP</t>
+  </si>
+  <si>
+    <t>NiLatticeCCBoBmTof4000</t>
+  </si>
+  <si>
+    <t>None</t>
+  </si>
+  <si>
+    <t>latticehold</t>
+  </si>
+  <si>
+    <t>DensityFit;AtomNumber;CenterFit</t>
+  </si>
+  <si>
+    <t>LSR</t>
+  </si>
+  <si>
+    <t>[784 1265;854 1223;1012 1216;1153 1216;1229 1282;1216 1360;1128 1373;965 1380;834 1382;786 1340]</t>
+  </si>
+  <si>
+    <t>HF</t>
+  </si>
+  <si>
+    <t>Absorption</t>
+  </si>
+  <si>
+    <t>StrongLight</t>
+  </si>
+  <si>
+    <t>BosonicGaussianFit1D</t>
+  </si>
+  <si>
+    <t>None</t>
+  </si>
+  <si>
+    <t>SineFit1D</t>
+  </si>
+  <si>
+    <t>StdErr</t>
+  </si>
+  <si>
+    <t>WaveformGeneratorName,XvWingMod;ChannelName,Ch1;WaveformListName,XvWingLatticeCC</t>
   </si>
   <si>
     <t>PhaseLockName,ImagingLock;Frequency,700000000;VariableName,hw_ImagingNi</t>
@@ -8714,7 +9578,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:V103"/>
+  <dimension ref="A1:V111"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="36.42578125" customWidth="true"/>
@@ -8737,7 +9601,7 @@
     <col min="18" max="18" width="16.42578125" customWidth="true"/>
     <col min="19" max="19" width="17" customWidth="true"/>
     <col min="20" max="20" width="16.85546875" customWidth="true"/>
-    <col min="21" max="21" width="113.7109375" customWidth="true"/>
+    <col min="21" max="21" width="116" customWidth="true"/>
     <col min="22" max="22" width="73.5703125" customWidth="true"/>
   </cols>
   <sheetData>
@@ -14700,134 +15564,134 @@
     </row>
     <row r="98">
       <c r="A98" s="0" t="s">
-        <v>2696</v>
+        <v>2876</v>
       </c>
       <c r="B98" s="0" t="s">
-        <v>2697</v>
+        <v>2877</v>
       </c>
       <c r="C98" s="0" t="s">
-        <v>2698</v>
+        <v>2878</v>
       </c>
       <c r="D98" s="0" t="s">
-        <v>2699</v>
+        <v>2879</v>
       </c>
       <c r="E98" s="0" t="s">
-        <v>2700</v>
+        <v>2880</v>
       </c>
       <c r="F98" s="0">
         <v>4</v>
       </c>
       <c r="G98" s="0" t="s">
-        <v>2701</v>
+        <v>2881</v>
       </c>
       <c r="H98" s="0" t="s">
-        <v>2702</v>
+        <v>2882</v>
       </c>
       <c r="I98" s="0" t="s">
-        <v>2703</v>
+        <v>2883</v>
       </c>
       <c r="J98" s="0" t="s">
-        <v>2704</v>
+        <v>2884</v>
       </c>
       <c r="K98" s="0" t="s">
-        <v>2705</v>
+        <v>2885</v>
       </c>
       <c r="L98" s="0" t="s">
-        <v>2706</v>
+        <v>2886</v>
       </c>
       <c r="M98" s="0" t="s">
-        <v>2707</v>
+        <v>2887</v>
       </c>
       <c r="N98" s="0">
         <v>2</v>
       </c>
       <c r="O98" s="0" t="s">
-        <v>2708</v>
+        <v>2888</v>
       </c>
       <c r="P98" s="0">
         <v>0.20000000000000001</v>
       </c>
       <c r="Q98" s="0" t="s">
-        <v>2709</v>
+        <v>2889</v>
       </c>
       <c r="R98" s="0" t="s">
-        <v>2710</v>
+        <v>2890</v>
       </c>
       <c r="S98" s="0" t="s">
-        <v>2711</v>
+        <v>2891</v>
       </c>
       <c r="T98" s="0"/>
       <c r="U98" s="0" t="s">
-        <v>2712</v>
+        <v>2892</v>
       </c>
       <c r="V98" s="0" t="s">
-        <v>2713</v>
+        <v>2893</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" s="0" t="s">
-        <v>2768</v>
+        <v>2786</v>
       </c>
       <c r="B99" s="0" t="s">
-        <v>2769</v>
+        <v>2787</v>
       </c>
       <c r="C99" s="0" t="s">
-        <v>2770</v>
+        <v>2788</v>
       </c>
       <c r="D99" s="0" t="s">
-        <v>2771</v>
+        <v>2789</v>
       </c>
       <c r="E99" s="0" t="s">
-        <v>2772</v>
+        <v>2790</v>
       </c>
       <c r="F99" s="0">
         <v>4</v>
       </c>
       <c r="G99" s="0" t="s">
-        <v>2773</v>
+        <v>2791</v>
       </c>
       <c r="H99" s="0" t="s">
-        <v>2774</v>
+        <v>2792</v>
       </c>
       <c r="I99" s="0" t="s">
-        <v>2775</v>
+        <v>2793</v>
       </c>
       <c r="J99" s="0" t="s">
-        <v>2776</v>
+        <v>2794</v>
       </c>
       <c r="K99" s="0" t="s">
-        <v>2777</v>
+        <v>2795</v>
       </c>
       <c r="L99" s="0" t="s">
-        <v>2778</v>
+        <v>2796</v>
       </c>
       <c r="M99" s="0" t="s">
-        <v>2779</v>
+        <v>2797</v>
       </c>
       <c r="N99" s="0">
         <v>4</v>
       </c>
       <c r="O99" s="0" t="s">
-        <v>2780</v>
+        <v>2798</v>
       </c>
       <c r="P99" s="0">
         <v>1</v>
       </c>
       <c r="Q99" s="0" t="s">
-        <v>2781</v>
+        <v>2799</v>
       </c>
       <c r="R99" s="0" t="s">
-        <v>2782</v>
+        <v>2800</v>
       </c>
       <c r="S99" s="0" t="s">
-        <v>2783</v>
+        <v>2801</v>
       </c>
       <c r="T99" s="0"/>
       <c r="U99" s="0" t="s">
-        <v>2784</v>
+        <v>2802</v>
       </c>
       <c r="V99" s="0" t="s">
-        <v>2785</v>
+        <v>2803</v>
       </c>
     </row>
     <row r="100">
@@ -15092,6 +15956,534 @@
       </c>
       <c r="V103" s="0" t="s">
         <v>2767</v>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" s="0" t="s">
+        <v>2804</v>
+      </c>
+      <c r="B104" s="0" t="s">
+        <v>2805</v>
+      </c>
+      <c r="C104" s="0" t="s">
+        <v>2806</v>
+      </c>
+      <c r="D104" s="0" t="s">
+        <v>2807</v>
+      </c>
+      <c r="E104" s="0" t="s">
+        <v>2808</v>
+      </c>
+      <c r="F104" s="0">
+        <v>4</v>
+      </c>
+      <c r="G104" s="0" t="s">
+        <v>2809</v>
+      </c>
+      <c r="H104" s="0" t="s">
+        <v>2810</v>
+      </c>
+      <c r="I104" s="0" t="s">
+        <v>2811</v>
+      </c>
+      <c r="J104" s="0" t="s">
+        <v>2812</v>
+      </c>
+      <c r="K104" s="0" t="s">
+        <v>2813</v>
+      </c>
+      <c r="L104" s="0" t="s">
+        <v>2814</v>
+      </c>
+      <c r="M104" s="0" t="s">
+        <v>2815</v>
+      </c>
+      <c r="N104" s="0">
+        <v>4</v>
+      </c>
+      <c r="O104" s="0" t="s">
+        <v>2816</v>
+      </c>
+      <c r="P104" s="0">
+        <v>1</v>
+      </c>
+      <c r="Q104" s="0" t="s">
+        <v>2817</v>
+      </c>
+      <c r="R104" s="0" t="s">
+        <v>2818</v>
+      </c>
+      <c r="S104" s="0" t="s">
+        <v>2819</v>
+      </c>
+      <c r="T104" s="0"/>
+      <c r="U104" s="0" t="s">
+        <v>2820</v>
+      </c>
+      <c r="V104" s="0" t="s">
+        <v>2821</v>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" s="0" t="s">
+        <v>3002</v>
+      </c>
+      <c r="B105" s="0" t="s">
+        <v>3003</v>
+      </c>
+      <c r="C105" s="0" t="s">
+        <v>3004</v>
+      </c>
+      <c r="D105" s="0" t="s">
+        <v>3005</v>
+      </c>
+      <c r="E105" s="0" t="s">
+        <v>3006</v>
+      </c>
+      <c r="F105" s="0">
+        <v>4</v>
+      </c>
+      <c r="G105" s="0" t="s">
+        <v>3007</v>
+      </c>
+      <c r="H105" s="0" t="s">
+        <v>3008</v>
+      </c>
+      <c r="I105" s="0" t="s">
+        <v>3009</v>
+      </c>
+      <c r="J105" s="0" t="s">
+        <v>3010</v>
+      </c>
+      <c r="K105" s="0" t="s">
+        <v>3011</v>
+      </c>
+      <c r="L105" s="0" t="s">
+        <v>3012</v>
+      </c>
+      <c r="M105" s="0" t="s">
+        <v>3013</v>
+      </c>
+      <c r="N105" s="0">
+        <v>2</v>
+      </c>
+      <c r="O105" s="0" t="s">
+        <v>3014</v>
+      </c>
+      <c r="P105" s="0">
+        <v>0.20000000000000001</v>
+      </c>
+      <c r="Q105" s="0" t="s">
+        <v>3015</v>
+      </c>
+      <c r="R105" s="0" t="s">
+        <v>3016</v>
+      </c>
+      <c r="S105" s="0" t="s">
+        <v>3017</v>
+      </c>
+      <c r="T105" s="0"/>
+      <c r="U105" s="0" t="s">
+        <v>3018</v>
+      </c>
+      <c r="V105" s="0" t="s">
+        <v>3019</v>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" s="0" t="s">
+        <v>2858</v>
+      </c>
+      <c r="B106" s="0" t="s">
+        <v>2859</v>
+      </c>
+      <c r="C106" s="0" t="s">
+        <v>2860</v>
+      </c>
+      <c r="D106" s="0" t="s">
+        <v>2861</v>
+      </c>
+      <c r="E106" s="0" t="s">
+        <v>2862</v>
+      </c>
+      <c r="F106" s="0">
+        <v>4</v>
+      </c>
+      <c r="G106" s="0" t="s">
+        <v>2863</v>
+      </c>
+      <c r="H106" s="0" t="s">
+        <v>2864</v>
+      </c>
+      <c r="I106" s="0" t="s">
+        <v>2865</v>
+      </c>
+      <c r="J106" s="0" t="s">
+        <v>2866</v>
+      </c>
+      <c r="K106" s="0" t="s">
+        <v>2867</v>
+      </c>
+      <c r="L106" s="0" t="s">
+        <v>2868</v>
+      </c>
+      <c r="M106" s="0" t="s">
+        <v>2869</v>
+      </c>
+      <c r="N106" s="0">
+        <v>4</v>
+      </c>
+      <c r="O106" s="0" t="s">
+        <v>2870</v>
+      </c>
+      <c r="P106" s="0">
+        <v>1</v>
+      </c>
+      <c r="Q106" s="0" t="s">
+        <v>2871</v>
+      </c>
+      <c r="R106" s="0" t="s">
+        <v>2872</v>
+      </c>
+      <c r="S106" s="0" t="s">
+        <v>2873</v>
+      </c>
+      <c r="T106" s="0"/>
+      <c r="U106" s="0" t="s">
+        <v>2874</v>
+      </c>
+      <c r="V106" s="0" t="s">
+        <v>2875</v>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" s="0" t="s">
+        <v>2984</v>
+      </c>
+      <c r="B107" s="0" t="s">
+        <v>2985</v>
+      </c>
+      <c r="C107" s="0" t="s">
+        <v>2986</v>
+      </c>
+      <c r="D107" s="0" t="s">
+        <v>2987</v>
+      </c>
+      <c r="E107" s="0" t="s">
+        <v>2988</v>
+      </c>
+      <c r="F107" s="0">
+        <v>4</v>
+      </c>
+      <c r="G107" s="0" t="s">
+        <v>2989</v>
+      </c>
+      <c r="H107" s="0" t="s">
+        <v>2990</v>
+      </c>
+      <c r="I107" s="0" t="s">
+        <v>2991</v>
+      </c>
+      <c r="J107" s="0" t="s">
+        <v>2992</v>
+      </c>
+      <c r="K107" s="0" t="s">
+        <v>2993</v>
+      </c>
+      <c r="L107" s="0" t="s">
+        <v>2994</v>
+      </c>
+      <c r="M107" s="0" t="s">
+        <v>2995</v>
+      </c>
+      <c r="N107" s="0">
+        <v>4</v>
+      </c>
+      <c r="O107" s="0" t="s">
+        <v>2996</v>
+      </c>
+      <c r="P107" s="0">
+        <v>1</v>
+      </c>
+      <c r="Q107" s="0" t="s">
+        <v>2997</v>
+      </c>
+      <c r="R107" s="0" t="s">
+        <v>2998</v>
+      </c>
+      <c r="S107" s="0" t="s">
+        <v>2999</v>
+      </c>
+      <c r="T107" s="0"/>
+      <c r="U107" s="0" t="s">
+        <v>3000</v>
+      </c>
+      <c r="V107" s="0" t="s">
+        <v>3001</v>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" s="0" t="s">
+        <v>2948</v>
+      </c>
+      <c r="B108" s="0" t="s">
+        <v>2949</v>
+      </c>
+      <c r="C108" s="0" t="s">
+        <v>2950</v>
+      </c>
+      <c r="D108" s="0" t="s">
+        <v>2951</v>
+      </c>
+      <c r="E108" s="0" t="s">
+        <v>2952</v>
+      </c>
+      <c r="F108" s="0">
+        <v>4</v>
+      </c>
+      <c r="G108" s="0" t="s">
+        <v>2953</v>
+      </c>
+      <c r="H108" s="0" t="s">
+        <v>2954</v>
+      </c>
+      <c r="I108" s="0" t="s">
+        <v>2955</v>
+      </c>
+      <c r="J108" s="0" t="s">
+        <v>2956</v>
+      </c>
+      <c r="K108" s="0" t="s">
+        <v>2957</v>
+      </c>
+      <c r="L108" s="0" t="s">
+        <v>2958</v>
+      </c>
+      <c r="M108" s="0" t="s">
+        <v>2959</v>
+      </c>
+      <c r="N108" s="0">
+        <v>4</v>
+      </c>
+      <c r="O108" s="0" t="s">
+        <v>2960</v>
+      </c>
+      <c r="P108" s="0">
+        <v>1</v>
+      </c>
+      <c r="Q108" s="0" t="s">
+        <v>2961</v>
+      </c>
+      <c r="R108" s="0" t="s">
+        <v>2962</v>
+      </c>
+      <c r="S108" s="0" t="s">
+        <v>2963</v>
+      </c>
+      <c r="T108" s="0"/>
+      <c r="U108" s="0" t="s">
+        <v>2964</v>
+      </c>
+      <c r="V108" s="0" t="s">
+        <v>2965</v>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" s="0" t="s">
+        <v>2966</v>
+      </c>
+      <c r="B109" s="0" t="s">
+        <v>2967</v>
+      </c>
+      <c r="C109" s="0" t="s">
+        <v>2968</v>
+      </c>
+      <c r="D109" s="0" t="s">
+        <v>2969</v>
+      </c>
+      <c r="E109" s="0" t="s">
+        <v>2970</v>
+      </c>
+      <c r="F109" s="0">
+        <v>4</v>
+      </c>
+      <c r="G109" s="0" t="s">
+        <v>2971</v>
+      </c>
+      <c r="H109" s="0" t="s">
+        <v>2972</v>
+      </c>
+      <c r="I109" s="0" t="s">
+        <v>2973</v>
+      </c>
+      <c r="J109" s="0" t="s">
+        <v>2974</v>
+      </c>
+      <c r="K109" s="0" t="s">
+        <v>2975</v>
+      </c>
+      <c r="L109" s="0" t="s">
+        <v>2976</v>
+      </c>
+      <c r="M109" s="0" t="s">
+        <v>2977</v>
+      </c>
+      <c r="N109" s="0">
+        <v>4</v>
+      </c>
+      <c r="O109" s="0" t="s">
+        <v>2978</v>
+      </c>
+      <c r="P109" s="0">
+        <v>1</v>
+      </c>
+      <c r="Q109" s="0" t="s">
+        <v>2979</v>
+      </c>
+      <c r="R109" s="0" t="s">
+        <v>2980</v>
+      </c>
+      <c r="S109" s="0" t="s">
+        <v>2981</v>
+      </c>
+      <c r="T109" s="0"/>
+      <c r="U109" s="0" t="s">
+        <v>2982</v>
+      </c>
+      <c r="V109" s="0" t="s">
+        <v>2983</v>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" s="0" t="s">
+        <v>3020</v>
+      </c>
+      <c r="B110" s="0" t="s">
+        <v>3021</v>
+      </c>
+      <c r="C110" s="0" t="s">
+        <v>3022</v>
+      </c>
+      <c r="D110" s="0" t="s">
+        <v>3023</v>
+      </c>
+      <c r="E110" s="0" t="s">
+        <v>3024</v>
+      </c>
+      <c r="F110" s="0">
+        <v>4</v>
+      </c>
+      <c r="G110" s="0" t="s">
+        <v>3025</v>
+      </c>
+      <c r="H110" s="0" t="s">
+        <v>3026</v>
+      </c>
+      <c r="I110" s="0" t="s">
+        <v>3027</v>
+      </c>
+      <c r="J110" s="0" t="s">
+        <v>3028</v>
+      </c>
+      <c r="K110" s="0" t="s">
+        <v>3029</v>
+      </c>
+      <c r="L110" s="0" t="s">
+        <v>3030</v>
+      </c>
+      <c r="M110" s="0" t="s">
+        <v>3031</v>
+      </c>
+      <c r="N110" s="0">
+        <v>2</v>
+      </c>
+      <c r="O110" s="0" t="s">
+        <v>3032</v>
+      </c>
+      <c r="P110" s="0">
+        <v>0.20000000000000001</v>
+      </c>
+      <c r="Q110" s="0" t="s">
+        <v>3033</v>
+      </c>
+      <c r="R110" s="0" t="s">
+        <v>3034</v>
+      </c>
+      <c r="S110" s="0" t="s">
+        <v>3035</v>
+      </c>
+      <c r="T110" s="0"/>
+      <c r="U110" s="0" t="s">
+        <v>3036</v>
+      </c>
+      <c r="V110" s="0" t="s">
+        <v>3037</v>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" s="0" t="s">
+        <v>3056</v>
+      </c>
+      <c r="B111" s="0" t="s">
+        <v>3057</v>
+      </c>
+      <c r="C111" s="0" t="s">
+        <v>3058</v>
+      </c>
+      <c r="D111" s="0" t="s">
+        <v>3059</v>
+      </c>
+      <c r="E111" s="0" t="s">
+        <v>3060</v>
+      </c>
+      <c r="F111" s="0">
+        <v>4</v>
+      </c>
+      <c r="G111" s="0" t="s">
+        <v>3061</v>
+      </c>
+      <c r="H111" s="0" t="s">
+        <v>3062</v>
+      </c>
+      <c r="I111" s="0" t="s">
+        <v>3063</v>
+      </c>
+      <c r="J111" s="0" t="s">
+        <v>3064</v>
+      </c>
+      <c r="K111" s="0" t="s">
+        <v>3065</v>
+      </c>
+      <c r="L111" s="0" t="s">
+        <v>3066</v>
+      </c>
+      <c r="M111" s="0" t="s">
+        <v>3067</v>
+      </c>
+      <c r="N111" s="0">
+        <v>2</v>
+      </c>
+      <c r="O111" s="0" t="s">
+        <v>3068</v>
+      </c>
+      <c r="P111" s="0">
+        <v>0.20000000000000001</v>
+      </c>
+      <c r="Q111" s="0" t="s">
+        <v>3069</v>
+      </c>
+      <c r="R111" s="0" t="s">
+        <v>3070</v>
+      </c>
+      <c r="S111" s="0" t="s">
+        <v>3071</v>
+      </c>
+      <c r="T111" s="0"/>
+      <c r="U111" s="0" t="s">
+        <v>3072</v>
+      </c>
+      <c r="V111" s="0" t="s">
+        <v>3073</v>
       </c>
     </row>
   </sheetData>

--- a/config/becExpConfig/becExpType.csv.xlsx
+++ b/config/becExpConfig/becExpType.csv.xlsx
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="382" uniqueCount="360">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="856" uniqueCount="807">
   <si>
     <t>TrialName</t>
   </si>
@@ -1106,6 +1106,1347 @@
   </si>
   <si>
     <t>StdErr</t>
+  </si>
+  <si>
+    <t>None</t>
+  </si>
+  <si>
+    <t>RM3ShakenTrap</t>
+  </si>
+  <si>
+    <t>Check BEC vs rm3shakentrap</t>
+  </si>
+  <si>
+    <t>TOP</t>
+  </si>
+  <si>
+    <t>BECTOF</t>
+  </si>
+  <si>
+    <t>None</t>
+  </si>
+  <si>
+    <t>[111 208;196 154;296 143;374 148;404 202;416 297;416 367;330 388;198 384;110 350]</t>
+  </si>
+  <si>
+    <t>RM3ShakenTrap</t>
+  </si>
+  <si>
+    <t>DensityFit;AtomNumber;CenterFit</t>
+  </si>
+  <si>
+    <t>None</t>
+  </si>
+  <si>
+    <t>LF</t>
+  </si>
+  <si>
+    <t>Absorption</t>
+  </si>
+  <si>
+    <t>RandomPolarization</t>
+  </si>
+  <si>
+    <t>BosonicGaussianFit1D</t>
+  </si>
+  <si>
+    <t>None</t>
+  </si>
+  <si>
+    <t>LinearFit1D</t>
+  </si>
+  <si>
+    <t>StdErr</t>
+  </si>
+  <si>
+    <t>None</t>
+  </si>
+  <si>
+    <t>BECHold</t>
+  </si>
+  <si>
+    <t>Check BECHold scanning hold time (s)</t>
+  </si>
+  <si>
+    <t>TOP</t>
+  </si>
+  <si>
+    <t>BECTOFRotated</t>
+  </si>
+  <si>
+    <t>None</t>
+  </si>
+  <si>
+    <t>[111 208;196 154;296 143;374 148;404 202;416 297;416 367;330 388;198 384;110 350]</t>
+  </si>
+  <si>
+    <t>BECHold</t>
+  </si>
+  <si>
+    <t>DensityFit;CenterFit;AtomNumber</t>
+  </si>
+  <si>
+    <t>None</t>
+  </si>
+  <si>
+    <t>LF</t>
+  </si>
+  <si>
+    <t>Absorption</t>
+  </si>
+  <si>
+    <t>RandomPolarization</t>
+  </si>
+  <si>
+    <t>BosonicGaussianFit1D</t>
+  </si>
+  <si>
+    <t>None</t>
+  </si>
+  <si>
+    <t>ParabolicFit1D</t>
+  </si>
+  <si>
+    <t>StdErr</t>
+  </si>
+  <si>
+    <t>None</t>
+  </si>
+  <si>
+    <t>TrapRamp</t>
+  </si>
+  <si>
+    <t>Check BECHold scanning hold time (s)</t>
+  </si>
+  <si>
+    <t>TOP</t>
+  </si>
+  <si>
+    <t>BECTOFRotated</t>
+  </si>
+  <si>
+    <t>None</t>
+  </si>
+  <si>
+    <t>[111 208;196 154;296 143;374 148;404 202;416 297;416 367;330 388;198 384;110 350]</t>
+  </si>
+  <si>
+    <t>LatticeRamp</t>
+  </si>
+  <si>
+    <t>DensityFit;CenterFit;AtomNumber</t>
+  </si>
+  <si>
+    <t>None</t>
+  </si>
+  <si>
+    <t>LF</t>
+  </si>
+  <si>
+    <t>Absorption</t>
+  </si>
+  <si>
+    <t>RandomPolarization</t>
+  </si>
+  <si>
+    <t>BosonicGaussianFit1D</t>
+  </si>
+  <si>
+    <t>None</t>
+  </si>
+  <si>
+    <t>ParabolicFit1D</t>
+  </si>
+  <si>
+    <t>StdErr</t>
+  </si>
+  <si>
+    <t>None</t>
+  </si>
+  <si>
+    <t>TrapRamp</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Try ramping up trap 10% higher VVA in lattice, shaken trap varying the ramp </t>
+  </si>
+  <si>
+    <t>TOP</t>
+  </si>
+  <si>
+    <t>BECTOFRotated</t>
+  </si>
+  <si>
+    <t>None</t>
+  </si>
+  <si>
+    <t>[111 208;196 154;296 143;374 148;404 202;416 297;416 367;330 388;198 384;110 350]</t>
+  </si>
+  <si>
+    <t>LatticeRamp</t>
+  </si>
+  <si>
+    <t>DensityFit;CenterFit;AtomNumber</t>
+  </si>
+  <si>
+    <t>None</t>
+  </si>
+  <si>
+    <t>LF</t>
+  </si>
+  <si>
+    <t>Absorption</t>
+  </si>
+  <si>
+    <t>RandomPolarization</t>
+  </si>
+  <si>
+    <t>BosonicGaussianFit1D</t>
+  </si>
+  <si>
+    <t>None</t>
+  </si>
+  <si>
+    <t>ParabolicFit1D</t>
+  </si>
+  <si>
+    <t>StdErr</t>
+  </si>
+  <si>
+    <t>None</t>
+  </si>
+  <si>
+    <t>BECHold</t>
+  </si>
+  <si>
+    <t>Check BECHold scanning hold time (s)</t>
+  </si>
+  <si>
+    <t>TOP</t>
+  </si>
+  <si>
+    <t>BECTOFRotated</t>
+  </si>
+  <si>
+    <t>None</t>
+  </si>
+  <si>
+    <t>[111 208;196 154;296 143;374 148;404 202;416 297;416 367;330 388;198 384;110 350]</t>
+  </si>
+  <si>
+    <t>BECHold</t>
+  </si>
+  <si>
+    <t>DensityFit;CenterFit;AtomNumber</t>
+  </si>
+  <si>
+    <t>None</t>
+  </si>
+  <si>
+    <t>LF</t>
+  </si>
+  <si>
+    <t>Absorption</t>
+  </si>
+  <si>
+    <t>RandomPolarization</t>
+  </si>
+  <si>
+    <t>BosonicGaussianFit1D</t>
+  </si>
+  <si>
+    <t>ExponentialWithOffsetFit</t>
+  </si>
+  <si>
+    <t>ParabolicFit1D</t>
+  </si>
+  <si>
+    <t>StdErr</t>
+  </si>
+  <si>
+    <t>None</t>
+  </si>
+  <si>
+    <t>BecInSitu</t>
+  </si>
+  <si>
+    <t>Vary hw_RampTime TOF insitu</t>
+  </si>
+  <si>
+    <t>TOP</t>
+  </si>
+  <si>
+    <t>BECTOFRotated</t>
+  </si>
+  <si>
+    <t>None</t>
+  </si>
+  <si>
+    <t>[111 208;196 154;296 143;374 148;404 202;416 297;416 367;330 388;198 384;110 350]</t>
+  </si>
+  <si>
+    <t>hw_RampTime</t>
+  </si>
+  <si>
+    <t>DensityFit;AtomNumber;CenterFit</t>
+  </si>
+  <si>
+    <t>None</t>
+  </si>
+  <si>
+    <t>LF</t>
+  </si>
+  <si>
+    <t>Absorption</t>
+  </si>
+  <si>
+    <t>RandomPolarization</t>
+  </si>
+  <si>
+    <t>BosonicGaussianFit1D</t>
+  </si>
+  <si>
+    <t>None</t>
+  </si>
+  <si>
+    <t>ParabolicFit1D</t>
+  </si>
+  <si>
+    <t>StdErr</t>
+  </si>
+  <si>
+    <t>None</t>
+  </si>
+  <si>
+    <t>BecInSitu</t>
+  </si>
+  <si>
+    <t>Vary hw_RampTime TOF insitu</t>
+  </si>
+  <si>
+    <t>TOP</t>
+  </si>
+  <si>
+    <t>BECTOFRotated</t>
+  </si>
+  <si>
+    <t>None</t>
+  </si>
+  <si>
+    <t>[111 208;196 154;296 143;374 148;404 202;416 297;416 367;330 388;198 384;110 350]</t>
+  </si>
+  <si>
+    <t>hw_RampTime</t>
+  </si>
+  <si>
+    <t>DensityFit;AtomNumber;CenterFit</t>
+  </si>
+  <si>
+    <t>None</t>
+  </si>
+  <si>
+    <t>LF</t>
+  </si>
+  <si>
+    <t>Absorption</t>
+  </si>
+  <si>
+    <t>RandomPolarization</t>
+  </si>
+  <si>
+    <t>BosonicGaussianFit1D</t>
+  </si>
+  <si>
+    <t>None</t>
+  </si>
+  <si>
+    <t>ParabolicFit1D</t>
+  </si>
+  <si>
+    <t>StdErr</t>
+  </si>
+  <si>
+    <t>None</t>
+  </si>
+  <si>
+    <t>BecInSitu</t>
+  </si>
+  <si>
+    <t>hw_RampTime 0.1s TTL off the beam during ramp. Vary RampTime (i.e. the time to shut off the beam). RampMax changed from 1 to 0.5V</t>
+  </si>
+  <si>
+    <t>TOP</t>
+  </si>
+  <si>
+    <t>BECTOFRotated</t>
+  </si>
+  <si>
+    <t>None</t>
+  </si>
+  <si>
+    <t>[111 208;196 154;296 143;374 148;404 202;416 297;416 367;330 388;198 384;110 350]</t>
+  </si>
+  <si>
+    <t>RampTime</t>
+  </si>
+  <si>
+    <t>DensityFit;AtomNumber;CenterFit</t>
+  </si>
+  <si>
+    <t>None</t>
+  </si>
+  <si>
+    <t>LF</t>
+  </si>
+  <si>
+    <t>Absorption</t>
+  </si>
+  <si>
+    <t>RandomPolarization</t>
+  </si>
+  <si>
+    <t>BosonicGaussianFit1D</t>
+  </si>
+  <si>
+    <t>None</t>
+  </si>
+  <si>
+    <t>LinearFit1D</t>
+  </si>
+  <si>
+    <t>StdErr</t>
+  </si>
+  <si>
+    <t>None</t>
+  </si>
+  <si>
+    <t>ODTShake</t>
+  </si>
+  <si>
+    <t>Check ODT with 10kHz modulation of the shaken trap beam snapped on at the beginning of ODTHold, varying hw_MaxShake (the amplitude of the modulation). first try in situ. change odt hold time to RampTime</t>
+  </si>
+  <si>
+    <t>TOP</t>
+  </si>
+  <si>
+    <t>ODT</t>
+  </si>
+  <si>
+    <t>None</t>
+  </si>
+  <si>
+    <t>[111 208;196 154;296 143;374 148;404 202;416 297;416 367;330 388;198 384;110 350]</t>
+  </si>
+  <si>
+    <t>hw_MaxShake</t>
+  </si>
+  <si>
+    <t>CenterFit;AtomNumber;DensityFit</t>
+  </si>
+  <si>
+    <t>LSR</t>
+  </si>
+  <si>
+    <t>LF</t>
+  </si>
+  <si>
+    <t>Absorption</t>
+  </si>
+  <si>
+    <t>RandomPolarization</t>
+  </si>
+  <si>
+    <t>BosonicGaussianFit1D</t>
+  </si>
+  <si>
+    <t>None</t>
+  </si>
+  <si>
+    <t>ParabolicFit1D</t>
+  </si>
+  <si>
+    <t>StdErr</t>
+  </si>
+  <si>
+    <t>None</t>
+  </si>
+  <si>
+    <t>ODTShake</t>
+  </si>
+  <si>
+    <t>Check ODT with 10kHz modulation of the shaken trap beam snapped on at the during ODTHold, varying hw_MaxShake (the amplitude of the modulation). first try in situ. add duplicate timestep ODTShake during which shaking occurs</t>
+  </si>
+  <si>
+    <t>TOP</t>
+  </si>
+  <si>
+    <t>ODT</t>
+  </si>
+  <si>
+    <t>None</t>
+  </si>
+  <si>
+    <t>[111 208;196 154;296 143;374 148;404 202;416 297;416 367;330 388;198 384;110 350]</t>
+  </si>
+  <si>
+    <t>hw_MaxShake</t>
+  </si>
+  <si>
+    <t>CenterFit;AtomNumber;DensityFit</t>
+  </si>
+  <si>
+    <t>LSR</t>
+  </si>
+  <si>
+    <t>LF</t>
+  </si>
+  <si>
+    <t>Absorption</t>
+  </si>
+  <si>
+    <t>RandomPolarization</t>
+  </si>
+  <si>
+    <t>BosonicGaussianFit1D</t>
+  </si>
+  <si>
+    <t>None</t>
+  </si>
+  <si>
+    <t>ParabolicFit1D</t>
+  </si>
+  <si>
+    <t>StdErr</t>
+  </si>
+  <si>
+    <t>None</t>
+  </si>
+  <si>
+    <t>TrapShake</t>
+  </si>
+  <si>
+    <t>Shake BEC in ramped trap varying shaking amplitude  in situ</t>
+  </si>
+  <si>
+    <t>TOP</t>
+  </si>
+  <si>
+    <t>LatticeInSitu</t>
+  </si>
+  <si>
+    <t>None</t>
+  </si>
+  <si>
+    <t>[111 208;196 154;296 143;374 148;404 202;416 297;416 367;330 388;198 384;110 350]</t>
+  </si>
+  <si>
+    <t>hw_MaxShake</t>
+  </si>
+  <si>
+    <t>DensityFit;CenterFit;AtomNumber</t>
+  </si>
+  <si>
+    <t>None</t>
+  </si>
+  <si>
+    <t>LF</t>
+  </si>
+  <si>
+    <t>Absorption</t>
+  </si>
+  <si>
+    <t>RandomPolarization</t>
+  </si>
+  <si>
+    <t>BosonicGaussianFit1D</t>
+  </si>
+  <si>
+    <t>None</t>
+  </si>
+  <si>
+    <t>ParabolicFit1D</t>
+  </si>
+  <si>
+    <t>StdErr</t>
+  </si>
+  <si>
+    <t>None</t>
+  </si>
+  <si>
+    <t>TrapShake</t>
+  </si>
+  <si>
+    <t>Shake BEC at low amplitude snapped on coarsely scanning shaking frequency up to 500 Hz over 0.1s. hw_MaxShake is 0.1 Tof 11000</t>
+  </si>
+  <si>
+    <t>TOP</t>
+  </si>
+  <si>
+    <t>LatticeInSitu</t>
+  </si>
+  <si>
+    <t>None</t>
+  </si>
+  <si>
+    <t>[111 208;196 154;296 143;374 148;404 202;416 297;416 367;330 388;198 384;110 350]</t>
+  </si>
+  <si>
+    <t>hw_MaxShake</t>
+  </si>
+  <si>
+    <t>DensityFit;CenterFit;AtomNumber</t>
+  </si>
+  <si>
+    <t>None</t>
+  </si>
+  <si>
+    <t>LF</t>
+  </si>
+  <si>
+    <t>Absorption</t>
+  </si>
+  <si>
+    <t>RandomPolarization</t>
+  </si>
+  <si>
+    <t>BosonicGaussianFit1D</t>
+  </si>
+  <si>
+    <t>None</t>
+  </si>
+  <si>
+    <t>ParabolicFit1D</t>
+  </si>
+  <si>
+    <t>StdErr</t>
+  </si>
+  <si>
+    <t>None</t>
+  </si>
+  <si>
+    <t>TrapShake</t>
+  </si>
+  <si>
+    <t>Shake BEC at low amplitude snapped on coarsely scanning shaking frequency up to 500 Hz over 0.1s. hw_MaxShake is 0.1 Tof 11000</t>
+  </si>
+  <si>
+    <t>TOP</t>
+  </si>
+  <si>
+    <t>LatticeInSitu</t>
+  </si>
+  <si>
+    <t>None</t>
+  </si>
+  <si>
+    <t>[111 208;196 154;296 143;374 148;404 202;416 297;416 367;330 388;198 384;110 350]</t>
+  </si>
+  <si>
+    <t>hw_ShakeFreq</t>
+  </si>
+  <si>
+    <t>DensityFit;CenterFit;AtomNumber</t>
+  </si>
+  <si>
+    <t>None</t>
+  </si>
+  <si>
+    <t>LF</t>
+  </si>
+  <si>
+    <t>Absorption</t>
+  </si>
+  <si>
+    <t>RandomPolarization</t>
+  </si>
+  <si>
+    <t>BosonicGaussianFit1D</t>
+  </si>
+  <si>
+    <t>None</t>
+  </si>
+  <si>
+    <t>ParabolicFit1D</t>
+  </si>
+  <si>
+    <t>StdErr</t>
+  </si>
+  <si>
+    <t>None</t>
+  </si>
+  <si>
+    <t>TrapShake</t>
+  </si>
+  <si>
+    <t>Shake BEC at low amplitude snapped on coarsely scanning shaking frequency up to 500 Hz over 0.1s. hw_MaxShake is 0.1 Tof 11000</t>
+  </si>
+  <si>
+    <t>TOP</t>
+  </si>
+  <si>
+    <t>LatticeInSitu</t>
+  </si>
+  <si>
+    <t>None</t>
+  </si>
+  <si>
+    <t>[111 208;196 154;296 143;374 148;404 202;416 297;416 367;330 388;198 384;110 350]</t>
+  </si>
+  <si>
+    <t>hw_ShakeFrequency</t>
+  </si>
+  <si>
+    <t>DensityFit;CenterFit;AtomNumber</t>
+  </si>
+  <si>
+    <t>None</t>
+  </si>
+  <si>
+    <t>LF</t>
+  </si>
+  <si>
+    <t>Absorption</t>
+  </si>
+  <si>
+    <t>RandomPolarization</t>
+  </si>
+  <si>
+    <t>BosonicGaussianFit1D</t>
+  </si>
+  <si>
+    <t>None</t>
+  </si>
+  <si>
+    <t>ParabolicFit1D</t>
+  </si>
+  <si>
+    <t>StdErr</t>
+  </si>
+  <si>
+    <t>None</t>
+  </si>
+  <si>
+    <t>TrapShake</t>
+  </si>
+  <si>
+    <t>shake the BEC with hw_MaxShakePktoPk 0.5 ramping up from 0. the entirety of the shaking is a ramp up, vary ramp time. TOF 11000</t>
+  </si>
+  <si>
+    <t>TOP</t>
+  </si>
+  <si>
+    <t>LatticeInSitu</t>
+  </si>
+  <si>
+    <t>None</t>
+  </si>
+  <si>
+    <t>[111 208;196 154;296 143;374 148;404 202;416 297;416 367;330 388;198 384;110 350]</t>
+  </si>
+  <si>
+    <t>hw_RampTime</t>
+  </si>
+  <si>
+    <t>DensityFit;CenterFit;AtomNumber</t>
+  </si>
+  <si>
+    <t>None</t>
+  </si>
+  <si>
+    <t>LF</t>
+  </si>
+  <si>
+    <t>Absorption</t>
+  </si>
+  <si>
+    <t>RandomPolarization</t>
+  </si>
+  <si>
+    <t>BosonicGaussianFit1D</t>
+  </si>
+  <si>
+    <t>None</t>
+  </si>
+  <si>
+    <t>ParabolicFit1D</t>
+  </si>
+  <si>
+    <t>StdErr</t>
+  </si>
+  <si>
+    <t>None</t>
+  </si>
+  <si>
+    <t>TrapShake</t>
+  </si>
+  <si>
+    <t>shake the BEC with hw_MaxShakePktoPk 0.25 ramping up from 0. the entirety of the shaking is a ramp up, ramptime 0.2s. TOF 110000 repeats</t>
+  </si>
+  <si>
+    <t>TOP</t>
+  </si>
+  <si>
+    <t>LatticeInSitu</t>
+  </si>
+  <si>
+    <t>None</t>
+  </si>
+  <si>
+    <t>[111 208;196 154;296 143;374 148;404 202;416 297;416 367;330 388;198 384;110 350]</t>
+  </si>
+  <si>
+    <t>CiceroLogTime</t>
+  </si>
+  <si>
+    <t>DensityFit;CenterFit;AtomNumber</t>
+  </si>
+  <si>
+    <t>None</t>
+  </si>
+  <si>
+    <t>LF</t>
+  </si>
+  <si>
+    <t>Absorption</t>
+  </si>
+  <si>
+    <t>RandomPolarization</t>
+  </si>
+  <si>
+    <t>BosonicGaussianFit1D</t>
+  </si>
+  <si>
+    <t>None</t>
+  </si>
+  <si>
+    <t>ParabolicFit1D</t>
+  </si>
+  <si>
+    <t>StdErr</t>
+  </si>
+  <si>
+    <t>None</t>
+  </si>
+  <si>
+    <t>TrapShake</t>
+  </si>
+  <si>
+    <t>shake the BEC with hw_MaxShake 0.05 (peaj to peak amp) snapped on shake for 15 cycles varying shaking frequency up to 200Hz TOF 110000</t>
+  </si>
+  <si>
+    <t>TOP</t>
+  </si>
+  <si>
+    <t>LatticeInSitu</t>
+  </si>
+  <si>
+    <t>None</t>
+  </si>
+  <si>
+    <t>[111 208;196 154;296 143;374 148;404 202;416 297;416 367;330 388;198 384;110 350]</t>
+  </si>
+  <si>
+    <t>hw_ShakeFrequency</t>
+  </si>
+  <si>
+    <t>DensityFit;CenterFit;AtomNumber</t>
+  </si>
+  <si>
+    <t>None</t>
+  </si>
+  <si>
+    <t>LF</t>
+  </si>
+  <si>
+    <t>Absorption</t>
+  </si>
+  <si>
+    <t>RandomPolarization</t>
+  </si>
+  <si>
+    <t>BosonicGaussianFit1D</t>
+  </si>
+  <si>
+    <t>None</t>
+  </si>
+  <si>
+    <t>ParabolicFit1D</t>
+  </si>
+  <si>
+    <t>StdErr</t>
+  </si>
+  <si>
+    <t>None</t>
+  </si>
+  <si>
+    <t>TrapShake</t>
+  </si>
+  <si>
+    <t>shakenTrap VVA 0.3V vary MaxShake from 0 to 1.8 in step of 0.1 ramptime 0.25s freq 40Hz mm failed</t>
+  </si>
+  <si>
+    <t>TOP</t>
+  </si>
+  <si>
+    <t>LatticeInSitu</t>
+  </si>
+  <si>
+    <t>None</t>
+  </si>
+  <si>
+    <t>[111 208;196 154;296 143;374 148;404 202;416 297;416 367;330 388;198 384;110 350]</t>
+  </si>
+  <si>
+    <t>hw_MaxShake</t>
+  </si>
+  <si>
+    <t>DensityFit;CenterFit;AtomNumber</t>
+  </si>
+  <si>
+    <t>None</t>
+  </si>
+  <si>
+    <t>LF</t>
+  </si>
+  <si>
+    <t>Absorption</t>
+  </si>
+  <si>
+    <t>RandomPolarization</t>
+  </si>
+  <si>
+    <t>BosonicGaussianFit1D</t>
+  </si>
+  <si>
+    <t>None</t>
+  </si>
+  <si>
+    <t>ParabolicFit1D</t>
+  </si>
+  <si>
+    <t>StdErr</t>
+  </si>
+  <si>
+    <t>None</t>
+  </si>
+  <si>
+    <t>WaveformGeneratorName,ShakenTrap;ChannelName,Ch1;WaveformListName,RampedSine</t>
+  </si>
+  <si>
+    <t>TrapShake</t>
+  </si>
+  <si>
+    <t>shakenTrap VVA 0.3V vary MaxShake from 0 to 1.8 in step of 0.1 ramptime 0.25s freq 40Hz mm failed</t>
+  </si>
+  <si>
+    <t>TOP</t>
+  </si>
+  <si>
+    <t>LatticeInSitu</t>
+  </si>
+  <si>
+    <t>None</t>
+  </si>
+  <si>
+    <t>[111 208;196 154;296 143;374 148;404 202;416 297;416 367;330 388;198 384;110 350]</t>
+  </si>
+  <si>
+    <t>hw_MaxShake</t>
+  </si>
+  <si>
+    <t>DensityFit;CenterFit;AtomNumber</t>
+  </si>
+  <si>
+    <t>None</t>
+  </si>
+  <si>
+    <t>LF</t>
+  </si>
+  <si>
+    <t>Absorption</t>
+  </si>
+  <si>
+    <t>RandomPolarization</t>
+  </si>
+  <si>
+    <t>BosonicGaussianFit1D</t>
+  </si>
+  <si>
+    <t>None</t>
+  </si>
+  <si>
+    <t>ParabolicFit1D</t>
+  </si>
+  <si>
+    <t>StdErr</t>
+  </si>
+  <si>
+    <t>None</t>
+  </si>
+  <si>
+    <t>WaveformGeneratorName,ShakenTrap;ChannelName,Ch1;WaveformListName,RampedSine</t>
+  </si>
+  <si>
+    <t>TrapShake</t>
+  </si>
+  <si>
+    <t>shakenTrap VVA 0.3V vary MaxShake from 0 to 1.8 in step of 0.1 ramptime 0.25s freq 40Hz mm failed</t>
+  </si>
+  <si>
+    <t>TOP</t>
+  </si>
+  <si>
+    <t>LatticeInSitu</t>
+  </si>
+  <si>
+    <t>None</t>
+  </si>
+  <si>
+    <t>[111 208;196 154;296 143;374 148;404 202;416 297;416 367;330 388;198 384;110 350]</t>
+  </si>
+  <si>
+    <t>hw_MaxShake</t>
+  </si>
+  <si>
+    <t>DensityFit;CenterFit;AtomNumber</t>
+  </si>
+  <si>
+    <t>None</t>
+  </si>
+  <si>
+    <t>LF</t>
+  </si>
+  <si>
+    <t>Absorption</t>
+  </si>
+  <si>
+    <t>RandomPolarization</t>
+  </si>
+  <si>
+    <t>BosonicGaussianFit1D</t>
+  </si>
+  <si>
+    <t>None</t>
+  </si>
+  <si>
+    <t>ParabolicFit1D</t>
+  </si>
+  <si>
+    <t>StdErr</t>
+  </si>
+  <si>
+    <t>None</t>
+  </si>
+  <si>
+    <t>WaveformGeneratorName,ShakenTrap;ChannelName,Ch1;WaveformListName,RampedSine</t>
+  </si>
+  <si>
+    <t>TrapShake</t>
+  </si>
+  <si>
+    <t>shakenTrap VVA 0.3V vary MaxShake from 0 to 1.8 in step of 0.1 ramptime 0.25s freq 40Hz mm failed</t>
+  </si>
+  <si>
+    <t>TOP</t>
+  </si>
+  <si>
+    <t>LatticeInSitu</t>
+  </si>
+  <si>
+    <t>None</t>
+  </si>
+  <si>
+    <t>[111 208;196 154;296 143;374 148;404 202;416 297;416 367;330 388;198 384;110 350]</t>
+  </si>
+  <si>
+    <t>hw_MaxShake</t>
+  </si>
+  <si>
+    <t>DensityFit;CenterFit;AtomNumber</t>
+  </si>
+  <si>
+    <t>None</t>
+  </si>
+  <si>
+    <t>LF</t>
+  </si>
+  <si>
+    <t>Absorption</t>
+  </si>
+  <si>
+    <t>RandomPolarization</t>
+  </si>
+  <si>
+    <t>BosonicGaussianFit1D</t>
+  </si>
+  <si>
+    <t>None</t>
+  </si>
+  <si>
+    <t>ParabolicFit1D</t>
+  </si>
+  <si>
+    <t>StdErr</t>
+  </si>
+  <si>
+    <t>None</t>
+  </si>
+  <si>
+    <t>WaveformGeneratorName,ShakenTrap;ChannelName,Ch1;WaveformListName,RampedSine</t>
+  </si>
+  <si>
+    <t>TrapShake</t>
+  </si>
+  <si>
+    <t>shakenTrap VVA 0.3V vary MaxShake from 0 to 1.8 in step of 0.1 ramptime 0.25s freq 40Hz mm failed</t>
+  </si>
+  <si>
+    <t>TOP</t>
+  </si>
+  <si>
+    <t>LatticeInSitu</t>
+  </si>
+  <si>
+    <t>None</t>
+  </si>
+  <si>
+    <t>[111 208;196 154;296 143;374 148;404 202;416 297;416 367;330 388;198 384;110 350]</t>
+  </si>
+  <si>
+    <t>hw_MaxShake</t>
+  </si>
+  <si>
+    <t>DensityFit;CenterFit;AtomNumber</t>
+  </si>
+  <si>
+    <t>None</t>
+  </si>
+  <si>
+    <t>LF</t>
+  </si>
+  <si>
+    <t>Absorption</t>
+  </si>
+  <si>
+    <t>RandomPolarization</t>
+  </si>
+  <si>
+    <t>BosonicGaussianFit1D</t>
+  </si>
+  <si>
+    <t>None</t>
+  </si>
+  <si>
+    <t>ParabolicFit1D</t>
+  </si>
+  <si>
+    <t>StdErr</t>
+  </si>
+  <si>
+    <t>None</t>
+  </si>
+  <si>
+    <t>TrapShake</t>
+  </si>
+  <si>
+    <t>shakenTrap VVA 0.3V vary MaxShake from 0 to 1.8 in step of 0.1 ramptime 0.25s freq 40Hz mm failed</t>
+  </si>
+  <si>
+    <t>TOP</t>
+  </si>
+  <si>
+    <t>LatticeInSitu</t>
+  </si>
+  <si>
+    <t>None</t>
+  </si>
+  <si>
+    <t>[111 208;196 154;296 143;374 148;404 202;416 297;416 367;330 388;198 384;110 350]</t>
+  </si>
+  <si>
+    <t>hw_MaxShake</t>
+  </si>
+  <si>
+    <t>DensityFit;CenterFit;AtomNumber</t>
+  </si>
+  <si>
+    <t>None</t>
+  </si>
+  <si>
+    <t>LF</t>
+  </si>
+  <si>
+    <t>Absorption</t>
+  </si>
+  <si>
+    <t>RandomPolarization</t>
+  </si>
+  <si>
+    <t>BosonicGaussianFit1D</t>
+  </si>
+  <si>
+    <t>None</t>
+  </si>
+  <si>
+    <t>ParabolicFit1D</t>
+  </si>
+  <si>
+    <t>StdErr</t>
+  </si>
+  <si>
+    <t>None</t>
+  </si>
+  <si>
+    <t>WaveformGeneratorName,ShakenTrap;ChannelName,Ch1;WaveformListName,RampedSine</t>
+  </si>
+  <si>
+    <t>TrapShake</t>
+  </si>
+  <si>
+    <t>shakenTrap VVA 0.3V vary MaxShake from 0 to 1.8 in step of 0.1 ramptime 0.25s freq 40Hz mm failed</t>
+  </si>
+  <si>
+    <t>TOP</t>
+  </si>
+  <si>
+    <t>LatticeInSitu</t>
+  </si>
+  <si>
+    <t>None</t>
+  </si>
+  <si>
+    <t>[111 208;196 154;296 143;374 148;404 202;416 297;416 367;330 388;198 384;110 350]</t>
+  </si>
+  <si>
+    <t>hw_MaxShake</t>
+  </si>
+  <si>
+    <t>DensityFit;CenterFit;AtomNumber</t>
+  </si>
+  <si>
+    <t>None</t>
+  </si>
+  <si>
+    <t>LF</t>
+  </si>
+  <si>
+    <t>Absorption</t>
+  </si>
+  <si>
+    <t>RandomPolarization</t>
+  </si>
+  <si>
+    <t>BosonicGaussianFit1D</t>
+  </si>
+  <si>
+    <t>None</t>
+  </si>
+  <si>
+    <t>ParabolicFit1D</t>
+  </si>
+  <si>
+    <t>StdErr</t>
+  </si>
+  <si>
+    <t>None</t>
+  </si>
+  <si>
+    <t>TrapShake</t>
+  </si>
+  <si>
+    <t>shakenTrap VVA 0.3V vary MaxShake from 0 to 1.8 in step of 0.1 ramptime 0.25s freq 40Hz mm failed</t>
+  </si>
+  <si>
+    <t>TOP</t>
+  </si>
+  <si>
+    <t>LatticeInSitu</t>
+  </si>
+  <si>
+    <t>None</t>
+  </si>
+  <si>
+    <t>[111 208;196 154;296 143;374 148;404 202;416 297;416 367;330 388;198 384;110 350]</t>
+  </si>
+  <si>
+    <t>hw_MaxShake</t>
+  </si>
+  <si>
+    <t>DensityFit;CenterFit;AtomNumber</t>
+  </si>
+  <si>
+    <t>None</t>
+  </si>
+  <si>
+    <t>LF</t>
+  </si>
+  <si>
+    <t>Absorption</t>
+  </si>
+  <si>
+    <t>RandomPolarization</t>
+  </si>
+  <si>
+    <t>BosonicGaussianFit1D</t>
+  </si>
+  <si>
+    <t>None</t>
+  </si>
+  <si>
+    <t>ParabolicFit1D</t>
+  </si>
+  <si>
+    <t>StdErr</t>
+  </si>
+  <si>
+    <t>None</t>
+  </si>
+  <si>
+    <t>WaveformGeneratorName,ShakenTrap;ChannelName,Ch1;WaveformListName,SineRampedSine</t>
+  </si>
+  <si>
+    <t>RM1Scan</t>
+  </si>
+  <si>
+    <t>Check Red MOT (RM) at different TOF</t>
+  </si>
+  <si>
+    <t>TOP</t>
+  </si>
+  <si>
+    <t>Full</t>
+  </si>
+  <si>
+    <t>None</t>
+  </si>
+  <si>
+    <t>[]</t>
+  </si>
+  <si>
+    <t>RedMOT1Offset</t>
+  </si>
+  <si>
+    <t>DensityFit;AtomNumber;Tof;CenterFit</t>
+  </si>
+  <si>
+    <t>None</t>
+  </si>
+  <si>
+    <t>LF</t>
+  </si>
+  <si>
+    <t>Absorption</t>
+  </si>
+  <si>
+    <t>RandomPolarization</t>
+  </si>
+  <si>
+    <t>BosonicGaussianFit1D</t>
+  </si>
+  <si>
+    <t>None</t>
+  </si>
+  <si>
+    <t>SineFit1D</t>
   </si>
   <si>
     <t>None</t>
@@ -1436,11 +2777,11 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:V21"/>
+  <dimension ref="A1:V28"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="40.7109375" customWidth="true"/>
-    <col min="2" max="2" width="139.140625" customWidth="true"/>
+    <col min="2" max="2" width="204.42578125" customWidth="true"/>
     <col min="3" max="3" width="16.42578125" customWidth="true"/>
     <col min="4" max="4" width="14.85546875" customWidth="true"/>
     <col min="5" max="5" width="21.42578125" customWidth="true"/>
@@ -1454,13 +2795,13 @@
     <col min="13" max="13" width="19" customWidth="true"/>
     <col min="14" max="14" width="7.85546875" customWidth="true"/>
     <col min="15" max="15" width="20.42578125" customWidth="true"/>
-    <col min="16" max="16" width="22.5703125" customWidth="true"/>
+    <col min="16" max="16" width="23.85546875" customWidth="true"/>
     <col min="17" max="17" width="17.42578125" customWidth="true"/>
     <col min="18" max="18" width="16.42578125" customWidth="true"/>
     <col min="19" max="19" width="17" customWidth="true"/>
     <col min="20" max="20" width="16.85546875" customWidth="true"/>
     <col min="21" max="21" width="20.42578125" customWidth="true"/>
-    <col min="22" max="22" width="20.5703125" customWidth="true"/>
+    <col min="22" max="22" width="86.28515625" customWidth="true"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -2831,6 +4172,470 @@
         <v>359</v>
       </c>
       <c r="V21" s="0"/>
+    </row>
+    <row r="22">
+      <c r="A22" s="0" t="s">
+        <v>360</v>
+      </c>
+      <c r="B22" s="0" t="s">
+        <v>361</v>
+      </c>
+      <c r="C22" s="0" t="s">
+        <v>362</v>
+      </c>
+      <c r="D22" s="0" t="s">
+        <v>363</v>
+      </c>
+      <c r="E22" s="0" t="s">
+        <v>364</v>
+      </c>
+      <c r="F22" s="0">
+        <v>4</v>
+      </c>
+      <c r="G22" s="0" t="s">
+        <v>365</v>
+      </c>
+      <c r="H22" s="0" t="s">
+        <v>366</v>
+      </c>
+      <c r="I22" s="0" t="s">
+        <v>367</v>
+      </c>
+      <c r="J22" s="0" t="s">
+        <v>368</v>
+      </c>
+      <c r="K22" s="0" t="s">
+        <v>369</v>
+      </c>
+      <c r="L22" s="0" t="s">
+        <v>370</v>
+      </c>
+      <c r="M22" s="0" t="s">
+        <v>371</v>
+      </c>
+      <c r="N22" s="0">
+        <v>8</v>
+      </c>
+      <c r="O22" s="0" t="s">
+        <v>372</v>
+      </c>
+      <c r="P22" s="0" t="s">
+        <v>373</v>
+      </c>
+      <c r="Q22" s="0">
+        <v>0.40000000000000002</v>
+      </c>
+      <c r="R22" s="0" t="s">
+        <v>374</v>
+      </c>
+      <c r="S22" s="0" t="s">
+        <v>375</v>
+      </c>
+      <c r="T22" s="0" t="s">
+        <v>376</v>
+      </c>
+      <c r="U22" s="0" t="s">
+        <v>376</v>
+      </c>
+      <c r="V22" s="0"/>
+    </row>
+    <row r="23">
+      <c r="A23" s="0" t="s">
+        <v>428</v>
+      </c>
+      <c r="B23" s="0" t="s">
+        <v>429</v>
+      </c>
+      <c r="C23" s="0" t="s">
+        <v>430</v>
+      </c>
+      <c r="D23" s="0" t="s">
+        <v>431</v>
+      </c>
+      <c r="E23" s="0" t="s">
+        <v>432</v>
+      </c>
+      <c r="F23" s="0">
+        <v>4</v>
+      </c>
+      <c r="G23" s="0" t="s">
+        <v>433</v>
+      </c>
+      <c r="H23" s="0" t="s">
+        <v>434</v>
+      </c>
+      <c r="I23" s="0" t="s">
+        <v>435</v>
+      </c>
+      <c r="J23" s="0" t="s">
+        <v>436</v>
+      </c>
+      <c r="K23" s="0" t="s">
+        <v>437</v>
+      </c>
+      <c r="L23" s="0" t="s">
+        <v>438</v>
+      </c>
+      <c r="M23" s="0" t="s">
+        <v>439</v>
+      </c>
+      <c r="N23" s="0">
+        <v>8</v>
+      </c>
+      <c r="O23" s="0" t="s">
+        <v>440</v>
+      </c>
+      <c r="P23" s="0" t="s">
+        <v>441</v>
+      </c>
+      <c r="Q23" s="0">
+        <v>0.40000000000000002</v>
+      </c>
+      <c r="R23" s="0" t="s">
+        <v>442</v>
+      </c>
+      <c r="S23" s="0" t="s">
+        <v>443</v>
+      </c>
+      <c r="T23" s="0" t="s">
+        <v>444</v>
+      </c>
+      <c r="U23" s="0" t="s">
+        <v>444</v>
+      </c>
+      <c r="V23" s="0"/>
+    </row>
+    <row r="24">
+      <c r="A24" s="0" t="s">
+        <v>411</v>
+      </c>
+      <c r="B24" s="0" t="s">
+        <v>412</v>
+      </c>
+      <c r="C24" s="0" t="s">
+        <v>413</v>
+      </c>
+      <c r="D24" s="0" t="s">
+        <v>414</v>
+      </c>
+      <c r="E24" s="0" t="s">
+        <v>415</v>
+      </c>
+      <c r="F24" s="0">
+        <v>4</v>
+      </c>
+      <c r="G24" s="0" t="s">
+        <v>416</v>
+      </c>
+      <c r="H24" s="0" t="s">
+        <v>417</v>
+      </c>
+      <c r="I24" s="0" t="s">
+        <v>418</v>
+      </c>
+      <c r="J24" s="0" t="s">
+        <v>419</v>
+      </c>
+      <c r="K24" s="0" t="s">
+        <v>420</v>
+      </c>
+      <c r="L24" s="0" t="s">
+        <v>421</v>
+      </c>
+      <c r="M24" s="0" t="s">
+        <v>422</v>
+      </c>
+      <c r="N24" s="0">
+        <v>8</v>
+      </c>
+      <c r="O24" s="0" t="s">
+        <v>423</v>
+      </c>
+      <c r="P24" s="0" t="s">
+        <v>424</v>
+      </c>
+      <c r="Q24" s="0">
+        <v>0.40000000000000002</v>
+      </c>
+      <c r="R24" s="0" t="s">
+        <v>425</v>
+      </c>
+      <c r="S24" s="0" t="s">
+        <v>426</v>
+      </c>
+      <c r="T24" s="0" t="s">
+        <v>427</v>
+      </c>
+      <c r="U24" s="0" t="s">
+        <v>427</v>
+      </c>
+      <c r="V24" s="0"/>
+    </row>
+    <row r="25">
+      <c r="A25" s="0" t="s">
+        <v>479</v>
+      </c>
+      <c r="B25" s="0" t="s">
+        <v>480</v>
+      </c>
+      <c r="C25" s="0" t="s">
+        <v>481</v>
+      </c>
+      <c r="D25" s="0" t="s">
+        <v>482</v>
+      </c>
+      <c r="E25" s="0" t="s">
+        <v>483</v>
+      </c>
+      <c r="F25" s="0">
+        <v>4</v>
+      </c>
+      <c r="G25" s="0" t="s">
+        <v>484</v>
+      </c>
+      <c r="H25" s="0" t="s">
+        <v>485</v>
+      </c>
+      <c r="I25" s="0" t="s">
+        <v>486</v>
+      </c>
+      <c r="J25" s="0" t="s">
+        <v>487</v>
+      </c>
+      <c r="K25" s="0" t="s">
+        <v>488</v>
+      </c>
+      <c r="L25" s="0" t="s">
+        <v>489</v>
+      </c>
+      <c r="M25" s="0" t="s">
+        <v>490</v>
+      </c>
+      <c r="N25" s="0">
+        <v>8</v>
+      </c>
+      <c r="O25" s="0" t="s">
+        <v>491</v>
+      </c>
+      <c r="P25" s="0" t="s">
+        <v>492</v>
+      </c>
+      <c r="Q25" s="0">
+        <v>0.40000000000000002</v>
+      </c>
+      <c r="R25" s="0" t="s">
+        <v>493</v>
+      </c>
+      <c r="S25" s="0" t="s">
+        <v>494</v>
+      </c>
+      <c r="T25" s="0" t="s">
+        <v>495</v>
+      </c>
+      <c r="U25" s="0" t="s">
+        <v>495</v>
+      </c>
+      <c r="V25" s="0"/>
+    </row>
+    <row r="26">
+      <c r="A26" s="0" t="s">
+        <v>513</v>
+      </c>
+      <c r="B26" s="0" t="s">
+        <v>514</v>
+      </c>
+      <c r="C26" s="0" t="s">
+        <v>515</v>
+      </c>
+      <c r="D26" s="0" t="s">
+        <v>516</v>
+      </c>
+      <c r="E26" s="0" t="s">
+        <v>517</v>
+      </c>
+      <c r="F26" s="0">
+        <v>4</v>
+      </c>
+      <c r="G26" s="0" t="s">
+        <v>518</v>
+      </c>
+      <c r="H26" s="0" t="s">
+        <v>519</v>
+      </c>
+      <c r="I26" s="0" t="s">
+        <v>520</v>
+      </c>
+      <c r="J26" s="0" t="s">
+        <v>521</v>
+      </c>
+      <c r="K26" s="0" t="s">
+        <v>522</v>
+      </c>
+      <c r="L26" s="0" t="s">
+        <v>523</v>
+      </c>
+      <c r="M26" s="0" t="s">
+        <v>524</v>
+      </c>
+      <c r="N26" s="0">
+        <v>8</v>
+      </c>
+      <c r="O26" s="0" t="s">
+        <v>525</v>
+      </c>
+      <c r="P26" s="0" t="s">
+        <v>526</v>
+      </c>
+      <c r="Q26" s="0">
+        <v>4</v>
+      </c>
+      <c r="R26" s="0" t="s">
+        <v>527</v>
+      </c>
+      <c r="S26" s="0" t="s">
+        <v>528</v>
+      </c>
+      <c r="T26" s="0" t="s">
+        <v>529</v>
+      </c>
+      <c r="U26" s="0" t="s">
+        <v>529</v>
+      </c>
+      <c r="V26" s="0"/>
+    </row>
+    <row r="27">
+      <c r="A27" s="0" t="s">
+        <v>773</v>
+      </c>
+      <c r="B27" s="0" t="s">
+        <v>774</v>
+      </c>
+      <c r="C27" s="0" t="s">
+        <v>775</v>
+      </c>
+      <c r="D27" s="0" t="s">
+        <v>776</v>
+      </c>
+      <c r="E27" s="0" t="s">
+        <v>777</v>
+      </c>
+      <c r="F27" s="0">
+        <v>4</v>
+      </c>
+      <c r="G27" s="0" t="s">
+        <v>778</v>
+      </c>
+      <c r="H27" s="0" t="s">
+        <v>779</v>
+      </c>
+      <c r="I27" s="0" t="s">
+        <v>780</v>
+      </c>
+      <c r="J27" s="0" t="s">
+        <v>781</v>
+      </c>
+      <c r="K27" s="0" t="s">
+        <v>782</v>
+      </c>
+      <c r="L27" s="0" t="s">
+        <v>783</v>
+      </c>
+      <c r="M27" s="0" t="s">
+        <v>784</v>
+      </c>
+      <c r="N27" s="0">
+        <v>8</v>
+      </c>
+      <c r="O27" s="0" t="s">
+        <v>785</v>
+      </c>
+      <c r="P27" s="0" t="s">
+        <v>786</v>
+      </c>
+      <c r="Q27" s="0">
+        <v>0.40000000000000002</v>
+      </c>
+      <c r="R27" s="0" t="s">
+        <v>787</v>
+      </c>
+      <c r="S27" s="0" t="s">
+        <v>788</v>
+      </c>
+      <c r="T27" s="0" t="s">
+        <v>789</v>
+      </c>
+      <c r="U27" s="0" t="s">
+        <v>789</v>
+      </c>
+      <c r="V27" s="0" t="s">
+        <v>790</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="0" t="s">
+        <v>791</v>
+      </c>
+      <c r="B28" s="0" t="s">
+        <v>792</v>
+      </c>
+      <c r="C28" s="0" t="s">
+        <v>793</v>
+      </c>
+      <c r="D28" s="0" t="s">
+        <v>794</v>
+      </c>
+      <c r="E28" s="0" t="s">
+        <v>795</v>
+      </c>
+      <c r="F28" s="0">
+        <v>4</v>
+      </c>
+      <c r="G28" s="0" t="s">
+        <v>796</v>
+      </c>
+      <c r="H28" s="0" t="s">
+        <v>797</v>
+      </c>
+      <c r="I28" s="0" t="s">
+        <v>798</v>
+      </c>
+      <c r="J28" s="0" t="s">
+        <v>799</v>
+      </c>
+      <c r="K28" s="0" t="s">
+        <v>800</v>
+      </c>
+      <c r="L28" s="0" t="s">
+        <v>801</v>
+      </c>
+      <c r="M28" s="0" t="s">
+        <v>802</v>
+      </c>
+      <c r="N28" s="0">
+        <v>8</v>
+      </c>
+      <c r="O28" s="0" t="s">
+        <v>803</v>
+      </c>
+      <c r="P28" s="0" t="s">
+        <v>804</v>
+      </c>
+      <c r="Q28" s="0">
+        <v>15</v>
+      </c>
+      <c r="R28" s="0" t="s">
+        <v>805</v>
+      </c>
+      <c r="S28" s="0" t="s">
+        <v>806</v>
+      </c>
+      <c r="T28" s="0" t="s">
+        <v>806</v>
+      </c>
+      <c r="U28" s="0" t="s">
+        <v>806</v>
+      </c>
+      <c r="V28" s="0"/>
     </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>

--- a/config/becExpConfig/becExpType.csv.xlsx
+++ b/config/becExpConfig/becExpType.csv.xlsx
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3341" uniqueCount="3074">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3411" uniqueCount="3144">
   <si>
     <t>TrialName</t>
   </si>
@@ -9249,6 +9249,216 @@
   </si>
   <si>
     <t>WaveformGeneratorName,XvWingMod;ChannelName,Ch1;WaveformListName,XvWingLatticeCC</t>
+  </si>
+  <si>
+    <t>PhaseLockName,ImagingLock;Frequency,700000000;VariableName,hw_ImagingNi</t>
+  </si>
+  <si>
+    <t>NiLatticeCC</t>
+  </si>
+  <si>
+    <t xml:space="preserve">A Bloch oscillation experiment at the non-interacting lattice stage. </t>
+  </si>
+  <si>
+    <t>TOP</t>
+  </si>
+  <si>
+    <t>NiLattice</t>
+  </si>
+  <si>
+    <t>None</t>
+  </si>
+  <si>
+    <t>latticehold</t>
+  </si>
+  <si>
+    <t>DensityFit;AtomNumber;CenterFit</t>
+  </si>
+  <si>
+    <t>LSR</t>
+  </si>
+  <si>
+    <t>[784 1265;854 1223;1012 1216;1153 1216;1229 1282;1216 1360;1128 1373;965 1380;834 1382;786 1340]</t>
+  </si>
+  <si>
+    <t>HF</t>
+  </si>
+  <si>
+    <t>Absorption</t>
+  </si>
+  <si>
+    <t>StrongLight</t>
+  </si>
+  <si>
+    <t>BosonicGaussianFit1D</t>
+  </si>
+  <si>
+    <t>None</t>
+  </si>
+  <si>
+    <t>SineFit1D</t>
+  </si>
+  <si>
+    <t>StdErr</t>
+  </si>
+  <si>
+    <t>WaveformGeneratorName,XvWingMod;ChannelName,Ch1;WaveformListName,XvWingLatticeCC</t>
+  </si>
+  <si>
+    <t>PhaseLockName,ImagingLock;Frequency,700000000;VariableName,hw_ImagingNi</t>
+  </si>
+  <si>
+    <t>NiLatticeCC</t>
+  </si>
+  <si>
+    <t>A Bloch oscillation experiment at the non-interacting lattice stage. kp2vva=3.9 trying atom bouncing.</t>
+  </si>
+  <si>
+    <t>TOP</t>
+  </si>
+  <si>
+    <t>NiLattice</t>
+  </si>
+  <si>
+    <t>None</t>
+  </si>
+  <si>
+    <t>latticehold</t>
+  </si>
+  <si>
+    <t>DensityFit;AtomNumber;CenterFit</t>
+  </si>
+  <si>
+    <t>LSR</t>
+  </si>
+  <si>
+    <t>[784 1265;854 1223;1012 1216;1153 1216;1229 1282;1216 1360;1128 1373;965 1380;834 1382;786 1340]</t>
+  </si>
+  <si>
+    <t>HF</t>
+  </si>
+  <si>
+    <t>Absorption</t>
+  </si>
+  <si>
+    <t>StrongLight</t>
+  </si>
+  <si>
+    <t>BosonicGaussianFit1D</t>
+  </si>
+  <si>
+    <t>None</t>
+  </si>
+  <si>
+    <t>SineFit1D</t>
+  </si>
+  <si>
+    <t>StdErr</t>
+  </si>
+  <si>
+    <t>PhaseLockName,ImagingLock;Frequency,700000000;VariableName,hw_ImagingNi</t>
+  </si>
+  <si>
+    <t>NiLatticeCCGWBounce</t>
+  </si>
+  <si>
+    <t>A Bloch oscillation experiment at the non-interacting lattice stage. kp2vva=3.9 trying atom bouncing.</t>
+  </si>
+  <si>
+    <t>TOP</t>
+  </si>
+  <si>
+    <t>NiLattice</t>
+  </si>
+  <si>
+    <t>None</t>
+  </si>
+  <si>
+    <t>latticehold</t>
+  </si>
+  <si>
+    <t>DensityFit;AtomNumber;CenterFit</t>
+  </si>
+  <si>
+    <t>LSR</t>
+  </si>
+  <si>
+    <t>[784 1265;854 1223;1012 1216;1153 1216;1229 1282;1216 1360;1128 1373;965 1380;834 1382;786 1340]</t>
+  </si>
+  <si>
+    <t>HF</t>
+  </si>
+  <si>
+    <t>Absorption</t>
+  </si>
+  <si>
+    <t>StrongLight</t>
+  </si>
+  <si>
+    <t>BosonicGaussianFit1D</t>
+  </si>
+  <si>
+    <t>None</t>
+  </si>
+  <si>
+    <t>SineFit1D</t>
+  </si>
+  <si>
+    <t>StdErr</t>
+  </si>
+  <si>
+    <t>PhaseLockName,ImagingLock;Frequency,700000000;VariableName,hw_ImagingNi</t>
+  </si>
+  <si>
+    <t>NiLatticeCCGWBounce</t>
+  </si>
+  <si>
+    <t>A Bloch oscillation experiment at the non-interacting lattice stage. kp2vva=3.9 trying atom bouncing.</t>
+  </si>
+  <si>
+    <t>TOP</t>
+  </si>
+  <si>
+    <t>NiLattice</t>
+  </si>
+  <si>
+    <t>None</t>
+  </si>
+  <si>
+    <t>latticehold</t>
+  </si>
+  <si>
+    <t>DensityFit;AtomNumber;CenterFit</t>
+  </si>
+  <si>
+    <t>LSR</t>
+  </si>
+  <si>
+    <t>[784 1265;854 1223;1012 1216;1153 1216;1229 1282;1216 1360;1128 1373;965 1380;834 1382;786 1340]</t>
+  </si>
+  <si>
+    <t>HF</t>
+  </si>
+  <si>
+    <t>Absorption</t>
+  </si>
+  <si>
+    <t>StrongLight</t>
+  </si>
+  <si>
+    <t>BosonicGaussianFit1D</t>
+  </si>
+  <si>
+    <t>None</t>
+  </si>
+  <si>
+    <t>SineFit1D</t>
+  </si>
+  <si>
+    <t>StdErr</t>
+  </si>
+  <si>
+    <t>WaveformGeneratorName,XvWingMod,GreenWallMod;ChannelName,Ch1,Ch1;WaveformListName,XvWingGW,GWOneWall</t>
   </si>
   <si>
     <t>PhaseLockName,ImagingLock;Frequency,700000000;VariableName,hw_ImagingNi</t>
@@ -9578,7 +9788,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:V111"/>
+  <dimension ref="A1:V113"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="36.42578125" customWidth="true"/>
@@ -16486,6 +16696,136 @@
         <v>3073</v>
       </c>
     </row>
+    <row r="112">
+      <c r="A112" s="0" t="s">
+        <v>3092</v>
+      </c>
+      <c r="B112" s="0" t="s">
+        <v>3093</v>
+      </c>
+      <c r="C112" s="0" t="s">
+        <v>3094</v>
+      </c>
+      <c r="D112" s="0" t="s">
+        <v>3095</v>
+      </c>
+      <c r="E112" s="0" t="s">
+        <v>3096</v>
+      </c>
+      <c r="F112" s="0">
+        <v>4</v>
+      </c>
+      <c r="G112" s="0" t="s">
+        <v>3097</v>
+      </c>
+      <c r="H112" s="0" t="s">
+        <v>3098</v>
+      </c>
+      <c r="I112" s="0" t="s">
+        <v>3099</v>
+      </c>
+      <c r="J112" s="0" t="s">
+        <v>3100</v>
+      </c>
+      <c r="K112" s="0" t="s">
+        <v>3101</v>
+      </c>
+      <c r="L112" s="0" t="s">
+        <v>3102</v>
+      </c>
+      <c r="M112" s="0" t="s">
+        <v>3103</v>
+      </c>
+      <c r="N112" s="0">
+        <v>2</v>
+      </c>
+      <c r="O112" s="0" t="s">
+        <v>3104</v>
+      </c>
+      <c r="P112" s="0">
+        <v>0.20000000000000001</v>
+      </c>
+      <c r="Q112" s="0" t="s">
+        <v>3105</v>
+      </c>
+      <c r="R112" s="0" t="s">
+        <v>3106</v>
+      </c>
+      <c r="S112" s="0" t="s">
+        <v>3107</v>
+      </c>
+      <c r="T112" s="0"/>
+      <c r="U112" s="0"/>
+      <c r="V112" s="0" t="s">
+        <v>3108</v>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" s="0" t="s">
+        <v>3126</v>
+      </c>
+      <c r="B113" s="0" t="s">
+        <v>3127</v>
+      </c>
+      <c r="C113" s="0" t="s">
+        <v>3128</v>
+      </c>
+      <c r="D113" s="0" t="s">
+        <v>3129</v>
+      </c>
+      <c r="E113" s="0" t="s">
+        <v>3130</v>
+      </c>
+      <c r="F113" s="0">
+        <v>4</v>
+      </c>
+      <c r="G113" s="0" t="s">
+        <v>3131</v>
+      </c>
+      <c r="H113" s="0" t="s">
+        <v>3132</v>
+      </c>
+      <c r="I113" s="0" t="s">
+        <v>3133</v>
+      </c>
+      <c r="J113" s="0" t="s">
+        <v>3134</v>
+      </c>
+      <c r="K113" s="0" t="s">
+        <v>3135</v>
+      </c>
+      <c r="L113" s="0" t="s">
+        <v>3136</v>
+      </c>
+      <c r="M113" s="0" t="s">
+        <v>3137</v>
+      </c>
+      <c r="N113" s="0">
+        <v>2</v>
+      </c>
+      <c r="O113" s="0" t="s">
+        <v>3138</v>
+      </c>
+      <c r="P113" s="0">
+        <v>0.20000000000000001</v>
+      </c>
+      <c r="Q113" s="0" t="s">
+        <v>3139</v>
+      </c>
+      <c r="R113" s="0" t="s">
+        <v>3140</v>
+      </c>
+      <c r="S113" s="0" t="s">
+        <v>3141</v>
+      </c>
+      <c r="T113" s="0"/>
+      <c r="U113" s="0" t="s">
+        <v>3142</v>
+      </c>
+      <c r="V113" s="0" t="s">
+        <v>3143</v>
+      </c>
+    </row>
   </sheetData>
   <sortState ref="A2:U83">
     <sortCondition ref="A2:A83"/>

--- a/config/becExpConfig/becExpType.csv.xlsx
+++ b/config/becExpConfig/becExpType.csv.xlsx
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3411" uniqueCount="3144">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3554" uniqueCount="3287">
   <si>
     <t>TrialName</t>
   </si>
@@ -9459,6 +9459,435 @@
   </si>
   <si>
     <t>WaveformGeneratorName,XvWingMod,GreenWallMod;ChannelName,Ch1,Ch1;WaveformListName,XvWingGW,GWOneWall</t>
+  </si>
+  <si>
+    <t>PhaseLockName,ImagingLock;Frequency,700000000;VariableName,hw_ImagingNi</t>
+  </si>
+  <si>
+    <t>NiLatticeCCGWBandPrep</t>
+  </si>
+  <si>
+    <t>A Bloch oscillation experiment at the non-interacting lattice stage. kp2vva=3.9 trying atom bouncing.</t>
+  </si>
+  <si>
+    <t>TOP</t>
+  </si>
+  <si>
+    <t>NiLattice</t>
+  </si>
+  <si>
+    <t>None</t>
+  </si>
+  <si>
+    <t>latticehold</t>
+  </si>
+  <si>
+    <t>DensityFit;AtomNumber;CenterFit</t>
+  </si>
+  <si>
+    <t>LSR</t>
+  </si>
+  <si>
+    <t>[784 1265;854 1223;1012 1216;1153 1216;1229 1282;1216 1360;1128 1373;965 1380;834 1382;786 1340]</t>
+  </si>
+  <si>
+    <t>HF</t>
+  </si>
+  <si>
+    <t>Absorption</t>
+  </si>
+  <si>
+    <t>StrongLight</t>
+  </si>
+  <si>
+    <t>BosonicGaussianFit1D</t>
+  </si>
+  <si>
+    <t>None</t>
+  </si>
+  <si>
+    <t>SineFit1D</t>
+  </si>
+  <si>
+    <t>StdErr</t>
+  </si>
+  <si>
+    <t>WaveformGeneratorName,XvWingMod,GreenWallMod;ChannelName,Ch1,Ch1;WaveformListName,XvWingGW,GWOneWall</t>
+  </si>
+  <si>
+    <t>PhaseLockName,ImagingLock;Frequency,700000000;VariableName,hw_ImagingNi</t>
+  </si>
+  <si>
+    <t>NiLatticeCCXVRampDown</t>
+  </si>
+  <si>
+    <t>A Bloch oscillation experiment at the non-interacting lattice stage. With band mapping. Testing s-d transfer at 13Er with shorter pulse (reduced from 4.5 to 4 ms).</t>
+  </si>
+  <si>
+    <t>TOP</t>
+  </si>
+  <si>
+    <t>NiLattice</t>
+  </si>
+  <si>
+    <t>None</t>
+  </si>
+  <si>
+    <t>latticehold</t>
+  </si>
+  <si>
+    <t>DensityFit;AtomNumber;CenterFit</t>
+  </si>
+  <si>
+    <t>LSR</t>
+  </si>
+  <si>
+    <t>[784 1265;854 1223;1012 1216;1153 1216;1229 1282;1216 1360;1128 1373;965 1380;834 1382;786 1340]</t>
+  </si>
+  <si>
+    <t>HF</t>
+  </si>
+  <si>
+    <t>Absorption</t>
+  </si>
+  <si>
+    <t>StrongLight</t>
+  </si>
+  <si>
+    <t>BosonicGaussianFit1D</t>
+  </si>
+  <si>
+    <t>None</t>
+  </si>
+  <si>
+    <t>SineFit1D</t>
+  </si>
+  <si>
+    <t>StdErr</t>
+  </si>
+  <si>
+    <t>WaveformGeneratorName,XvWingMod;ChannelName,Ch1;WaveformListName,XvWingLatticeCC</t>
+  </si>
+  <si>
+    <t>PhaseLockName,ImagingLock;Frequency,700000000;VariableName,hw_ImagingNi</t>
+  </si>
+  <si>
+    <t>NiLatticeCCXVRampDown</t>
+  </si>
+  <si>
+    <t>A Bloch oscillation experiment at the non-interacting lattice stage. With band mapping. Testing s-d transfer at 13Er with shorter pulse (reduced from 4.5 to 4 ms).</t>
+  </si>
+  <si>
+    <t>TOP</t>
+  </si>
+  <si>
+    <t>NiLattice</t>
+  </si>
+  <si>
+    <t>None</t>
+  </si>
+  <si>
+    <t>latticehold</t>
+  </si>
+  <si>
+    <t>DensityFit;AtomNumber;CenterFit</t>
+  </si>
+  <si>
+    <t>LSR</t>
+  </si>
+  <si>
+    <t>[784 1265;854 1223;1012 1216;1153 1216;1229 1282;1216 1360;1128 1373;965 1380;834 1382;786 1340]</t>
+  </si>
+  <si>
+    <t>HF</t>
+  </si>
+  <si>
+    <t>Absorption</t>
+  </si>
+  <si>
+    <t>StrongLight</t>
+  </si>
+  <si>
+    <t>BosonicGaussianFit1D</t>
+  </si>
+  <si>
+    <t>None</t>
+  </si>
+  <si>
+    <t>SineFit1D</t>
+  </si>
+  <si>
+    <t>StdErr</t>
+  </si>
+  <si>
+    <t>WaveformGeneratorName,XvWingMod;ChannelName,Ch1;WaveformListName,XvWingLatticeCcRampDown</t>
+  </si>
+  <si>
+    <t>PhaseLockName,ImagingLock;Frequency,700000000;VariableName,hw_ImagingNi</t>
+  </si>
+  <si>
+    <t>NiLatticeCCXVRampDown</t>
+  </si>
+  <si>
+    <t>A Bloch oscillation experiment at the non-interacting lattice stage. With band mapping. Testing s-d transfer at 13Er with shorter pulse (reduced from 4.5 to 4 ms).</t>
+  </si>
+  <si>
+    <t>TOP</t>
+  </si>
+  <si>
+    <t>NiLattice</t>
+  </si>
+  <si>
+    <t>None</t>
+  </si>
+  <si>
+    <t>dummy2</t>
+  </si>
+  <si>
+    <t>DensityFit;AtomNumber;CenterFit</t>
+  </si>
+  <si>
+    <t>LSR</t>
+  </si>
+  <si>
+    <t>[784 1265;854 1223;1012 1216;1153 1216;1229 1282;1216 1360;1128 1373;965 1380;834 1382;786 1340]</t>
+  </si>
+  <si>
+    <t>HF</t>
+  </si>
+  <si>
+    <t>Absorption</t>
+  </si>
+  <si>
+    <t>StrongLight</t>
+  </si>
+  <si>
+    <t>BosonicGaussianFit1D</t>
+  </si>
+  <si>
+    <t>None</t>
+  </si>
+  <si>
+    <t>SineFit1D</t>
+  </si>
+  <si>
+    <t>StdErr</t>
+  </si>
+  <si>
+    <t>WaveformGeneratorName,XvWingMod;ChannelName,Ch1;WaveformListName,XvWingLatticeCcRampDown</t>
+  </si>
+  <si>
+    <t>PhaseLockName,ImagingLock;Frequency,700000000;VariableName,hw_ImagingNi</t>
+  </si>
+  <si>
+    <t>NiLatticeCCXVRampDown</t>
+  </si>
+  <si>
+    <t>A Bloch oscillation experiment at the non-interacting lattice stage. With band mapping. Testing s-d transfer at 13Er with shorter pulse (reduced from 4.5 to 4 ms).</t>
+  </si>
+  <si>
+    <t>TOP</t>
+  </si>
+  <si>
+    <t>NiLattice</t>
+  </si>
+  <si>
+    <t>None</t>
+  </si>
+  <si>
+    <t>dummy2</t>
+  </si>
+  <si>
+    <t>DensityFit;AtomNumber;CenterFit</t>
+  </si>
+  <si>
+    <t>LSR</t>
+  </si>
+  <si>
+    <t>[1008 1230;1386 1210;1391 1288;1007 1303]</t>
+  </si>
+  <si>
+    <t>HF</t>
+  </si>
+  <si>
+    <t>Absorption</t>
+  </si>
+  <si>
+    <t>StrongLight</t>
+  </si>
+  <si>
+    <t>BosonicGaussianFit1D</t>
+  </si>
+  <si>
+    <t>None</t>
+  </si>
+  <si>
+    <t>SineFit1D</t>
+  </si>
+  <si>
+    <t>StdErr</t>
+  </si>
+  <si>
+    <t>WaveformGeneratorName,XvWingMod;ChannelName,Ch1;WaveformListName,XvWingLatticeCcRampDown</t>
+  </si>
+  <si>
+    <t>PhaseLockName,ImagingLock;Frequency,700000000;VariableName,hw_ImagingNi</t>
+  </si>
+  <si>
+    <t>NiLatticeCCXVRampDown</t>
+  </si>
+  <si>
+    <t>A Bloch oscillation experiment at the non-interacting lattice stage. With band mapping. Testing s-d transfer at 13Er with shorter pulse (reduced from 4.5 to 4 ms).</t>
+  </si>
+  <si>
+    <t>TOP</t>
+  </si>
+  <si>
+    <t>NiLattice</t>
+  </si>
+  <si>
+    <t>None</t>
+  </si>
+  <si>
+    <t>GwHoldTime</t>
+  </si>
+  <si>
+    <t>DensityFit;AtomNumber;CenterFit</t>
+  </si>
+  <si>
+    <t>LSR</t>
+  </si>
+  <si>
+    <t>[1008 1230;1386 1210;1391 1288;1007 1303]</t>
+  </si>
+  <si>
+    <t>HF</t>
+  </si>
+  <si>
+    <t>Absorption</t>
+  </si>
+  <si>
+    <t>StrongLight</t>
+  </si>
+  <si>
+    <t>BosonicGaussianFit1D</t>
+  </si>
+  <si>
+    <t>None</t>
+  </si>
+  <si>
+    <t>SineFit1D</t>
+  </si>
+  <si>
+    <t>StdErr</t>
+  </si>
+  <si>
+    <t>WaveformGeneratorName,XvWingMod;ChannelName,Ch1;WaveformListName,XvWingLatticeCcRampDown</t>
+  </si>
+  <si>
+    <t>PhaseLockName,ImagingLock;Frequency,700000000;VariableName,hw_ImagingNi</t>
+  </si>
+  <si>
+    <t>NiLatticeCCXVRampDown</t>
+  </si>
+  <si>
+    <t>A Bloch oscillation experiment at the non-interacting lattice stage. With band mapping. Testing s-d transfer at 13Er with shorter pulse (reduced from 4.5 to 4 ms).</t>
+  </si>
+  <si>
+    <t>TOP</t>
+  </si>
+  <si>
+    <t>NiLattice10MHzGwCavity</t>
+  </si>
+  <si>
+    <t>None</t>
+  </si>
+  <si>
+    <t>GwHoldTime</t>
+  </si>
+  <si>
+    <t>DensityFit;AtomNumber;CenterFit</t>
+  </si>
+  <si>
+    <t>LSR</t>
+  </si>
+  <si>
+    <t>[1008 1230;1386 1210;1391 1288;1007 1303]</t>
+  </si>
+  <si>
+    <t>HF</t>
+  </si>
+  <si>
+    <t>Absorption</t>
+  </si>
+  <si>
+    <t>StrongLight</t>
+  </si>
+  <si>
+    <t>BosonicGaussianFit1D</t>
+  </si>
+  <si>
+    <t>None</t>
+  </si>
+  <si>
+    <t>SineFit1D</t>
+  </si>
+  <si>
+    <t>StdErr</t>
+  </si>
+  <si>
+    <t>WaveformGeneratorName,XvWingMod;ChannelName,Ch1;WaveformListName,XvWingLatticeCcRampDown</t>
+  </si>
+  <si>
+    <t>PhaseLockName,ImagingLock;Frequency,700000000;VariableName,hw_ImagingNi</t>
+  </si>
+  <si>
+    <t>NiLatticeCC</t>
+  </si>
+  <si>
+    <t xml:space="preserve">A Bloch oscillation experiment at the non-interacting lattice stage. </t>
+  </si>
+  <si>
+    <t>TOP</t>
+  </si>
+  <si>
+    <t>NiLattice</t>
+  </si>
+  <si>
+    <t>None</t>
+  </si>
+  <si>
+    <t>latticehold</t>
+  </si>
+  <si>
+    <t>DensityFit;AtomNumber;CenterFit</t>
+  </si>
+  <si>
+    <t>LSR</t>
+  </si>
+  <si>
+    <t>[784 1265;854 1223;1012 1216;1153 1216;1229 1282;1216 1360;1128 1373;965 1380;834 1382;786 1340]</t>
+  </si>
+  <si>
+    <t>HF</t>
+  </si>
+  <si>
+    <t>Absorption</t>
+  </si>
+  <si>
+    <t>StrongLight</t>
+  </si>
+  <si>
+    <t>BosonicGaussianFit1D</t>
+  </si>
+  <si>
+    <t>None</t>
+  </si>
+  <si>
+    <t>SineFit1D</t>
+  </si>
+  <si>
+    <t>StdErr</t>
   </si>
   <si>
     <t>PhaseLockName,ImagingLock;Frequency,700000000;VariableName,hw_ImagingNi</t>
@@ -9788,11 +10217,11 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:V113"/>
+  <dimension ref="A1:V115"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="36.42578125" customWidth="true"/>
-    <col min="2" max="2" width="95.28515625" customWidth="true"/>
+    <col min="2" max="2" width="142.28515625" customWidth="true"/>
     <col min="3" max="3" width="16.42578125" customWidth="true"/>
     <col min="4" max="4" width="25.7109375" customWidth="true"/>
     <col min="5" max="5" width="21.42578125" customWidth="true"/>
@@ -16698,66 +17127,66 @@
     </row>
     <row r="112">
       <c r="A112" s="0" t="s">
-        <v>3092</v>
+        <v>3270</v>
       </c>
       <c r="B112" s="0" t="s">
-        <v>3093</v>
+        <v>3271</v>
       </c>
       <c r="C112" s="0" t="s">
-        <v>3094</v>
+        <v>3272</v>
       </c>
       <c r="D112" s="0" t="s">
-        <v>3095</v>
+        <v>3273</v>
       </c>
       <c r="E112" s="0" t="s">
-        <v>3096</v>
+        <v>3274</v>
       </c>
       <c r="F112" s="0">
         <v>4</v>
       </c>
       <c r="G112" s="0" t="s">
-        <v>3097</v>
+        <v>3275</v>
       </c>
       <c r="H112" s="0" t="s">
-        <v>3098</v>
+        <v>3276</v>
       </c>
       <c r="I112" s="0" t="s">
-        <v>3099</v>
+        <v>3277</v>
       </c>
       <c r="J112" s="0" t="s">
-        <v>3100</v>
+        <v>3278</v>
       </c>
       <c r="K112" s="0" t="s">
-        <v>3101</v>
+        <v>3279</v>
       </c>
       <c r="L112" s="0" t="s">
-        <v>3102</v>
+        <v>3280</v>
       </c>
       <c r="M112" s="0" t="s">
-        <v>3103</v>
+        <v>3281</v>
       </c>
       <c r="N112" s="0">
         <v>2</v>
       </c>
       <c r="O112" s="0" t="s">
-        <v>3104</v>
+        <v>3282</v>
       </c>
       <c r="P112" s="0">
         <v>0.20000000000000001</v>
       </c>
       <c r="Q112" s="0" t="s">
-        <v>3105</v>
+        <v>3283</v>
       </c>
       <c r="R112" s="0" t="s">
-        <v>3106</v>
+        <v>3284</v>
       </c>
       <c r="S112" s="0" t="s">
-        <v>3107</v>
+        <v>3285</v>
       </c>
       <c r="T112" s="0"/>
       <c r="U112" s="0"/>
       <c r="V112" s="0" t="s">
-        <v>3108</v>
+        <v>3286</v>
       </c>
     </row>
     <row r="113">
@@ -16824,6 +17253,138 @@
       </c>
       <c r="V113" s="0" t="s">
         <v>3143</v>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" s="0" t="s">
+        <v>3144</v>
+      </c>
+      <c r="B114" s="0" t="s">
+        <v>3145</v>
+      </c>
+      <c r="C114" s="0" t="s">
+        <v>3146</v>
+      </c>
+      <c r="D114" s="0" t="s">
+        <v>3147</v>
+      </c>
+      <c r="E114" s="0" t="s">
+        <v>3148</v>
+      </c>
+      <c r="F114" s="0">
+        <v>4</v>
+      </c>
+      <c r="G114" s="0" t="s">
+        <v>3149</v>
+      </c>
+      <c r="H114" s="0" t="s">
+        <v>3150</v>
+      </c>
+      <c r="I114" s="0" t="s">
+        <v>3151</v>
+      </c>
+      <c r="J114" s="0" t="s">
+        <v>3152</v>
+      </c>
+      <c r="K114" s="0" t="s">
+        <v>3153</v>
+      </c>
+      <c r="L114" s="0" t="s">
+        <v>3154</v>
+      </c>
+      <c r="M114" s="0" t="s">
+        <v>3155</v>
+      </c>
+      <c r="N114" s="0">
+        <v>2</v>
+      </c>
+      <c r="O114" s="0" t="s">
+        <v>3156</v>
+      </c>
+      <c r="P114" s="0">
+        <v>0.20000000000000001</v>
+      </c>
+      <c r="Q114" s="0" t="s">
+        <v>3157</v>
+      </c>
+      <c r="R114" s="0" t="s">
+        <v>3158</v>
+      </c>
+      <c r="S114" s="0" t="s">
+        <v>3159</v>
+      </c>
+      <c r="T114" s="0"/>
+      <c r="U114" s="0" t="s">
+        <v>3160</v>
+      </c>
+      <c r="V114" s="0" t="s">
+        <v>3161</v>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" s="0" t="s">
+        <v>3252</v>
+      </c>
+      <c r="B115" s="0" t="s">
+        <v>3253</v>
+      </c>
+      <c r="C115" s="0" t="s">
+        <v>3254</v>
+      </c>
+      <c r="D115" s="0" t="s">
+        <v>3255</v>
+      </c>
+      <c r="E115" s="0" t="s">
+        <v>3256</v>
+      </c>
+      <c r="F115" s="0">
+        <v>4</v>
+      </c>
+      <c r="G115" s="0" t="s">
+        <v>3257</v>
+      </c>
+      <c r="H115" s="0" t="s">
+        <v>3258</v>
+      </c>
+      <c r="I115" s="0" t="s">
+        <v>3259</v>
+      </c>
+      <c r="J115" s="0" t="s">
+        <v>3260</v>
+      </c>
+      <c r="K115" s="0" t="s">
+        <v>3261</v>
+      </c>
+      <c r="L115" s="0" t="s">
+        <v>3262</v>
+      </c>
+      <c r="M115" s="0" t="s">
+        <v>3263</v>
+      </c>
+      <c r="N115" s="0">
+        <v>2</v>
+      </c>
+      <c r="O115" s="0" t="s">
+        <v>3264</v>
+      </c>
+      <c r="P115" s="0">
+        <v>0.20000000000000001</v>
+      </c>
+      <c r="Q115" s="0" t="s">
+        <v>3265</v>
+      </c>
+      <c r="R115" s="0" t="s">
+        <v>3266</v>
+      </c>
+      <c r="S115" s="0" t="s">
+        <v>3267</v>
+      </c>
+      <c r="T115" s="0"/>
+      <c r="U115" s="0" t="s">
+        <v>3268</v>
+      </c>
+      <c r="V115" s="0" t="s">
+        <v>3269</v>
       </c>
     </row>
   </sheetData>
